--- a/io betibel.xlsx
+++ b/io betibel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{5ECE58BD-8314-4A0D-8E60-0098AB06E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1982E828-0ED4-46F8-900C-07EA2AD60DD0}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{5ECE58BD-8314-4A0D-8E60-0098AB06E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9A8476-4106-462A-98EE-BBAA3F5E1452}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3A7F3E9-C459-4210-B485-72C402A5A280}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Kode I-O</t>
   </si>
@@ -252,6 +252,30 @@
   </si>
   <si>
     <t>Sektor lain yang tidak jelas batasannya</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>210</t>
   </si>
 </sst>
 </file>
@@ -1083,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="BQ2" s="5">
-        <v>-3.5527136788005009E-12</v>
+        <v>0</v>
       </c>
       <c r="BR2" s="6">
-        <v>-3.5527136788005009E-12</v>
+        <v>0</v>
       </c>
       <c r="BS2" s="5">
-        <v>28430.609999999993</v>
+        <v>28430.609999999997</v>
       </c>
       <c r="BT2" s="5">
         <v>0</v>
@@ -1115,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>4.5783214307264259</v>
+        <v>4.6740295677125525</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -1142,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>63.460514574690002</v>
+        <v>63.647471197291559</v>
       </c>
       <c r="N3" s="5">
-        <v>3.6614889055572424</v>
+        <v>3.6695559782883151</v>
       </c>
       <c r="O3" s="5">
-        <v>437.33874450582243</v>
+        <v>438.01551338354767</v>
       </c>
       <c r="P3" s="5">
         <v>0</v>
@@ -1181,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5">
-        <v>1396.9469394701844</v>
+        <v>1396.4914801270729</v>
       </c>
       <c r="AA3" s="5">
         <v>0</v>
@@ -1190,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="AC3" s="5">
-        <v>2820.266275289272</v>
+        <v>2819.7542339223396</v>
       </c>
       <c r="AD3" s="5">
         <v>0</v>
@@ -1325,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="BV3" s="6">
-        <v>6459.449999999998</v>
+        <v>6459.4499999999989</v>
       </c>
       <c r="BW3" s="1">
-        <v>6459.449999999998</v>
+        <v>6459.4499999999989</v>
       </c>
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.3">
@@ -1345,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>7.5657710118878327</v>
+        <v>5.3604110962406395</v>
       </c>
       <c r="F4" s="5">
         <v>0</v>
@@ -1369,13 +1393,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>10.136793184952815</v>
+        <v>6.5057339274958519</v>
       </c>
       <c r="N4" s="5">
-        <v>0.20894509462052432</v>
+        <v>0.10596541724118191</v>
       </c>
       <c r="O4" s="5">
-        <v>77.80841295282724</v>
+        <v>73.38332869543818</v>
       </c>
       <c r="P4" s="5">
         <v>0</v>
@@ -1408,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="5">
-        <v>1524.9749345397029</v>
+        <v>1586.0683811052581</v>
       </c>
       <c r="AA4" s="5">
         <v>0</v>
@@ -1417,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="5">
-        <v>717.77350253009251</v>
+        <v>667.04453907241009</v>
       </c>
       <c r="AD4" s="5">
         <v>0</v>
@@ -1522,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="BL4" s="6">
-        <v>2338.468359314084</v>
+        <v>2338.4683593140844</v>
       </c>
       <c r="BM4" s="5">
         <v>2464.3816406859164</v>
@@ -1552,10 +1576,10 @@
         <v>0</v>
       </c>
       <c r="BV4" s="6">
-        <v>4802.8500000000004</v>
+        <v>4802.8499999999995</v>
       </c>
       <c r="BW4" s="1">
-        <v>4802.8500000000004</v>
+        <v>4802.8499999999995</v>
       </c>
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.3">
@@ -1575,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>542.70432963472979</v>
+        <v>563.13268295633691</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -1638,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="5">
-        <v>8412.6271769535488</v>
+        <v>8405.3764052411607</v>
       </c>
       <c r="AB5" s="5">
         <v>0</v>
@@ -1716,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="BA5" s="5">
-        <v>16713.043811963696</v>
+        <v>16699.866230354473</v>
       </c>
       <c r="BB5" s="5">
         <v>0</v>
@@ -1749,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="BL5" s="6">
-        <v>25668.375318551974</v>
+        <v>25668.375318551971</v>
       </c>
       <c r="BM5" s="5">
         <v>45960.044681448038</v>
@@ -1805,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>582.4362511063166</v>
+        <v>564.21121627168577</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -1865,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="5">
-        <v>13640.301750668646</v>
+        <v>13756.175965667955</v>
       </c>
       <c r="AB6" s="5">
         <v>0</v>
@@ -1874,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="5">
-        <v>5602.0783127400719</v>
+        <v>5464.6436225690704</v>
       </c>
       <c r="AE6" s="5">
         <v>0</v>
@@ -1943,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="BA6" s="5">
-        <v>18303.957921787583</v>
+        <v>18343.743431793951</v>
       </c>
       <c r="BB6" s="5">
         <v>0</v>
@@ -1976,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="BL6" s="6">
-        <v>38128.774236302619</v>
+        <v>38128.774236302663</v>
       </c>
       <c r="BM6" s="5">
         <v>39829.249763697393</v>
@@ -1997,7 +2021,7 @@
         <v>39829.249763697393</v>
       </c>
       <c r="BS6" s="5">
-        <v>77958.024000000005</v>
+        <v>77958.024000000063</v>
       </c>
       <c r="BT6" s="5">
         <v>0</v>
@@ -2035,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>109891.70069282265</v>
+        <v>110501.10739909273</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -2086,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="Y7" s="5">
-        <v>1477009.7638833735</v>
+        <v>1478551.7118463269</v>
       </c>
       <c r="Z7" s="5">
         <v>0</v>
@@ -2203,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="BL7" s="6">
-        <v>1586901.4645761962</v>
+        <v>1589052.8192454197</v>
       </c>
       <c r="BM7" s="5">
         <v>0</v>
@@ -2212,16 +2236,16 @@
         <v>0</v>
       </c>
       <c r="BO7" s="5">
-        <v>251312</v>
+        <v>254312</v>
       </c>
       <c r="BP7" s="5">
-        <v>23823.786072251642</v>
+        <v>23823.786072251645</v>
       </c>
       <c r="BQ7" s="5">
-        <v>2726061.2680556863</v>
+        <v>2720909.9133864632</v>
       </c>
       <c r="BR7" s="6">
-        <v>3001197.0541279381</v>
+        <v>2999045.6994587146</v>
       </c>
       <c r="BS7" s="5">
         <v>4588098.518704134</v>
@@ -2233,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="BV7" s="6">
-        <v>4588098.518704134</v>
+        <v>4588098.518704135</v>
       </c>
       <c r="BW7" s="1">
-        <v>4588098.518704134</v>
+        <v>4588098.518704135</v>
       </c>
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.3">
@@ -2265,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>20528.064899147761</v>
+        <v>20691.322598833161</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -2274,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>0</v>
+        <v>272.25734532923332</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -2322,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="5">
-        <v>20689.473509334857</v>
+        <v>20971.679182715143</v>
       </c>
       <c r="AC8" s="5">
         <v>0</v>
@@ -2394,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AZ8" s="5">
-        <v>0</v>
+        <v>124.54569400144639</v>
       </c>
       <c r="BA8" s="5">
-        <v>0</v>
+        <v>605.28595448967576</v>
       </c>
       <c r="BB8" s="5">
         <v>0</v>
@@ -2430,10 +2454,10 @@
         <v>0</v>
       </c>
       <c r="BL8" s="6">
-        <v>41217.538408482622</v>
+        <v>42665.090775368662</v>
       </c>
       <c r="BM8" s="5">
-        <v>19410.478421052634</v>
+        <v>19232.036842105266</v>
       </c>
       <c r="BN8" s="5">
         <v>0</v>
@@ -2442,16 +2466,16 @@
         <v>0</v>
       </c>
       <c r="BP8" s="5">
-        <v>7217.1073765132642</v>
+        <v>207217.10737651328</v>
       </c>
       <c r="BQ8" s="5">
-        <v>1164006.550916489</v>
+        <v>962737.44012855063</v>
       </c>
       <c r="BR8" s="6">
-        <v>1190634.136714055</v>
+        <v>1189186.5843471691</v>
       </c>
       <c r="BS8" s="5">
-        <v>1231851.6751225377</v>
+        <v>1231851.6751225379</v>
       </c>
       <c r="BT8" s="5">
         <v>0</v>
@@ -2495,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>7492.6252724058877</v>
+        <v>7543.4119556413043</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -2567,10 +2591,10 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5">
-        <v>0</v>
+        <v>208.0672027483817</v>
       </c>
       <c r="AI9" s="5">
-        <v>29880.961957018462</v>
+        <v>35790.729682082805</v>
       </c>
       <c r="AJ9" s="5">
         <v>0</v>
@@ -2582,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="AM9" s="5">
-        <v>0</v>
+        <v>23.413712758031167</v>
       </c>
       <c r="AN9" s="5">
-        <v>0</v>
+        <v>172.65429661902994</v>
       </c>
       <c r="AO9" s="5">
         <v>0</v>
@@ -2657,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="BL9" s="6">
-        <v>37373.587229424353</v>
+        <v>43738.276849849557</v>
       </c>
       <c r="BM9" s="5">
         <v>0</v>
@@ -2672,10 +2696,10 @@
         <v>394.93830478748021</v>
       </c>
       <c r="BQ9" s="5">
-        <v>281337.92040324118</v>
+        <v>274973.23078281595</v>
       </c>
       <c r="BR9" s="6">
-        <v>281732.85870802868</v>
+        <v>275368.16908760346</v>
       </c>
       <c r="BS9" s="5">
         <v>319106.44593745301</v>
@@ -2725,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>611.84283405784151</v>
+        <v>633.17283777401894</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
@@ -2776,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="5">
-        <v>7033.5389994923707</v>
+        <v>7326.3755990971349</v>
       </c>
       <c r="AC10" s="5">
         <v>0</v>
@@ -2851,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="BA10" s="5">
-        <v>0</v>
+        <v>778.77251114977048</v>
       </c>
       <c r="BB10" s="5">
         <v>0</v>
@@ -2884,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="BL10" s="6">
-        <v>7645.3818335502119</v>
+        <v>8738.3209480209243</v>
       </c>
       <c r="BM10" s="5">
-        <v>32301.287201872703</v>
+        <v>31621.28460862226</v>
       </c>
       <c r="BN10" s="5">
         <v>0</v>
@@ -2899,25 +2923,25 @@
         <v>39.034599891785845</v>
       </c>
       <c r="BQ10" s="5">
-        <v>7421.889121568207</v>
+        <v>7008.952600347935</v>
       </c>
       <c r="BR10" s="6">
-        <v>39762.210923332699</v>
+        <v>38669.27180886198</v>
       </c>
       <c r="BS10" s="5">
+        <v>47407.592756882907</v>
+      </c>
+      <c r="BT10" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU10" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV10" s="6">
         <v>47407.592756882914</v>
       </c>
-      <c r="BT10" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU10" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV10" s="6">
-        <v>47407.592756882907</v>
-      </c>
       <c r="BW10" s="1">
-        <v>47407.592756882907</v>
+        <v>47407.592756882914</v>
       </c>
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.3">
@@ -2937,16 +2961,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="5">
-        <v>78.422585971781274</v>
+        <v>73.216303014378354</v>
       </c>
       <c r="G11" s="5">
-        <v>284.28234608811471</v>
+        <v>265.40953231786352</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>911.44845658702343</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
@@ -2955,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>9712.3360375519569</v>
+        <v>10077.189992157637</v>
       </c>
       <c r="M11" s="5">
-        <v>0</v>
+        <v>36.879904479343253</v>
       </c>
       <c r="N11" s="5">
         <v>0</v>
@@ -2970,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="5">
-        <v>886.41560284525201</v>
+        <v>827.56862072727824</v>
       </c>
       <c r="R11" s="5">
         <v>0</v>
@@ -3000,19 +3024,19 @@
         <v>0</v>
       </c>
       <c r="AA11" s="5">
-        <v>0</v>
+        <v>767.4479493310165</v>
       </c>
       <c r="AB11" s="5">
-        <v>40354.665850636287</v>
+        <v>70397.365040764329</v>
       </c>
       <c r="AC11" s="5">
-        <v>0</v>
+        <v>381.02698007137508</v>
       </c>
       <c r="AD11" s="5">
-        <v>10649.409847278946</v>
+        <v>11544.390414747068</v>
       </c>
       <c r="AE11" s="5">
-        <v>3696.5901533101173</v>
+        <v>3705.6997154579562</v>
       </c>
       <c r="AF11" s="5">
         <v>0</v>
@@ -3021,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5">
-        <v>12999.276733604802</v>
+        <v>12013.774786927437</v>
       </c>
       <c r="AI11" s="5">
         <v>0</v>
@@ -3042,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="5">
-        <v>0</v>
+        <v>1057.5806478551344</v>
       </c>
       <c r="AP11" s="5">
         <v>0</v>
@@ -3078,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="BA11" s="5">
-        <v>0</v>
+        <v>1000.1059755451967</v>
       </c>
       <c r="BB11" s="5">
         <v>0</v>
@@ -3105,31 +3129,31 @@
         <v>0</v>
       </c>
       <c r="BJ11" s="5">
-        <v>0</v>
+        <v>44.745175379551426</v>
       </c>
       <c r="BK11" s="5">
         <v>0</v>
       </c>
       <c r="BL11" s="6">
-        <v>78661.399157287262</v>
+        <v>113103.84949536259</v>
       </c>
       <c r="BM11" s="5">
-        <v>5850.2783117565632</v>
+        <v>3033.051628408632</v>
       </c>
       <c r="BN11" s="5">
         <v>0</v>
       </c>
       <c r="BO11" s="5">
-        <v>4980.3673469387759</v>
+        <v>0</v>
       </c>
       <c r="BP11" s="5">
-        <v>225.26492683819583</v>
+        <v>0</v>
       </c>
       <c r="BQ11" s="5">
-        <v>473042.94853634358</v>
+        <v>446623.35715539317</v>
       </c>
       <c r="BR11" s="6">
-        <v>484098.85912187712</v>
+        <v>449656.40878380177</v>
       </c>
       <c r="BS11" s="5">
         <v>562760.25827916432</v>
@@ -3227,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="AA12" s="5">
-        <v>11626.031300493303</v>
+        <v>11626.031300493301</v>
       </c>
       <c r="AB12" s="5">
         <v>0</v>
@@ -3338,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="BL12" s="6">
-        <v>22361.26303556568</v>
+        <v>22361.263035565677</v>
       </c>
       <c r="BM12" s="5">
-        <v>30182.901964434321</v>
+        <v>272.90196443432069</v>
       </c>
       <c r="BN12" s="5">
         <v>0</v>
       </c>
       <c r="BO12" s="5">
-        <v>8321</v>
+        <v>38231</v>
       </c>
       <c r="BP12" s="5">
         <v>0</v>
@@ -3359,7 +3383,7 @@
         <v>38503.901964434321</v>
       </c>
       <c r="BS12" s="5">
-        <v>60865.165000000001</v>
+        <v>60865.164999999994</v>
       </c>
       <c r="BT12" s="5">
         <v>0</v>
@@ -3368,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="BV12" s="6">
-        <v>60865.165000000001</v>
+        <v>60865.165000000008</v>
       </c>
       <c r="BW12" s="1">
-        <v>60865.165000000001</v>
+        <v>60865.165000000008</v>
       </c>
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.3">
@@ -3681,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="5">
-        <v>35929.253841178062</v>
+        <v>37046.182956137702</v>
       </c>
       <c r="AB14" s="5">
-        <v>24353.76593292637</v>
+        <v>26195.1625126828</v>
       </c>
       <c r="AC14" s="5">
         <v>0</v>
@@ -3759,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="BA14" s="5">
-        <v>39579.857786368615</v>
+        <v>42598.752647510191</v>
       </c>
       <c r="BB14" s="5">
         <v>0</v>
@@ -3792,28 +3816,28 @@
         <v>0</v>
       </c>
       <c r="BL14" s="6">
-        <v>99862.877560473047</v>
+        <v>105840.09811633069</v>
       </c>
       <c r="BM14" s="5">
-        <v>202995.67917541997</v>
+        <v>198505.00203915228</v>
       </c>
       <c r="BN14" s="5">
         <v>0</v>
       </c>
       <c r="BO14" s="5">
-        <v>10647.288368478914</v>
+        <v>9569.9445374155257</v>
       </c>
       <c r="BP14" s="5">
-        <v>228.62828330767715</v>
+        <v>205.49457431963671</v>
       </c>
       <c r="BQ14" s="5">
-        <v>12355.496612320438</v>
+        <v>11969.430732781844</v>
       </c>
       <c r="BR14" s="6">
-        <v>226227.09243952701</v>
+        <v>220249.87188366929</v>
       </c>
       <c r="BS14" s="5">
-        <v>326089.97000000009</v>
+        <v>326089.96999999997</v>
       </c>
       <c r="BT14" s="5">
         <v>0</v>
@@ -3822,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="BV14" s="6">
-        <v>326089.97000000009</v>
+        <v>326089.96999999997</v>
       </c>
       <c r="BW14" s="1">
-        <v>326089.97000000009</v>
+        <v>326089.96999999997</v>
       </c>
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.3">
@@ -3836,55 +3860,55 @@
         <v>16</v>
       </c>
       <c r="C15" s="5">
-        <v>590.30284310482352</v>
+        <v>593.7674510405036</v>
       </c>
       <c r="D15" s="5">
-        <v>100.03630415885603</v>
+        <v>99.702066984019694</v>
       </c>
       <c r="E15" s="5">
-        <v>71.501821802603388</v>
+        <v>70.907391131248346</v>
       </c>
       <c r="F15" s="5">
-        <v>1215.4112720149733</v>
+        <v>1203.7798813216402</v>
       </c>
       <c r="G15" s="5">
-        <v>1372.7757588049903</v>
+        <v>1366.9268229811821</v>
       </c>
       <c r="H15" s="5">
-        <v>144539.84603669806</v>
+        <v>144699.77202480368</v>
       </c>
       <c r="I15" s="5">
-        <v>23833.849218651278</v>
+        <v>23751.605624514006</v>
       </c>
       <c r="J15" s="5">
-        <v>9559.4253562500762</v>
+        <v>9527.5154334891486</v>
       </c>
       <c r="K15" s="5">
-        <v>759.12719133031294</v>
+        <v>753.16350377482763</v>
       </c>
       <c r="L15" s="5">
-        <v>12726.710287895845</v>
+        <v>12709.199348369544</v>
       </c>
       <c r="M15" s="5">
-        <v>533.01007414623803</v>
+        <v>531.14067576834873</v>
       </c>
       <c r="N15" s="5">
-        <v>28.346786409727084</v>
+        <v>27.570665808569391</v>
       </c>
       <c r="O15" s="5">
-        <v>2656.2013263316094</v>
+        <v>2654.0536012383104</v>
       </c>
       <c r="P15" s="5">
         <v>0</v>
       </c>
       <c r="Q15" s="5">
-        <v>1612.2885647967239</v>
+        <v>1620.5059532472369</v>
       </c>
       <c r="R15" s="5">
         <v>0</v>
       </c>
       <c r="S15" s="5">
-        <v>101.36702435936537</v>
+        <v>90.589422283214958</v>
       </c>
       <c r="T15" s="5">
         <v>0</v>
@@ -4019,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="BL15" s="6">
-        <v>199700.19986675549</v>
+        <v>199700.19986675552</v>
       </c>
       <c r="BM15" s="5">
         <v>0</v>
@@ -4040,7 +4064,7 @@
         <v>2.4868995751603507E-11</v>
       </c>
       <c r="BS15" s="5">
-        <v>199700.19986675552</v>
+        <v>199700.19986675555</v>
       </c>
       <c r="BT15" s="5">
         <v>0</v>
@@ -4150,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="AF16" s="5">
-        <v>82958.307666782654</v>
+        <v>84261.026406128454</v>
       </c>
       <c r="AG16" s="5">
-        <v>10091.886579230102</v>
+        <v>10215.053178681368</v>
       </c>
       <c r="AH16" s="5">
         <v>0</v>
@@ -4189,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="5">
-        <v>0</v>
+        <v>5141.5627824183957</v>
       </c>
       <c r="AT16" s="5">
         <v>0</v>
@@ -4246,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="BL16" s="6">
-        <v>93050.194246012761</v>
+        <v>99617.642367228211</v>
       </c>
       <c r="BM16" s="5">
         <v>3469.5004887994933</v>
@@ -4261,10 +4285,10 @@
         <v>0</v>
       </c>
       <c r="BQ16" s="5">
-        <v>52841.513162981006</v>
+        <v>46274.065041765556</v>
       </c>
       <c r="BR16" s="6">
-        <v>56311.0136517805</v>
+        <v>49743.565530565051</v>
       </c>
       <c r="BS16" s="5">
         <v>149361.20789779327</v>
@@ -4326,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="5">
-        <v>0</v>
+        <v>34.782938186861415</v>
       </c>
       <c r="P17" s="5">
         <v>0</v>
@@ -4338,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="5">
-        <v>0</v>
+        <v>43.278364855012782</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
@@ -4353,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="X17" s="5">
-        <v>226803.53444558859</v>
+        <v>242126.21931322481</v>
       </c>
       <c r="Y17" s="5">
         <v>0</v>
@@ -4362,13 +4386,13 @@
         <v>0</v>
       </c>
       <c r="AA17" s="5">
-        <v>8638.9375638328474</v>
+        <v>9305.0290418467976</v>
       </c>
       <c r="AB17" s="5">
         <v>0</v>
       </c>
       <c r="AC17" s="5">
-        <v>16893.216372420131</v>
+        <v>17035.682374641379</v>
       </c>
       <c r="AD17" s="5">
         <v>0</v>
@@ -4404,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="AO17" s="5">
-        <v>0</v>
+        <v>43.817847844850746</v>
       </c>
       <c r="AP17" s="5">
         <v>0</v>
@@ -4428,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="AW17" s="5">
-        <v>0</v>
+        <v>334.18283465818882</v>
       </c>
       <c r="AX17" s="5">
         <v>0</v>
@@ -4437,10 +4461,10 @@
         <v>0</v>
       </c>
       <c r="AZ17" s="5">
-        <v>0</v>
+        <v>46.816550000970665</v>
       </c>
       <c r="BA17" s="5">
-        <v>81442.639229603024</v>
+        <v>86206.423912637838</v>
       </c>
       <c r="BB17" s="5">
         <v>0</v>
@@ -4464,19 +4488,19 @@
         <v>0</v>
       </c>
       <c r="BI17" s="5">
-        <v>0</v>
+        <v>816.01379066029222</v>
       </c>
       <c r="BJ17" s="5">
-        <v>0</v>
+        <v>159.85389502371942</v>
       </c>
       <c r="BK17" s="5">
         <v>0</v>
       </c>
       <c r="BL17" s="6">
-        <v>333778.32761144463</v>
+        <v>356152.10086358071</v>
       </c>
       <c r="BM17" s="5">
-        <v>1430434.3827841068</v>
+        <v>1405724.4545384343</v>
       </c>
       <c r="BN17" s="5">
         <v>0</v>
@@ -4485,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="BP17" s="5">
-        <v>11466.307845276071</v>
+        <v>11368.970465509861</v>
       </c>
       <c r="BQ17" s="5">
-        <v>613695.64175917278</v>
+        <v>616129.13413247524</v>
       </c>
       <c r="BR17" s="6">
-        <v>2055596.3323885556</v>
+        <v>2033222.5591364196</v>
       </c>
       <c r="BS17" s="5">
         <v>2389374.66</v>
@@ -4503,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="BV17" s="6">
-        <v>2389374.66</v>
+        <v>2389374.6600000006</v>
       </c>
       <c r="BW17" s="1">
-        <v>2389374.66</v>
+        <v>2389374.6600000006</v>
       </c>
     </row>
     <row r="18" spans="1:75" x14ac:dyDescent="0.3">
@@ -4580,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="5">
-        <v>17250.422364755472</v>
+        <v>18042.295699831517</v>
       </c>
       <c r="Y18" s="5">
         <v>0</v>
@@ -4700,10 +4724,10 @@
         <v>0</v>
       </c>
       <c r="BL18" s="6">
-        <v>17250.422364755472</v>
+        <v>18042.295699831517</v>
       </c>
       <c r="BM18" s="5">
-        <v>66462.139558527153</v>
+        <v>63294.646218222973</v>
       </c>
       <c r="BN18" s="5">
         <v>0</v>
@@ -4715,10 +4739,10 @@
         <v>234.14514626112199</v>
       </c>
       <c r="BQ18" s="5">
-        <v>4751.2400104562648</v>
+        <v>7126.8600156843968</v>
       </c>
       <c r="BR18" s="6">
-        <v>71447.524715244537</v>
+        <v>70655.651380168492</v>
       </c>
       <c r="BS18" s="5">
         <v>88697.947080000013</v>
@@ -4730,10 +4754,10 @@
         <v>0</v>
       </c>
       <c r="BV18" s="6">
-        <v>88697.947079999998</v>
+        <v>88697.947080000013</v>
       </c>
       <c r="BW18" s="1">
-        <v>88697.947079999998</v>
+        <v>88697.947080000013</v>
       </c>
     </row>
     <row r="19" spans="1:75" x14ac:dyDescent="0.3">
@@ -4846,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="5">
-        <v>780219.03456689464</v>
+        <v>844252.04868903605</v>
       </c>
       <c r="AL19" s="5">
         <v>0</v>
@@ -4858,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="5">
-        <v>0</v>
+        <v>190.50558425280281</v>
       </c>
       <c r="AP19" s="5">
         <v>0</v>
@@ -4927,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="BL19" s="6">
-        <v>780219.03456689464</v>
+        <v>844442.55427328881</v>
       </c>
       <c r="BM19" s="5">
         <v>0</v>
@@ -4942,10 +4966,10 @@
         <v>11430.09738011471</v>
       </c>
       <c r="BQ19" s="5">
-        <v>1818375.2760646956</v>
+        <v>1754151.7563583013</v>
       </c>
       <c r="BR19" s="6">
-        <v>1829805.3734448103</v>
+        <v>1765581.853738416</v>
       </c>
       <c r="BS19" s="5">
         <v>2610024.4080117047</v>
@@ -4957,10 +4981,10 @@
         <v>0</v>
       </c>
       <c r="BV19" s="6">
-        <v>2610024.4080117047</v>
+        <v>2610024.4080117038</v>
       </c>
       <c r="BW19" s="1">
-        <v>2610024.4080117047</v>
+        <v>2610024.4080117038</v>
       </c>
     </row>
     <row r="20" spans="1:75" x14ac:dyDescent="0.3">
@@ -5064,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="AH20" s="5">
-        <v>0</v>
+        <v>1438.9990862961047</v>
       </c>
       <c r="AI20" s="5">
         <v>0</v>
       </c>
       <c r="AJ20" s="5">
-        <v>353031.48787183943</v>
+        <v>354477.82202043239</v>
       </c>
       <c r="AK20" s="5">
-        <v>0</v>
+        <v>630.11953922137661</v>
       </c>
       <c r="AL20" s="5">
         <v>0</v>
@@ -5154,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="BL20" s="6">
-        <v>353031.48787183943</v>
+        <v>356546.94064594992</v>
       </c>
       <c r="BM20" s="5">
         <v>0</v>
@@ -5169,10 +5193,10 @@
         <v>3712.5709330153941</v>
       </c>
       <c r="BQ20" s="5">
-        <v>328239.64379223494</v>
+        <v>324724.19101812452</v>
       </c>
       <c r="BR20" s="6">
-        <v>331952.21472525032</v>
+        <v>328436.7619511399</v>
       </c>
       <c r="BS20" s="5">
         <v>684983.70259708981</v>
@@ -5184,10 +5208,10 @@
         <v>0</v>
       </c>
       <c r="BV20" s="6">
-        <v>684983.70259708969</v>
+        <v>684983.70259708981</v>
       </c>
       <c r="BW20" s="1">
-        <v>684983.70259708969</v>
+        <v>684983.70259708981</v>
       </c>
     </row>
     <row r="21" spans="1:75" x14ac:dyDescent="0.3">
@@ -5297,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="AJ21" s="5">
-        <v>152211.43362525833</v>
+        <v>154196.59814293493</v>
       </c>
       <c r="AK21" s="5">
         <v>0</v>
@@ -5324,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="AS21" s="5">
-        <v>0</v>
+        <v>5585.9077743680318</v>
       </c>
       <c r="AT21" s="5">
         <v>0</v>
@@ -5381,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="BL21" s="6">
-        <v>152211.43362525833</v>
+        <v>159782.50591730297</v>
       </c>
       <c r="BM21" s="5">
         <v>0</v>
@@ -5396,25 +5420,25 @@
         <v>454.03048829682774</v>
       </c>
       <c r="BQ21" s="5">
-        <v>57844.2422613569</v>
+        <v>50273.169969312279</v>
       </c>
       <c r="BR21" s="6">
-        <v>58298.272749653726</v>
+        <v>50727.200457609106</v>
       </c>
       <c r="BS21" s="5">
+        <v>210509.70637491209</v>
+      </c>
+      <c r="BT21" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU21" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV21" s="6">
         <v>210509.70637491206</v>
       </c>
-      <c r="BT21" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU21" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV21" s="6">
-        <v>210509.70637491212</v>
-      </c>
       <c r="BW21" s="1">
-        <v>210509.70637491212</v>
+        <v>210509.70637491206</v>
       </c>
     </row>
     <row r="22" spans="1:75" x14ac:dyDescent="0.3">
@@ -5476,13 +5500,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="5">
-        <v>119262.31893304789</v>
+        <v>119479.86660052396</v>
       </c>
       <c r="U22" s="5">
-        <v>29393.37030923491</v>
+        <v>29180.289080762515</v>
       </c>
       <c r="V22" s="5">
-        <v>9883.5922402014603</v>
+        <v>9879.1258011977916</v>
       </c>
       <c r="W22" s="5">
         <v>0</v>
@@ -5638,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="BV22" s="6">
-        <v>184326.07852531195</v>
+        <v>184326.07852531201</v>
       </c>
       <c r="BW22" s="1">
-        <v>184326.07852531195</v>
+        <v>184326.07852531201</v>
       </c>
     </row>
     <row r="23" spans="1:75" x14ac:dyDescent="0.3">
@@ -5715,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="5">
-        <v>0</v>
+        <v>780.94252578536657</v>
       </c>
       <c r="Y23" s="5">
         <v>0</v>
@@ -5730,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="AC23" s="5">
-        <v>6959.8608609821958</v>
+        <v>7458.7347441437114</v>
       </c>
       <c r="AD23" s="5">
         <v>0</v>
@@ -5790,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="AW23" s="5">
-        <v>0</v>
+        <v>386.76679585873342</v>
       </c>
       <c r="AX23" s="5">
         <v>0</v>
@@ -5799,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="AZ23" s="5">
-        <v>7126.7697594501715</v>
+        <v>6873.5997335552102</v>
       </c>
       <c r="BA23" s="5">
-        <v>30401.314259296567</v>
+        <v>35486.638462127215</v>
       </c>
       <c r="BB23" s="5">
         <v>0</v>
@@ -5835,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="BL23" s="6">
-        <v>44487.944879728937</v>
+        <v>50986.68226147024</v>
       </c>
       <c r="BM23" s="5">
-        <v>312623.12728131982</v>
+        <v>307666.41675500397</v>
       </c>
       <c r="BN23" s="5">
         <v>0</v>
@@ -5850,13 +5874,13 @@
         <v>4690.0921529102798</v>
       </c>
       <c r="BQ23" s="5">
-        <v>468653.75977442949</v>
+        <v>467111.73291900399</v>
       </c>
       <c r="BR23" s="6">
-        <v>785966.97920865961</v>
+        <v>779468.24182691821</v>
       </c>
       <c r="BS23" s="5">
-        <v>830454.92408838856</v>
+        <v>830454.92408838845</v>
       </c>
       <c r="BT23" s="5">
         <v>0</v>
@@ -5909,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="5">
-        <v>0</v>
+        <v>45.446686218058034</v>
       </c>
       <c r="N24" s="5">
         <v>0</v>
@@ -5945,19 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Y24" s="5">
-        <v>0</v>
+        <v>23861.422478764012</v>
       </c>
       <c r="Z24" s="5">
         <v>0</v>
       </c>
       <c r="AA24" s="5">
-        <v>0</v>
+        <v>2131.4632273767347</v>
       </c>
       <c r="AB24" s="5">
-        <v>45498.658976630461</v>
+        <v>45572.078525656281</v>
       </c>
       <c r="AC24" s="5">
-        <v>5519.729486917242</v>
+        <v>5966.9877953149689</v>
       </c>
       <c r="AD24" s="5">
         <v>0</v>
@@ -5972,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="5">
-        <v>0</v>
+        <v>4128.0623245098432</v>
       </c>
       <c r="AI24" s="5">
         <v>0</v>
@@ -6017,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="AW24" s="5">
-        <v>0</v>
+        <v>725.17610688497598</v>
       </c>
       <c r="AX24" s="5">
         <v>0</v>
@@ -6026,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="AZ24" s="5">
-        <v>0</v>
+        <v>3240.7762192090559</v>
       </c>
       <c r="BA24" s="5">
-        <v>26601.149976884495</v>
+        <v>46551.357186177338</v>
       </c>
       <c r="BB24" s="5">
         <v>0</v>
@@ -6050,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="BH24" s="5">
-        <v>0</v>
+        <v>402.28300848362693</v>
       </c>
       <c r="BI24" s="5">
-        <v>0</v>
+        <v>578.98621582614169</v>
       </c>
       <c r="BJ24" s="5">
         <v>0</v>
@@ -6062,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="BL24" s="6">
-        <v>77619.538440432196</v>
+        <v>133204.03977442102</v>
       </c>
       <c r="BM24" s="5">
         <v>902497.87190165475</v>
@@ -6074,16 +6098,16 @@
         <v>0</v>
       </c>
       <c r="BP24" s="5">
-        <v>11002.836554484218</v>
+        <v>11002.83655448422</v>
       </c>
       <c r="BQ24" s="5">
-        <v>1767989.5468064682</v>
+        <v>1712405.0454724792</v>
       </c>
       <c r="BR24" s="6">
-        <v>2681490.2552626072</v>
+        <v>2625905.753928618</v>
       </c>
       <c r="BS24" s="5">
-        <v>2759109.7937030396</v>
+        <v>2759109.7937030392</v>
       </c>
       <c r="BT24" s="5">
         <v>0</v>
@@ -6092,10 +6116,10 @@
         <v>0</v>
       </c>
       <c r="BV24" s="6">
-        <v>2759109.7937030387</v>
+        <v>2759109.7937030392</v>
       </c>
       <c r="BW24" s="1">
-        <v>2759109.7937030387</v>
+        <v>2759109.7937030392</v>
       </c>
     </row>
     <row r="25" spans="1:75" x14ac:dyDescent="0.3">
@@ -6181,10 +6205,10 @@
         <v>0</v>
       </c>
       <c r="AB25" s="5">
-        <v>150820.14244811883</v>
+        <v>152711.23246084328</v>
       </c>
       <c r="AC25" s="5">
-        <v>14698.437689311979</v>
+        <v>12807.347676587544</v>
       </c>
       <c r="AD25" s="5">
         <v>0</v>
@@ -6289,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="BL25" s="6">
-        <v>202893.63951390359</v>
+        <v>202893.63951390362</v>
       </c>
       <c r="BM25" s="5">
         <v>260722.33575930385</v>
@@ -6319,10 +6343,10 @@
         <v>0</v>
       </c>
       <c r="BV25" s="6">
-        <v>464308.74238864298</v>
+        <v>464308.74238864309</v>
       </c>
       <c r="BW25" s="1">
-        <v>464308.74238864298</v>
+        <v>464308.74238864309</v>
       </c>
     </row>
     <row r="26" spans="1:75" x14ac:dyDescent="0.3">
@@ -6411,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="5">
-        <v>3772.2163439893588</v>
+        <v>3730.9939992598938</v>
       </c>
       <c r="AD26" s="5">
         <v>0</v>
@@ -6480,10 +6504,10 @@
         <v>0</v>
       </c>
       <c r="AZ26" s="5">
-        <v>14109.615662154351</v>
+        <v>14299.476707883819</v>
       </c>
       <c r="BA26" s="5">
-        <v>115425.42264582333</v>
+        <v>115944.67754753583</v>
       </c>
       <c r="BB26" s="5">
         <v>0</v>
@@ -6507,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="5">
-        <v>13211.680677911341</v>
+        <v>12543.787075198805</v>
       </c>
       <c r="BJ26" s="5">
         <v>0</v>
@@ -6516,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="BL26" s="6">
-        <v>146518.93532987838</v>
+        <v>146518.93532987835</v>
       </c>
       <c r="BM26" s="5">
-        <v>390984.74445408623</v>
+        <v>390984.74445408618</v>
       </c>
       <c r="BN26" s="5">
         <v>0</v>
@@ -6534,10 +6558,10 @@
         <v>0</v>
       </c>
       <c r="BR26" s="6">
-        <v>391925.3800332208</v>
+        <v>391925.38003322075</v>
       </c>
       <c r="BS26" s="5">
-        <v>538444.31536309922</v>
+        <v>538444.3153630991</v>
       </c>
       <c r="BT26" s="5">
         <v>0</v>
@@ -6546,10 +6570,10 @@
         <v>0</v>
       </c>
       <c r="BV26" s="6">
-        <v>538444.31536309922</v>
+        <v>538444.3153630991</v>
       </c>
       <c r="BW26" s="1">
-        <v>538444.31536309922</v>
+        <v>538444.3153630991</v>
       </c>
     </row>
     <row r="27" spans="1:75" x14ac:dyDescent="0.3">
@@ -6641,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="5">
-        <v>7054.4272967844581</v>
+        <v>7873.2569992989465</v>
       </c>
       <c r="AE27" s="5">
         <v>0</v>
@@ -6707,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="AZ27" s="5">
-        <v>13382.740070148257</v>
+        <v>15128.712304092609</v>
       </c>
       <c r="BA27" s="5">
-        <v>71327.742814385303</v>
+        <v>79730.829971568441</v>
       </c>
       <c r="BB27" s="5">
         <v>0</v>
@@ -6728,13 +6752,13 @@
         <v>0</v>
       </c>
       <c r="BG27" s="5">
-        <v>11987.240796110214</v>
+        <v>16962.022428234886</v>
       </c>
       <c r="BH27" s="5">
-        <v>2434.9672332793912</v>
+        <v>2692.1197370850887</v>
       </c>
       <c r="BI27" s="5">
-        <v>8907.1513319447058</v>
+        <v>9661.5416454834249</v>
       </c>
       <c r="BJ27" s="5">
         <v>0</v>
@@ -6743,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="BL27" s="6">
-        <v>115094.26954265233</v>
+        <v>132048.48308576338</v>
       </c>
       <c r="BM27" s="5">
-        <v>858912.41775863105</v>
+        <v>841692.96167772962</v>
       </c>
       <c r="BN27" s="5">
         <v>0</v>
@@ -6755,13 +6779,13 @@
         <v>0</v>
       </c>
       <c r="BP27" s="5">
-        <v>5420.1278393363154</v>
+        <v>5362.918450182613</v>
       </c>
       <c r="BQ27" s="5">
-        <v>94293.976769274828</v>
+        <v>94616.428696218733</v>
       </c>
       <c r="BR27" s="6">
-        <v>958626.52236724214</v>
+        <v>941672.30882413103</v>
       </c>
       <c r="BS27" s="5">
         <v>1073720.7919098944</v>
@@ -6773,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="BV27" s="6">
-        <v>1073720.7919098942</v>
+        <v>1073720.7919098944</v>
       </c>
       <c r="BW27" s="1">
-        <v>1073720.7919098942</v>
+        <v>1073720.7919098944</v>
       </c>
     </row>
     <row r="28" spans="1:75" x14ac:dyDescent="0.3">
@@ -6817,13 +6841,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="5">
-        <v>6485.07988904586</v>
+        <v>7271.6749491203991</v>
       </c>
       <c r="N28" s="5">
-        <v>455.35086564717085</v>
+        <v>520.79264839054781</v>
       </c>
       <c r="O28" s="5">
-        <v>60475.498892607684</v>
+        <v>64960.108974852796</v>
       </c>
       <c r="P28" s="5">
         <v>0</v>
@@ -6835,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="5">
-        <v>10977.779428824164</v>
+        <v>14379.506454282411</v>
       </c>
       <c r="T28" s="5">
         <v>0</v>
@@ -6970,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="BL28" s="6">
-        <v>78393.709076124884</v>
+        <v>87132.083026646156</v>
       </c>
       <c r="BM28" s="5">
         <v>12816.846474205297</v>
@@ -6985,10 +7009,10 @@
         <v>557.78827419922845</v>
       </c>
       <c r="BQ28" s="5">
-        <v>259923.4544349511</v>
+        <v>251185.08048442984</v>
       </c>
       <c r="BR28" s="6">
-        <v>273298.08918335562</v>
+        <v>264559.71523283434</v>
       </c>
       <c r="BS28" s="5">
         <v>351691.79825948051</v>
@@ -7089,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="AB29" s="5">
-        <v>5920.9448539347641</v>
+        <v>5717.7199168189763</v>
       </c>
       <c r="AC29" s="5">
         <v>0</v>
@@ -7161,10 +7185,10 @@
         <v>0</v>
       </c>
       <c r="AZ29" s="5">
-        <v>8954.5398182198205</v>
+        <v>9033.5316249289808</v>
       </c>
       <c r="BA29" s="5">
-        <v>38125.205235288478</v>
+        <v>38249.43836569511</v>
       </c>
       <c r="BB29" s="5">
         <v>0</v>
@@ -7197,10 +7221,10 @@
         <v>0</v>
       </c>
       <c r="BL29" s="6">
-        <v>54972.831184038805</v>
+        <v>54972.831184038812</v>
       </c>
       <c r="BM29" s="5">
-        <v>169793.95462960316</v>
+        <v>169793.95462960313</v>
       </c>
       <c r="BN29" s="5">
         <v>0</v>
@@ -7215,10 +7239,10 @@
         <v>0</v>
       </c>
       <c r="BR29" s="6">
-        <v>169980.6928795097</v>
+        <v>169980.69287950968</v>
       </c>
       <c r="BS29" s="5">
-        <v>224953.52406354851</v>
+        <v>224953.52406354848</v>
       </c>
       <c r="BT29" s="5">
         <v>0</v>
@@ -7227,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="BV29" s="6">
-        <v>224953.52406354848</v>
+        <v>224953.52406354842</v>
       </c>
       <c r="BW29" s="1">
-        <v>224953.52406354848</v>
+        <v>224953.52406354842</v>
       </c>
     </row>
     <row r="30" spans="1:75" x14ac:dyDescent="0.3">
@@ -7286,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="5">
-        <v>20080.613920989377</v>
+        <v>22255.471318157775</v>
       </c>
       <c r="S30" s="5">
         <v>0</v>
@@ -7325,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="AE30" s="5">
-        <v>7205.4323990314087</v>
+        <v>11210.18823932693</v>
       </c>
       <c r="AF30" s="5">
         <v>0</v>
@@ -7349,10 +7373,10 @@
         <v>0</v>
       </c>
       <c r="AM30" s="5">
-        <v>198.37118327558827</v>
+        <v>395.64473657397934</v>
       </c>
       <c r="AN30" s="5">
-        <v>3523.7123421246292</v>
+        <v>4160.2800561953336</v>
       </c>
       <c r="AO30" s="5">
         <v>0</v>
@@ -7382,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="AX30" s="5">
-        <v>0</v>
+        <v>3249.1426574740544</v>
       </c>
       <c r="AY30" s="5">
         <v>0</v>
@@ -7424,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="BL30" s="6">
-        <v>31008.129845421001</v>
+        <v>41270.72700772807</v>
       </c>
       <c r="BM30" s="5">
-        <v>70649.255166766408</v>
+        <v>65697.204883122322</v>
       </c>
       <c r="BN30" s="5">
         <v>0</v>
@@ -7439,25 +7463,25 @@
         <v>236.13711831884609</v>
       </c>
       <c r="BQ30" s="5">
-        <v>53527.308462567591</v>
+        <v>48216.761583904598</v>
       </c>
       <c r="BR30" s="6">
-        <v>124412.70074765285</v>
+        <v>114150.10358534576</v>
       </c>
       <c r="BS30" s="5">
+        <v>155420.83059307383</v>
+      </c>
+      <c r="BT30" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU30" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV30" s="6">
         <v>155420.83059307386</v>
       </c>
-      <c r="BT30" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU30" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV30" s="6">
-        <v>155420.83059307383</v>
-      </c>
       <c r="BW30" s="1">
-        <v>155420.83059307383</v>
+        <v>155420.83059307386</v>
       </c>
     </row>
     <row r="31" spans="1:75" x14ac:dyDescent="0.3">
@@ -7558,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="AG31" s="5">
-        <v>4749.4896900627318</v>
+        <v>4748.073029453225</v>
       </c>
       <c r="AH31" s="5">
         <v>0</v>
@@ -7579,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="AN31" s="5">
-        <v>11790.775753362244</v>
+        <v>11953.828954404273</v>
       </c>
       <c r="AO31" s="5">
         <v>0</v>
@@ -7594,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="AS31" s="5">
-        <v>214130.1632681211</v>
+        <v>213968.52672768853</v>
       </c>
       <c r="AT31" s="5">
         <v>0</v>
@@ -7651,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="BL31" s="6">
-        <v>230670.42871154609</v>
+        <v>230670.42871154603</v>
       </c>
       <c r="BM31" s="5">
         <v>25380.711248484353</v>
@@ -7672,7 +7696,7 @@
         <v>25704.63014210678</v>
       </c>
       <c r="BS31" s="5">
-        <v>256375.05885365288</v>
+        <v>256375.05885365282</v>
       </c>
       <c r="BT31" s="5">
         <v>0</v>
@@ -7681,10 +7705,10 @@
         <v>0</v>
       </c>
       <c r="BV31" s="6">
-        <v>256375.05885365274</v>
+        <v>256375.05885365279</v>
       </c>
       <c r="BW31" s="1">
-        <v>256375.05885365274</v>
+        <v>256375.05885365279</v>
       </c>
     </row>
     <row r="32" spans="1:75" x14ac:dyDescent="0.3">
@@ -7758,25 +7782,25 @@
         <v>0</v>
       </c>
       <c r="X32" s="5">
-        <v>6181.2467905128551</v>
+        <v>6183.9091927239451</v>
       </c>
       <c r="Y32" s="5">
         <v>0</v>
       </c>
       <c r="Z32" s="5">
-        <v>2943.747268279435</v>
+        <v>2943.8203698354805</v>
       </c>
       <c r="AA32" s="5">
-        <v>3393.4697989360197</v>
+        <v>3396.5289335857328</v>
       </c>
       <c r="AB32" s="5">
-        <v>7269.8350667262921</v>
+        <v>7276.3517628017307</v>
       </c>
       <c r="AC32" s="5">
-        <v>1694.0563806376686</v>
+        <v>1692.3783539548422</v>
       </c>
       <c r="AD32" s="5">
-        <v>1871.8675066485255</v>
+        <v>1875.6747661896532</v>
       </c>
       <c r="AE32" s="5">
         <v>0</v>
@@ -7785,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="5">
-        <v>2743.6593940800453</v>
+        <v>2203.9688817939023</v>
       </c>
       <c r="AH32" s="5">
         <v>0</v>
@@ -7809,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="5">
-        <v>716.25465693983722</v>
+        <v>750.91205823616428</v>
       </c>
       <c r="AP32" s="5">
         <v>0</v>
@@ -7842,34 +7866,34 @@
         <v>0</v>
       </c>
       <c r="AZ32" s="5">
-        <v>1175.7886614163958</v>
+        <v>1174.6667570870798</v>
       </c>
       <c r="BA32" s="5">
-        <v>2881.5885585514752</v>
+        <v>2871.7837358459187</v>
       </c>
       <c r="BB32" s="5">
-        <v>2871.2998159431222</v>
+        <v>2675.3207807503359</v>
       </c>
       <c r="BC32" s="5">
-        <v>952.03432633621833</v>
+        <v>955.68923710138358</v>
       </c>
       <c r="BD32" s="5">
-        <v>146.29209403153979</v>
+        <v>136.00776518664802</v>
       </c>
       <c r="BE32" s="5">
         <v>0</v>
       </c>
       <c r="BF32" s="5">
-        <v>954.4875479081212</v>
+        <v>978.62695150476191</v>
       </c>
       <c r="BG32" s="5">
-        <v>27930.692448940612</v>
+        <v>28586.224133161715</v>
       </c>
       <c r="BH32" s="5">
-        <v>8722.2105793376923</v>
+        <v>9200.8522691128492</v>
       </c>
       <c r="BI32" s="5">
-        <v>4219.6109775330933</v>
+        <v>3765.4259238867935</v>
       </c>
       <c r="BJ32" s="5">
         <v>0</v>
@@ -7878,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="BL32" s="6">
-        <v>76668.141872758963</v>
+        <v>76668.141872758933</v>
       </c>
       <c r="BM32" s="5">
         <v>19297.57363028924</v>
@@ -7899,7 +7923,7 @@
         <v>19297.57363028924</v>
       </c>
       <c r="BS32" s="5">
-        <v>95965.71550304821</v>
+        <v>95965.715503048181</v>
       </c>
       <c r="BT32" s="5">
         <v>0</v>
@@ -7922,133 +7946,133 @@
         <v>34</v>
       </c>
       <c r="C33" s="5">
-        <v>451.67253606796265</v>
+        <v>517.32749106400513</v>
       </c>
       <c r="D33" s="5">
-        <v>48.02408705421324</v>
+        <v>49.090822803680055</v>
       </c>
       <c r="E33" s="5">
-        <v>30.064128186077941</v>
+        <v>30.398895642504151</v>
       </c>
       <c r="F33" s="5">
-        <v>396.9467874067459</v>
+        <v>362.94905893887972</v>
       </c>
       <c r="G33" s="5">
-        <v>618.96166539799663</v>
+        <v>633.9284267103526</v>
       </c>
       <c r="H33" s="5">
-        <v>76939.88709120985</v>
+        <v>79299.303772452637</v>
       </c>
       <c r="I33" s="5">
-        <v>10216.15640517905</v>
+        <v>10291.020063641907</v>
       </c>
       <c r="J33" s="5">
-        <v>4442.8060237528634</v>
+        <v>4527.7480152933231</v>
       </c>
       <c r="K33" s="5">
-        <v>277.89083799433234</v>
+        <v>280.9122346060837</v>
       </c>
       <c r="L33" s="5">
-        <v>6539.8455214470159</v>
+        <v>6829.7202715257945</v>
       </c>
       <c r="M33" s="5">
-        <v>206.69165214014765</v>
+        <v>206.67695379291899</v>
       </c>
       <c r="N33" s="5">
-        <v>8.7599933304247841</v>
+        <v>8.588425038245477</v>
       </c>
       <c r="O33" s="5">
-        <v>1715.3178608280869</v>
+        <v>1726.8101905652015</v>
       </c>
       <c r="P33" s="5">
-        <v>457.23498953782263</v>
+        <v>224.5695899923308</v>
       </c>
       <c r="Q33" s="5">
-        <v>69.17807675377361</v>
+        <v>44.080707892960348</v>
       </c>
       <c r="R33" s="5">
-        <v>1771.6704538795993</v>
+        <v>743.3902839653</v>
       </c>
       <c r="S33" s="5">
-        <v>736.49850606074017</v>
+        <v>756.01387623297671</v>
       </c>
       <c r="T33" s="5">
-        <v>2766.4466775132032</v>
+        <v>1336.3119808248432</v>
       </c>
       <c r="U33" s="5">
-        <v>944.14222947179178</v>
+        <v>718.90403061467055</v>
       </c>
       <c r="V33" s="5">
-        <v>231.30540144078589</v>
+        <v>152.82196470741258</v>
       </c>
       <c r="W33" s="5">
-        <v>136.93905257049752</v>
+        <v>69.973543978336906</v>
       </c>
       <c r="X33" s="5">
-        <v>782.47328532703546</v>
+        <v>764.49921228032861</v>
       </c>
       <c r="Y33" s="5">
-        <v>22027.358252747978</v>
+        <v>22112.815509057218</v>
       </c>
       <c r="Z33" s="5">
-        <v>311.17634293453403</v>
+        <v>305.43269597335006</v>
       </c>
       <c r="AA33" s="5">
-        <v>461.26534662249514</v>
+        <v>396.64958258741541</v>
       </c>
       <c r="AB33" s="5">
-        <v>969.75416643104563</v>
+        <v>794.49321917572172</v>
       </c>
       <c r="AC33" s="5">
-        <v>2716.614775108415</v>
+        <v>2868.2580637414858</v>
       </c>
       <c r="AD33" s="5">
-        <v>314.05949075549631</v>
+        <v>287.0977092182689</v>
       </c>
       <c r="AE33" s="5">
-        <v>2932.2132521307385</v>
+        <v>3001.7541780509955</v>
       </c>
       <c r="AF33" s="5">
-        <v>1852.0351044321565</v>
+        <v>2003.6604960171635</v>
       </c>
       <c r="AG33" s="5">
-        <v>1575.623707359646</v>
+        <v>1632.6270601565602</v>
       </c>
       <c r="AH33" s="5">
-        <v>10634.318229825274</v>
+        <v>11432.390147419765</v>
       </c>
       <c r="AI33" s="5">
-        <v>5257.6019888875799</v>
+        <v>5675.6108964765299</v>
       </c>
       <c r="AJ33" s="5">
-        <v>3394.7286929458642</v>
+        <v>1522.565933940019</v>
       </c>
       <c r="AK33" s="5">
-        <v>22523.153687484213</v>
+        <v>23243.620946620304</v>
       </c>
       <c r="AL33" s="5">
-        <v>3241.7335888575562</v>
+        <v>3499.4681361635598</v>
       </c>
       <c r="AM33" s="5">
-        <v>221.55633880387407</v>
+        <v>228.67682711385223</v>
       </c>
       <c r="AN33" s="5">
-        <v>707.68978551470286</v>
+        <v>761.65951747299505</v>
       </c>
       <c r="AO33" s="5">
-        <v>1316.6489239930156</v>
+        <v>1361.5133982960961</v>
       </c>
       <c r="AP33" s="5">
         <v>0</v>
       </c>
       <c r="AQ33" s="5">
-        <v>248.47151231424567</v>
+        <v>225.4485221987772</v>
       </c>
       <c r="AR33" s="5">
-        <v>400.45863764690603</v>
+        <v>412.4688716458445</v>
       </c>
       <c r="AS33" s="5">
-        <v>13998.676144066991</v>
+        <v>12218.559907751531</v>
       </c>
       <c r="AT33" s="5">
         <v>0</v>
@@ -8069,10 +8093,10 @@
         <v>0</v>
       </c>
       <c r="AZ33" s="5">
-        <v>385.20085492418929</v>
+        <v>362.00595340568424</v>
       </c>
       <c r="BA33" s="5">
-        <v>1002.4339755017691</v>
+        <v>891.78274940020128</v>
       </c>
       <c r="BB33" s="5">
         <v>0</v>
@@ -8096,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="5">
-        <v>48020.285299817384</v>
+        <v>49488.371227208037</v>
       </c>
       <c r="BJ33" s="5">
         <v>0</v>
@@ -8105,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="BL33" s="6">
-        <v>254301.97136165612</v>
+        <v>254301.97136165606</v>
       </c>
       <c r="BM33" s="5">
         <v>18384.162697203352</v>
@@ -8126,7 +8150,7 @@
         <v>19096.621027244608</v>
       </c>
       <c r="BS33" s="5">
-        <v>273398.59238890075</v>
+        <v>273398.5923889007</v>
       </c>
       <c r="BT33" s="5">
         <v>0</v>
@@ -8135,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="BV33" s="6">
-        <v>273398.59238890064</v>
+        <v>273398.5923889007</v>
       </c>
       <c r="BW33" s="1">
-        <v>273398.59238890064</v>
+        <v>273398.5923889007</v>
       </c>
     </row>
     <row r="34" spans="1:75" x14ac:dyDescent="0.3">
@@ -8194,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="R34" s="5">
-        <v>13042.63168056233</v>
+        <v>12316.345093296226</v>
       </c>
       <c r="S34" s="5">
-        <v>871.53078161972212</v>
+        <v>753.66133279240773</v>
       </c>
       <c r="T34" s="5">
         <v>0</v>
@@ -8212,40 +8236,40 @@
         <v>0</v>
       </c>
       <c r="X34" s="5">
-        <v>13499.062211304805</v>
+        <v>15613.708493160389</v>
       </c>
       <c r="Y34" s="5">
-        <v>3934.7323486195937</v>
+        <v>5212.7122960291299</v>
       </c>
       <c r="Z34" s="5">
-        <v>4578.9680465879346</v>
+        <v>4890.5458935229553</v>
       </c>
       <c r="AA34" s="5">
-        <v>7878.1742760700217</v>
+        <v>8252.5134205701397</v>
       </c>
       <c r="AB34" s="5">
-        <v>13612.830244076697</v>
+        <v>14112.693075135321</v>
       </c>
       <c r="AC34" s="5">
-        <v>1791.6340852004364</v>
+        <v>2420.3494100665921</v>
       </c>
       <c r="AD34" s="5">
-        <v>4699.1417169716597</v>
+        <v>5452.4065928865075</v>
       </c>
       <c r="AE34" s="5">
-        <v>4374.9862743909798</v>
+        <v>4159.3220441755593</v>
       </c>
       <c r="AF34" s="5">
-        <v>992.21564900678788</v>
+        <v>1076.8583200883518</v>
       </c>
       <c r="AG34" s="5">
-        <v>413.57935069468169</v>
+        <v>522.43619905235823</v>
       </c>
       <c r="AH34" s="5">
         <v>0</v>
       </c>
       <c r="AI34" s="5">
-        <v>2254.6542830436588</v>
+        <v>2548.4307688649078</v>
       </c>
       <c r="AJ34" s="5">
         <v>0</v>
@@ -8254,19 +8278,19 @@
         <v>0</v>
       </c>
       <c r="AL34" s="5">
-        <v>7838.4574485158691</v>
+        <v>8356.6389514490693</v>
       </c>
       <c r="AM34" s="5">
-        <v>1654.6695803786181</v>
+        <v>1774.6504822498325</v>
       </c>
       <c r="AN34" s="5">
-        <v>1026.4639548282812</v>
+        <v>1073.7855500295595</v>
       </c>
       <c r="AO34" s="5">
-        <v>2707.0413911310188</v>
+        <v>2774.0805435280436</v>
       </c>
       <c r="AP34" s="5">
-        <v>11057.663715001529</v>
+        <v>10273.974785157507</v>
       </c>
       <c r="AQ34" s="5">
         <v>0</v>
@@ -8275,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="AS34" s="5">
-        <v>0</v>
+        <v>2356.9631846812417</v>
       </c>
       <c r="AT34" s="5">
         <v>0</v>
@@ -8284,10 +8308,10 @@
         <v>0</v>
       </c>
       <c r="AV34" s="5">
-        <v>3817.4480042555278</v>
+        <v>3978.6370821162391</v>
       </c>
       <c r="AW34" s="5">
-        <v>3415.1595406455172</v>
+        <v>3939.4238358902071</v>
       </c>
       <c r="AX34" s="5">
         <v>0</v>
@@ -8296,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="5">
-        <v>1513.6422640524204</v>
+        <v>2027.6135212720808</v>
       </c>
       <c r="BA34" s="5">
-        <v>5519.653259370778</v>
+        <v>7386.0362311065473</v>
       </c>
       <c r="BB34" s="5">
         <v>0</v>
@@ -8323,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="5">
-        <v>5186.2728623656649</v>
+        <v>6009.0162437978006</v>
       </c>
       <c r="BJ34" s="5">
         <v>0</v>
@@ -8332,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="BL34" s="6">
-        <v>115680.61296869451</v>
+        <v>127282.803350919</v>
       </c>
       <c r="BM34" s="5">
-        <v>49212.401775932973</v>
+        <v>49212.40177593298</v>
       </c>
       <c r="BN34" s="5">
         <v>0</v>
@@ -8347,13 +8371,13 @@
         <v>254.61293399778313</v>
       </c>
       <c r="BQ34" s="5">
-        <v>32814.859044381978</v>
+        <v>21212.668662131175</v>
       </c>
       <c r="BR34" s="6">
-        <v>82281.873754312735</v>
+        <v>70679.683372061932</v>
       </c>
       <c r="BS34" s="5">
-        <v>197962.48672300723</v>
+        <v>197962.48672298092</v>
       </c>
       <c r="BT34" s="5">
         <v>0</v>
@@ -8362,10 +8386,10 @@
         <v>0</v>
       </c>
       <c r="BV34" s="6">
-        <v>197962.48672300734</v>
+        <v>197962.48672300729</v>
       </c>
       <c r="BW34" s="1">
-        <v>197962.48672300734</v>
+        <v>197962.48672300729</v>
       </c>
     </row>
     <row r="35" spans="1:75" x14ac:dyDescent="0.3">
@@ -8463,37 +8487,37 @@
         <v>0</v>
       </c>
       <c r="AF35" s="5">
-        <v>0</v>
+        <v>36.062785829984101</v>
       </c>
       <c r="AG35" s="5">
         <v>0</v>
       </c>
       <c r="AH35" s="5">
-        <v>0</v>
+        <v>19.509265001793921</v>
       </c>
       <c r="AI35" s="5">
         <v>0</v>
       </c>
       <c r="AJ35" s="5">
-        <v>0</v>
+        <v>9760.6353548703555</v>
       </c>
       <c r="AK35" s="5">
         <v>0</v>
       </c>
       <c r="AL35" s="5">
-        <v>0</v>
+        <v>319.49050732812719</v>
       </c>
       <c r="AM35" s="5">
-        <v>0</v>
+        <v>48.784978238914043</v>
       </c>
       <c r="AN35" s="5">
         <v>0</v>
       </c>
       <c r="AO35" s="5">
-        <v>0</v>
+        <v>22.693614931236901</v>
       </c>
       <c r="AP35" s="5">
-        <v>0</v>
+        <v>159.45489864140532</v>
       </c>
       <c r="AQ35" s="5">
         <v>0</v>
@@ -8502,7 +8526,7 @@
         <v>0</v>
       </c>
       <c r="AS35" s="5">
-        <v>1084238.8393490263</v>
+        <v>1131894.3653280339</v>
       </c>
       <c r="AT35" s="5">
         <v>0</v>
@@ -8511,16 +8535,16 @@
         <v>0</v>
       </c>
       <c r="AV35" s="5">
-        <v>0</v>
+        <v>619.55853884830492</v>
       </c>
       <c r="AW35" s="5">
-        <v>0</v>
+        <v>381.85072434944345</v>
       </c>
       <c r="AX35" s="5">
-        <v>0</v>
+        <v>1414.8388802154959</v>
       </c>
       <c r="AY35" s="5">
-        <v>0</v>
+        <v>297.57564625585422</v>
       </c>
       <c r="AZ35" s="5">
         <v>0</v>
@@ -8538,19 +8562,19 @@
         <v>0</v>
       </c>
       <c r="BE35" s="5">
-        <v>0</v>
+        <v>321.42694007907903</v>
       </c>
       <c r="BF35" s="5">
-        <v>0</v>
+        <v>32.802717284118017</v>
       </c>
       <c r="BG35" s="5">
-        <v>0</v>
+        <v>668.03862783973113</v>
       </c>
       <c r="BH35" s="5">
-        <v>0</v>
+        <v>123.20312504686854</v>
       </c>
       <c r="BI35" s="5">
-        <v>0</v>
+        <v>240.73210085746496</v>
       </c>
       <c r="BJ35" s="5">
         <v>0</v>
@@ -8559,10 +8583,10 @@
         <v>0</v>
       </c>
       <c r="BL35" s="6">
-        <v>1084238.8393490263</v>
+        <v>1146361.0240336519</v>
       </c>
       <c r="BM35" s="5">
-        <v>22050.794318517248</v>
+        <v>20861.183792201442</v>
       </c>
       <c r="BN35" s="5">
         <v>0</v>
@@ -8571,28 +8595,28 @@
         <v>0</v>
       </c>
       <c r="BP35" s="5">
-        <v>7892.2797940697965</v>
+        <v>7892.2797940697974</v>
       </c>
       <c r="BQ35" s="5">
-        <v>469728.10005519405</v>
+        <v>408795.52589688386</v>
       </c>
       <c r="BR35" s="6">
-        <v>499671.17416778108</v>
+        <v>437548.98948315508</v>
       </c>
       <c r="BS35" s="5">
+        <v>1583910.013516807</v>
+      </c>
+      <c r="BT35" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU35" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV35" s="6">
         <v>1583910.0135168075</v>
       </c>
-      <c r="BT35" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU35" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV35" s="6">
-        <v>1583910.0135168072</v>
-      </c>
       <c r="BW35" s="1">
-        <v>1583910.0135168072</v>
+        <v>1583910.0135168075</v>
       </c>
     </row>
     <row r="36" spans="1:75" x14ac:dyDescent="0.3">
@@ -8654,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="5">
-        <v>0</v>
+        <v>825.44973140503294</v>
       </c>
       <c r="U36" s="5">
         <v>0</v>
@@ -8705,22 +8729,22 @@
         <v>0</v>
       </c>
       <c r="AK36" s="5">
-        <v>0</v>
+        <v>2864.149332510729</v>
       </c>
       <c r="AL36" s="5">
-        <v>83994.117898889133</v>
+        <v>88488.585246725561</v>
       </c>
       <c r="AM36" s="5">
-        <v>5678.2810565744121</v>
+        <v>6067.8856347253368</v>
       </c>
       <c r="AN36" s="5">
-        <v>0</v>
+        <v>175.03852887529754</v>
       </c>
       <c r="AO36" s="5">
-        <v>4802.7684691846234</v>
+        <v>4733.290822507769</v>
       </c>
       <c r="AP36" s="5">
-        <v>14903.710239949854</v>
+        <v>15907.137826952832</v>
       </c>
       <c r="AQ36" s="5">
         <v>0</v>
@@ -8729,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="AS36" s="5">
-        <v>466975.28788117901</v>
+        <v>488781.69958719995</v>
       </c>
       <c r="AT36" s="5">
         <v>0</v>
@@ -8786,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="BL36" s="6">
-        <v>576354.16554577707</v>
+        <v>607843.23671090254</v>
       </c>
       <c r="BM36" s="5">
         <v>1.4017296183056812E-19</v>
@@ -8801,10 +8825,10 @@
         <v>12969.638436597954</v>
       </c>
       <c r="BQ36" s="5">
-        <v>1987118.4940444508</v>
+        <v>1955629.4228793252</v>
       </c>
       <c r="BR36" s="6">
-        <v>2000088.1324810488</v>
+        <v>1968599.0613159232</v>
       </c>
       <c r="BS36" s="5">
         <v>2576442.2980268258</v>
@@ -8869,28 +8893,28 @@
         <v>0</v>
       </c>
       <c r="P37" s="5">
-        <v>1233.5487325487527</v>
+        <v>1242.3074191723058</v>
       </c>
       <c r="Q37" s="5">
-        <v>326.44746778400167</v>
+        <v>329.40100118816423</v>
       </c>
       <c r="R37" s="5">
-        <v>2708.1462415375859</v>
+        <v>2641.9477041443047</v>
       </c>
       <c r="S37" s="5">
         <v>0</v>
       </c>
       <c r="T37" s="5">
-        <v>28769.042676840869</v>
+        <v>29174.243811010372</v>
       </c>
       <c r="U37" s="5">
-        <v>5087.888349577147</v>
+        <v>5142.5590231192837</v>
       </c>
       <c r="V37" s="5">
-        <v>2069.1694904061669</v>
+        <v>2098.4786957802207</v>
       </c>
       <c r="W37" s="5">
-        <v>2141.2630053132539</v>
+        <v>2172.4203945651216</v>
       </c>
       <c r="X37" s="5">
         <v>0</v>
@@ -8914,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="AE37" s="5">
-        <v>680.99867055875552</v>
+        <v>667.47953160374971</v>
       </c>
       <c r="AF37" s="5">
         <v>0</v>
@@ -8926,37 +8950,37 @@
         <v>0</v>
       </c>
       <c r="AI37" s="5">
-        <v>415.87769452817702</v>
+        <v>402.60006937696244</v>
       </c>
       <c r="AJ37" s="5">
-        <v>7496.0269244712154</v>
+        <v>7513.9866220595322</v>
       </c>
       <c r="AK37" s="5">
-        <v>6692.4257443624483</v>
+        <v>6425.3242025202881</v>
       </c>
       <c r="AL37" s="5">
-        <v>4940.991680543636</v>
+        <v>4154.7845366158226</v>
       </c>
       <c r="AM37" s="5">
-        <v>1759.9254698360216</v>
+        <v>1767.7126748677797</v>
       </c>
       <c r="AN37" s="5">
         <v>0</v>
       </c>
       <c r="AO37" s="5">
-        <v>721.58321730817795</v>
+        <v>725.2514391931727</v>
       </c>
       <c r="AP37" s="5">
-        <v>15542.689107932327</v>
+        <v>15796.190261186355</v>
       </c>
       <c r="AQ37" s="5">
-        <v>3031.1422518242657</v>
+        <v>3031.0940347416872</v>
       </c>
       <c r="AR37" s="5">
-        <v>104.06915041596871</v>
+        <v>104.55619950926337</v>
       </c>
       <c r="AS37" s="5">
-        <v>129709.70539999379</v>
+        <v>130041.37160323074</v>
       </c>
       <c r="AT37" s="5">
         <v>0</v>
@@ -8983,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="BB37" s="5">
-        <v>13628.189549876815</v>
+        <v>13627.421601774251</v>
       </c>
       <c r="BC37" s="5">
         <v>0</v>
@@ -9013,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="BL37" s="6">
-        <v>227059.13082565938</v>
+        <v>227059.13082565935</v>
       </c>
       <c r="BM37" s="5">
         <v>18630.875554531875</v>
@@ -9034,7 +9058,7 @@
         <v>178346.00831583884</v>
       </c>
       <c r="BS37" s="5">
-        <v>405405.13914149825</v>
+        <v>405405.13914149819</v>
       </c>
       <c r="BT37" s="5">
         <v>0</v>
@@ -9043,10 +9067,10 @@
         <v>0</v>
       </c>
       <c r="BV37" s="6">
-        <v>405405.13914149825</v>
+        <v>405405.13914149819</v>
       </c>
       <c r="BW37" s="1">
-        <v>405405.13914149825</v>
+        <v>405405.13914149819</v>
       </c>
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.3">
@@ -9117,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="5">
-        <v>70.377408065766502</v>
+        <v>57.442392721937772</v>
       </c>
       <c r="X38" s="5">
         <v>0</v>
@@ -9165,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="AM38" s="5">
-        <v>358.86743047581206</v>
+        <v>296.03465900200439</v>
       </c>
       <c r="AN38" s="5">
         <v>0</v>
@@ -9174,13 +9198,13 @@
         <v>0</v>
       </c>
       <c r="AP38" s="5">
-        <v>2702.9343721471569</v>
+        <v>2762.9808216058877</v>
       </c>
       <c r="AQ38" s="5">
         <v>0</v>
       </c>
       <c r="AR38" s="5">
-        <v>10.42687352658599</v>
+        <v>10.281264971832028</v>
       </c>
       <c r="AS38" s="5">
         <v>0</v>
@@ -9192,13 +9216,13 @@
         <v>0</v>
       </c>
       <c r="AV38" s="5">
-        <v>2981.7647152827767</v>
+        <v>2997.4997668976766</v>
       </c>
       <c r="AW38" s="5">
-        <v>3310.9671150181271</v>
+        <v>3331.2183677626381</v>
       </c>
       <c r="AX38" s="5">
-        <v>4329.6713221210803</v>
+        <v>4318.4506081374884</v>
       </c>
       <c r="AY38" s="5">
         <v>0</v>
@@ -9222,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="BF38" s="5">
-        <v>122.71481483700335</v>
+        <v>113.81617037484384</v>
       </c>
       <c r="BG38" s="5">
         <v>0</v>
@@ -9416,7 +9440,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="5">
-        <v>6362.8594688149478</v>
+        <v>6362.7946738805558</v>
       </c>
       <c r="AV39" s="5">
         <v>0</v>
@@ -9431,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="AZ39" s="5">
-        <v>360.71444957134582</v>
+        <v>357.59148222782278</v>
       </c>
       <c r="BA39" s="5">
         <v>0</v>
@@ -9449,16 +9473,16 @@
         <v>0</v>
       </c>
       <c r="BF39" s="5">
-        <v>1328.4867490096601</v>
+        <v>1277.5093172888844</v>
       </c>
       <c r="BG39" s="5">
-        <v>12583.999906803921</v>
+        <v>12583.99990680392</v>
       </c>
       <c r="BH39" s="5">
-        <v>4995.444286714468</v>
+        <v>5230.3240755838015</v>
       </c>
       <c r="BI39" s="5">
-        <v>5115.9250195345867</v>
+        <v>4935.2104246639437</v>
       </c>
       <c r="BJ39" s="5">
         <v>0</v>
@@ -9467,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="BL39" s="6">
-        <v>30747.42988044893</v>
+        <v>30747.429880448926</v>
       </c>
       <c r="BM39" s="5">
         <v>24533.091926131223</v>
@@ -9488,7 +9512,7 @@
         <v>55270.842570469395</v>
       </c>
       <c r="BS39" s="5">
-        <v>86018.272450918332</v>
+        <v>86018.272450918317</v>
       </c>
       <c r="BT39" s="5">
         <v>0</v>
@@ -9511,151 +9535,151 @@
         <v>41</v>
       </c>
       <c r="C40" s="5">
-        <v>42.47398265542332</v>
+        <v>42.097314820253928</v>
       </c>
       <c r="D40" s="5">
-        <v>5.0247087987317451</v>
+        <v>4.9784103295525384</v>
       </c>
       <c r="E40" s="5">
-        <v>3.3934118014637487</v>
+        <v>3.3621869854149873</v>
       </c>
       <c r="F40" s="5">
-        <v>45.394927398984713</v>
+        <v>44.961588851985766</v>
       </c>
       <c r="G40" s="5">
-        <v>65.812188695158341</v>
+        <v>65.219713403594497</v>
       </c>
       <c r="H40" s="5">
-        <v>8253.5228468005444</v>
+        <v>8179.0386311838156</v>
       </c>
       <c r="I40" s="5">
-        <v>1195.3608406716642</v>
+        <v>1185.9778239551324</v>
       </c>
       <c r="J40" s="5">
-        <v>497.56501102013078</v>
+        <v>493.2202800516655</v>
       </c>
       <c r="K40" s="5">
-        <v>32.555515689374175</v>
+        <v>32.251421604213242</v>
       </c>
       <c r="L40" s="5">
-        <v>696.62286897210276</v>
+        <v>691.58417881477828</v>
       </c>
       <c r="M40" s="5">
-        <v>29.223216891502332</v>
+        <v>28.966629216693775</v>
       </c>
       <c r="N40" s="5">
-        <v>1.6750739168513324</v>
+        <v>1.6588737465950998</v>
       </c>
       <c r="O40" s="5">
-        <v>191.43106482560555</v>
+        <v>189.76591133509163</v>
       </c>
       <c r="P40" s="5">
-        <v>568.84299479545734</v>
+        <v>565.37632270122708</v>
       </c>
       <c r="Q40" s="5">
-        <v>293.48646978317947</v>
+        <v>290.87188939043597</v>
       </c>
       <c r="R40" s="5">
-        <v>5837.7844896308234</v>
+        <v>5803.3551762729403</v>
       </c>
       <c r="S40" s="5">
-        <v>112.60010713070655</v>
+        <v>111.86951190246162</v>
       </c>
       <c r="T40" s="5">
-        <v>11361.041450832254</v>
+        <v>11776.615707413439</v>
       </c>
       <c r="U40" s="5">
-        <v>1610.3374706446846</v>
+        <v>1596.6524475438146</v>
       </c>
       <c r="V40" s="5">
-        <v>784.72868807895054</v>
+        <v>804.08497906820594</v>
       </c>
       <c r="W40" s="5">
-        <v>797.91008766606024</v>
+        <v>801.06336395490825</v>
       </c>
       <c r="X40" s="5">
-        <v>532.34010103651576</v>
+        <v>526.4195376165037</v>
       </c>
       <c r="Y40" s="5">
-        <v>394.02061931630328</v>
+        <v>380.71990394215464</v>
       </c>
       <c r="Z40" s="5">
-        <v>213.07788487090758</v>
+        <v>210.89772506283506</v>
       </c>
       <c r="AA40" s="5">
-        <v>229.58953848831277</v>
+        <v>209.85388580246931</v>
       </c>
       <c r="AB40" s="5">
-        <v>402.82673408254846</v>
+        <v>393.16753843099184</v>
       </c>
       <c r="AC40" s="5">
-        <v>134.65684807497865</v>
+        <v>132.3389207257606</v>
       </c>
       <c r="AD40" s="5">
-        <v>110.99161995741946</v>
+        <v>108.967285159122</v>
       </c>
       <c r="AE40" s="5">
-        <v>353.2551950801286</v>
+        <v>355.24835177262116</v>
       </c>
       <c r="AF40" s="5">
-        <v>344.37475047891769</v>
+        <v>373.05885947821969</v>
       </c>
       <c r="AG40" s="5">
-        <v>100.82805676493734</v>
+        <v>80.438305718964926</v>
       </c>
       <c r="AH40" s="5">
-        <v>2410.7411412566917</v>
+        <v>2877.0890291225214</v>
       </c>
       <c r="AI40" s="5">
-        <v>574.40099869350229</v>
+        <v>575.9967831919862</v>
       </c>
       <c r="AJ40" s="5">
-        <v>5007.015361993771</v>
+        <v>5262.0505862892924</v>
       </c>
       <c r="AK40" s="5">
-        <v>9403.9186625088423</v>
+        <v>9429.9552998391136</v>
       </c>
       <c r="AL40" s="5">
-        <v>1080.0907355074664</v>
+        <v>1555.6654153597615</v>
       </c>
       <c r="AM40" s="5">
-        <v>55.895688963795045</v>
+        <v>42.558580975760066</v>
       </c>
       <c r="AN40" s="5">
-        <v>27.553549244499063</v>
+        <v>22.504613974508963</v>
       </c>
       <c r="AO40" s="5">
-        <v>786.30854686326836</v>
+        <v>604.04506871689534</v>
       </c>
       <c r="AP40" s="5">
-        <v>2033.3971739698882</v>
+        <v>976.78485121344727</v>
       </c>
       <c r="AQ40" s="5">
-        <v>2011.8573284711233</v>
+        <v>1995.7007122788593</v>
       </c>
       <c r="AR40" s="5">
-        <v>6.9198486133723307</v>
+        <v>6.2808756209235819</v>
       </c>
       <c r="AS40" s="5">
-        <v>3683.0628344379711</v>
+        <v>3358.1705965358624</v>
       </c>
       <c r="AT40" s="5">
-        <v>580.5558272259907</v>
+        <v>523.5956045593922</v>
       </c>
       <c r="AU40" s="5">
         <v>0</v>
       </c>
       <c r="AV40" s="5">
-        <v>6594.7845607086447</v>
+        <v>6751.6383055349434</v>
       </c>
       <c r="AW40" s="5">
-        <v>6482.1136215935576</v>
+        <v>6617.5591247163748</v>
       </c>
       <c r="AX40" s="5">
-        <v>8680.7188356763472</v>
+        <v>8485.5061574352439</v>
       </c>
       <c r="AY40" s="5">
-        <v>1365.2507003038747</v>
+        <v>1458.1498992624765</v>
       </c>
       <c r="AZ40" s="5">
         <v>0</v>
@@ -9694,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="BL40" s="6">
-        <v>86027.334180883234</v>
+        <v>86027.334180883219</v>
       </c>
       <c r="BM40" s="5">
         <v>2448.4953298777314</v>
@@ -9715,7 +9739,7 @@
         <v>2448.4953298779601</v>
       </c>
       <c r="BS40" s="5">
-        <v>88475.829510761192</v>
+        <v>88475.829510761178</v>
       </c>
       <c r="BT40" s="5">
         <v>0</v>
@@ -9738,190 +9762,190 @@
         <v>42</v>
       </c>
       <c r="C41" s="5">
-        <v>79.599665921159101</v>
+        <v>84.467162929267687</v>
       </c>
       <c r="D41" s="5">
-        <v>14.475120757150044</v>
+        <v>14.339281040852548</v>
       </c>
       <c r="E41" s="5">
-        <v>9.6373571935355056</v>
+        <v>9.5647552386341683</v>
       </c>
       <c r="F41" s="5">
-        <v>181.63999870909856</v>
+        <v>172.22057553082294</v>
       </c>
       <c r="G41" s="5">
-        <v>205.91426488894808</v>
+        <v>198.66180684212571</v>
       </c>
       <c r="H41" s="5">
-        <v>19200.552068293026</v>
+        <v>19618.554569797612</v>
       </c>
       <c r="I41" s="5">
-        <v>3452.3742022262982</v>
+        <v>3417.3873430762465</v>
       </c>
       <c r="J41" s="5">
-        <v>1290.7449214396192</v>
+        <v>1298.1061136168121</v>
       </c>
       <c r="K41" s="5">
-        <v>105.65595821813429</v>
+        <v>103.10722725469114</v>
       </c>
       <c r="L41" s="5">
-        <v>1767.0458945762978</v>
+        <v>1782.9066984945798</v>
       </c>
       <c r="M41" s="5">
-        <v>149.76759116188595</v>
+        <v>146.82712311075863</v>
       </c>
       <c r="N41" s="5">
-        <v>8.8985601634577574</v>
+        <v>8.5200219036939764</v>
       </c>
       <c r="O41" s="5">
-        <v>1195.2921967239201</v>
+        <v>1201.3096224151445</v>
       </c>
       <c r="P41" s="5">
-        <v>2992.1572971521664</v>
+        <v>3140.9034075530885</v>
       </c>
       <c r="Q41" s="5">
-        <v>1502.2598988085822</v>
+        <v>1581.1447380597297</v>
       </c>
       <c r="R41" s="5">
-        <v>21217.093064202545</v>
+        <v>21561.070071748742</v>
       </c>
       <c r="S41" s="5">
-        <v>461.68540088823863</v>
+        <v>481.58624228596983</v>
       </c>
       <c r="T41" s="5">
-        <v>54249.743427756992</v>
+        <v>57966.969422154594</v>
       </c>
       <c r="U41" s="5">
-        <v>7531.4717052123378</v>
+        <v>7743.782098437111</v>
       </c>
       <c r="V41" s="5">
-        <v>3746.6683881540962</v>
+        <v>3957.1412080412842</v>
       </c>
       <c r="W41" s="5">
-        <v>4631.7113881901678</v>
+        <v>4934.0734341159778</v>
       </c>
       <c r="X41" s="5">
-        <v>4434.0494623140439</v>
+        <v>4397.5309911767035</v>
       </c>
       <c r="Y41" s="5">
-        <v>17308.49823657759</v>
+        <v>18232.932826632856</v>
       </c>
       <c r="Z41" s="5">
-        <v>2699.2189681202785</v>
+        <v>2706.1271486926362</v>
       </c>
       <c r="AA41" s="5">
-        <v>3492.4427060514508</v>
+        <v>3528.5410064184325</v>
       </c>
       <c r="AB41" s="5">
-        <v>6365.3762375467413</v>
+        <v>6490.6288676335134</v>
       </c>
       <c r="AC41" s="5">
-        <v>2141.2385914742317</v>
+        <v>2182.4398243229352</v>
       </c>
       <c r="AD41" s="5">
-        <v>1249.8073744137441</v>
+        <v>1243.0981276974126</v>
       </c>
       <c r="AE41" s="5">
-        <v>1340.7208071999376</v>
+        <v>1368.0668064226131</v>
       </c>
       <c r="AF41" s="5">
-        <v>1529.1705329748145</v>
+        <v>1534.7327013845859</v>
       </c>
       <c r="AG41" s="5">
-        <v>688.46359247034275</v>
+        <v>698.11267716939017</v>
       </c>
       <c r="AH41" s="5">
-        <v>2916.1255339941367</v>
+        <v>3110.6917015918716</v>
       </c>
       <c r="AI41" s="5">
-        <v>1108.2474449346551</v>
+        <v>1108.7265311078816</v>
       </c>
       <c r="AJ41" s="5">
-        <v>10053.954402438552</v>
+        <v>10153.160975318802</v>
       </c>
       <c r="AK41" s="5">
-        <v>18922.787659611251</v>
+        <v>19059.853174922893</v>
       </c>
       <c r="AL41" s="5">
-        <v>2860.3685056552995</v>
+        <v>2916.3911374348186</v>
       </c>
       <c r="AM41" s="5">
-        <v>365.25195104871398</v>
+        <v>365.0445896067672</v>
       </c>
       <c r="AN41" s="5">
-        <v>455.41235281001843</v>
+        <v>467.50008324009394</v>
       </c>
       <c r="AO41" s="5">
-        <v>608.26915459908309</v>
+        <v>636.49123984783034</v>
       </c>
       <c r="AP41" s="5">
-        <v>4759.5088021231868</v>
+        <v>4219.0225003399228</v>
       </c>
       <c r="AQ41" s="5">
-        <v>4476.8378297448226</v>
+        <v>4464.7698039861552</v>
       </c>
       <c r="AR41" s="5">
-        <v>374.30934965521612</v>
+        <v>396.02205672040759</v>
       </c>
       <c r="AS41" s="5">
-        <v>27641.661257567306</v>
+        <v>27838.372813874172</v>
       </c>
       <c r="AT41" s="5">
-        <v>12890.272421582193</v>
+        <v>13570.966363113826</v>
       </c>
       <c r="AU41" s="5">
-        <v>12664.780329007555</v>
+        <v>13170.000159727539</v>
       </c>
       <c r="AV41" s="5">
-        <v>21861.659246235842</v>
+        <v>22025.371643802238</v>
       </c>
       <c r="AW41" s="5">
-        <v>27669.606859263818</v>
+        <v>23761.911288501764</v>
       </c>
       <c r="AX41" s="5">
-        <v>32618.857870235359</v>
+        <v>28688.081559403861</v>
       </c>
       <c r="AY41" s="5">
-        <v>8203.638486992566</v>
+        <v>7908.1054343230899</v>
       </c>
       <c r="AZ41" s="5">
-        <v>418.53667247835676</v>
+        <v>450.09780973730557</v>
       </c>
       <c r="BA41" s="5">
-        <v>2455.4658401272372</v>
+        <v>2653.8885914543616</v>
       </c>
       <c r="BB41" s="5">
-        <v>15562.822508320209</v>
+        <v>16228.781147945416</v>
       </c>
       <c r="BC41" s="5">
         <v>855.14198929846941</v>
       </c>
       <c r="BD41" s="5">
-        <v>129.2992490084925</v>
+        <v>138.95164855611304</v>
       </c>
       <c r="BE41" s="5">
-        <v>20218.123731833562</v>
+        <v>21666.573387251767</v>
       </c>
       <c r="BF41" s="5">
-        <v>1789.989835065224</v>
+        <v>1886.2052855927022</v>
       </c>
       <c r="BG41" s="5">
         <v>21855.11773521018</v>
       </c>
       <c r="BH41" s="5">
-        <v>5796.5094689809903</v>
+        <v>5830.1238955298659</v>
       </c>
       <c r="BI41" s="5">
-        <v>13603.789500173301</v>
+        <v>11424.059851417282</v>
       </c>
       <c r="BJ41" s="5">
-        <v>4238.3154274182652</v>
+        <v>3963.757995140214</v>
       </c>
       <c r="BK41" s="5">
         <v>0</v>
       </c>
       <c r="BL41" s="6">
-        <v>442618.03629519459</v>
+        <v>442618.03629519639</v>
       </c>
       <c r="BM41" s="5">
         <v>25269.690767699161</v>
@@ -9942,7 +9966,7 @@
         <v>45272.40273825825</v>
       </c>
       <c r="BS41" s="5">
-        <v>487890.43903345283</v>
+        <v>487890.43903345463</v>
       </c>
       <c r="BT41" s="5">
         <v>0</v>
@@ -9965,190 +9989,190 @@
         <v>43</v>
       </c>
       <c r="C42" s="5">
-        <v>7.3406675531749332</v>
+        <v>7.4697169680571331</v>
       </c>
       <c r="D42" s="5">
-        <v>2.7356756566625693</v>
+        <v>2.6297913823193459</v>
       </c>
       <c r="E42" s="5">
-        <v>1.7929165449428806</v>
+        <v>1.7225323760474511</v>
       </c>
       <c r="F42" s="5">
-        <v>45.924946444752258</v>
+        <v>45.060238846568744</v>
       </c>
       <c r="G42" s="5">
-        <v>40.350027999954413</v>
+        <v>39.165440494158204</v>
       </c>
       <c r="H42" s="5">
-        <v>2795.435326442027</v>
+        <v>2726.0213955227964</v>
       </c>
       <c r="I42" s="5">
-        <v>648.43200385585794</v>
+        <v>621.14122682504421</v>
       </c>
       <c r="J42" s="5">
-        <v>213.76010319614295</v>
+        <v>206.29365885903229</v>
       </c>
       <c r="K42" s="5">
-        <v>24.704546282671675</v>
+        <v>24.324564821243257</v>
       </c>
       <c r="L42" s="5">
-        <v>287.70908169236623</v>
+        <v>278.61638427397446</v>
       </c>
       <c r="M42" s="5">
-        <v>80.157313281111172</v>
+        <v>76.419324428170455</v>
       </c>
       <c r="N42" s="5">
-        <v>5.7117226372774965</v>
+        <v>5.439398860023128</v>
       </c>
       <c r="O42" s="5">
-        <v>697.66762470391484</v>
+        <v>664.99383117509717</v>
       </c>
       <c r="P42" s="5">
-        <v>133.63016424501114</v>
+        <v>131.79608225832607</v>
       </c>
       <c r="Q42" s="5">
-        <v>64.287691922646928</v>
+        <v>64.408073578223338</v>
       </c>
       <c r="R42" s="5">
-        <v>3669.2349278909405</v>
+        <v>3633.1952684662974</v>
       </c>
       <c r="S42" s="5">
-        <v>128.58692457740696</v>
+        <v>130.31629154233212</v>
       </c>
       <c r="T42" s="5">
-        <v>4551.0734450303289</v>
+        <v>4585.8443113661051</v>
       </c>
       <c r="U42" s="5">
-        <v>1676.3599816427993</v>
+        <v>1662.3829769393569</v>
       </c>
       <c r="V42" s="5">
-        <v>427.62838259927071</v>
+        <v>426.33723856448785</v>
       </c>
       <c r="W42" s="5">
-        <v>261.93768877695368</v>
+        <v>202.99364235100717</v>
       </c>
       <c r="X42" s="5">
-        <v>4241.2608790216191</v>
+        <v>4103.2011343045706</v>
       </c>
       <c r="Y42" s="5">
-        <v>6084.977023983105</v>
+        <v>6286.2842803477106</v>
       </c>
       <c r="Z42" s="5">
-        <v>1611.2071296963409</v>
+        <v>1562.5149657621639</v>
       </c>
       <c r="AA42" s="5">
-        <v>2081.772404502794</v>
+        <v>2052.6410413765834</v>
       </c>
       <c r="AB42" s="5">
-        <v>3774.7504637579209</v>
+        <v>3699.0490456187949</v>
       </c>
       <c r="AC42" s="5">
-        <v>1180.6058283469747</v>
+        <v>1145.8452773508113</v>
       </c>
       <c r="AD42" s="5">
-        <v>998.52596388354436</v>
+        <v>960.26796909820644</v>
       </c>
       <c r="AE42" s="5">
-        <v>712.3108417677339</v>
+        <v>703.60230430767001</v>
       </c>
       <c r="AF42" s="5">
-        <v>830.33213298832004</v>
+        <v>827.45816063366851</v>
       </c>
       <c r="AG42" s="5">
-        <v>525.48255774640847</v>
+        <v>520.54360889039685</v>
       </c>
       <c r="AH42" s="5">
-        <v>1069.4656399165365</v>
+        <v>1093.4547358798852</v>
       </c>
       <c r="AI42" s="5">
-        <v>899.77097753420674</v>
+        <v>875.51926607175869</v>
       </c>
       <c r="AJ42" s="5">
-        <v>8800.5732170289248</v>
+        <v>8224.298011231931</v>
       </c>
       <c r="AK42" s="5">
-        <v>20300.585232776077</v>
+        <v>19067.151618807773</v>
       </c>
       <c r="AL42" s="5">
-        <v>1748.5122022521616</v>
+        <v>1754.9899446261597</v>
       </c>
       <c r="AM42" s="5">
-        <v>195.25137615531978</v>
+        <v>192.71129560021407</v>
       </c>
       <c r="AN42" s="5">
-        <v>213.04303882670573</v>
+        <v>212.01306486901385</v>
       </c>
       <c r="AO42" s="5">
-        <v>284.49551849955236</v>
+        <v>282.49475111799802</v>
       </c>
       <c r="AP42" s="5">
-        <v>865.18909392466583</v>
+        <v>842.28346117004776</v>
       </c>
       <c r="AQ42" s="5">
         <v>34.237024993036059</v>
       </c>
       <c r="AR42" s="5">
-        <v>147.21374140805625</v>
+        <v>153.17631063503575</v>
       </c>
       <c r="AS42" s="5">
-        <v>8920.3176402735371</v>
+        <v>8874.0958348400163</v>
       </c>
       <c r="AT42" s="5">
-        <v>4426.6849784301157</v>
+        <v>4541.5917668128604</v>
       </c>
       <c r="AU42" s="5">
-        <v>5984.6869608275956</v>
+        <v>6076.3434502020182</v>
       </c>
       <c r="AV42" s="5">
-        <v>1481.1094792541799</v>
+        <v>1466.4955477446345</v>
       </c>
       <c r="AW42" s="5">
-        <v>1413.4006989998361</v>
+        <v>1402.8348723018867</v>
       </c>
       <c r="AX42" s="5">
-        <v>4120.6608056667001</v>
+        <v>4465.410313198041</v>
       </c>
       <c r="AY42" s="5">
-        <v>3711.636762555785</v>
+        <v>4004.1084617646702</v>
       </c>
       <c r="AZ42" s="5">
-        <v>1976.1165716411008</v>
+        <v>1994.0965046865933</v>
       </c>
       <c r="BA42" s="5">
-        <v>4132.6970867031332</v>
+        <v>3998.1142896605575</v>
       </c>
       <c r="BB42" s="5">
-        <v>6155.891540767012</v>
+        <v>6596.6464749135257</v>
       </c>
       <c r="BC42" s="5">
-        <v>659.37411825947038</v>
+        <v>665.10850862323116</v>
       </c>
       <c r="BD42" s="5">
-        <v>138.42741350448173</v>
+        <v>142.3592666723215</v>
       </c>
       <c r="BE42" s="5">
-        <v>2634.2693625091929</v>
+        <v>2693.4283645267142</v>
       </c>
       <c r="BF42" s="5">
-        <v>466.92005762442381</v>
+        <v>480.82494455397438</v>
       </c>
       <c r="BG42" s="5">
-        <v>11346.267815593343</v>
+        <v>11928.031510347018</v>
       </c>
       <c r="BH42" s="5">
-        <v>2489.8161685904952</v>
+        <v>2585.5123443901512</v>
       </c>
       <c r="BI42" s="5">
-        <v>5579.9963578207271</v>
+        <v>5820.8266564694077</v>
       </c>
       <c r="BJ42" s="5">
-        <v>1973.3596495860718</v>
+        <v>2109.5191462936796</v>
       </c>
       <c r="BK42" s="5">
         <v>0</v>
       </c>
       <c r="BL42" s="6">
-        <v>139975.65692059346</v>
+        <v>139975.65692059338</v>
       </c>
       <c r="BM42" s="5">
         <v>30387.97944304295</v>
@@ -10169,7 +10193,7 @@
         <v>30387.979443042947</v>
       </c>
       <c r="BS42" s="5">
-        <v>170363.63636363641</v>
+        <v>170363.63636363632</v>
       </c>
       <c r="BT42" s="5">
         <v>0</v>
@@ -10192,55 +10216,55 @@
         <v>44</v>
       </c>
       <c r="C43" s="5">
-        <v>1.0547934499267482</v>
+        <v>1.0542671835719595</v>
       </c>
       <c r="D43" s="5">
-        <v>0.32517670981223507</v>
+        <v>0.30599931102901679</v>
       </c>
       <c r="E43" s="5">
-        <v>0.21465921047108438</v>
+        <v>0.20217849498467311</v>
       </c>
       <c r="F43" s="5">
-        <v>4.9514001106343448</v>
+        <v>4.7013912374727234</v>
       </c>
       <c r="G43" s="5">
-        <v>4.5868441207066368</v>
+        <v>4.3258957860717624</v>
       </c>
       <c r="H43" s="5">
-        <v>355.90984328838613</v>
+        <v>342.50485143234636</v>
       </c>
       <c r="I43" s="5">
-        <v>78.30752347247028</v>
+        <v>73.92503733770188</v>
       </c>
       <c r="J43" s="5">
-        <v>26.31764151663446</v>
+        <v>24.968150211129501</v>
       </c>
       <c r="K43" s="5">
-        <v>2.5843281427796101</v>
+        <v>2.4156951787238352</v>
       </c>
       <c r="L43" s="5">
-        <v>43.152703977002844</v>
+        <v>43.409054428963501</v>
       </c>
       <c r="M43" s="5">
-        <v>11.004327520545644</v>
+        <v>10.302673085236783</v>
       </c>
       <c r="N43" s="5">
-        <v>0.7829736412277235</v>
+        <v>0.73418689948917748</v>
       </c>
       <c r="O43" s="5">
-        <v>69.881419767620002</v>
+        <v>65.338732909303687</v>
       </c>
       <c r="P43" s="5">
-        <v>6.2978226961454613</v>
+        <v>6.5692800330441701</v>
       </c>
       <c r="Q43" s="5">
-        <v>3.4048215451189257</v>
+        <v>3.5662497940624864</v>
       </c>
       <c r="R43" s="5">
-        <v>116.1295973556589</v>
+        <v>114.98612800181428</v>
       </c>
       <c r="S43" s="5">
-        <v>18.380402814699011</v>
+        <v>18.6575655423234</v>
       </c>
       <c r="T43" s="5">
         <v>106.9755995662637</v>
@@ -10255,40 +10279,40 @@
         <v>8.4812223583011512</v>
       </c>
       <c r="X43" s="5">
-        <v>264.80101952079258</v>
+        <v>251.36380362757615</v>
       </c>
       <c r="Y43" s="5">
-        <v>742.72512382281536</v>
+        <v>764.31897599119316</v>
       </c>
       <c r="Z43" s="5">
-        <v>84.187474085038417</v>
+        <v>81.153339108916782</v>
       </c>
       <c r="AA43" s="5">
-        <v>160.09111385704691</v>
+        <v>154.70937875684587</v>
       </c>
       <c r="AB43" s="5">
-        <v>217.66822483124034</v>
+        <v>212.24136598464949</v>
       </c>
       <c r="AC43" s="5">
-        <v>58.461224404258225</v>
+        <v>55.595724621523011</v>
       </c>
       <c r="AD43" s="5">
-        <v>339.19689547244667</v>
+        <v>320.11531131448351</v>
       </c>
       <c r="AE43" s="5">
-        <v>8.1643112505756203</v>
+        <v>8.088916990521227</v>
       </c>
       <c r="AF43" s="5">
-        <v>7.6560817129546086</v>
+        <v>7.3585186370832956</v>
       </c>
       <c r="AG43" s="5">
-        <v>13.031087039830986</v>
+        <v>13.219402298598766</v>
       </c>
       <c r="AH43" s="5">
-        <v>112.00154689836627</v>
+        <v>113.79140585476853</v>
       </c>
       <c r="AI43" s="5">
-        <v>5.0339985373918292</v>
+        <v>4.9247052090590486</v>
       </c>
       <c r="AJ43" s="5">
         <v>56.042801531830087</v>
@@ -10303,28 +10327,28 @@
         <v>2.173654511047824</v>
       </c>
       <c r="AN43" s="5">
-        <v>3.0607754899745836</v>
+        <v>3.1623260726276108</v>
       </c>
       <c r="AO43" s="5">
         <v>5.2841073171818529</v>
       </c>
       <c r="AP43" s="5">
-        <v>25.455599821853063</v>
+        <v>25.494524546608048</v>
       </c>
       <c r="AQ43" s="5">
-        <v>85.22358310984832</v>
+        <v>80.763054876294561</v>
       </c>
       <c r="AR43" s="5">
-        <v>9.6329436864723448</v>
+        <v>9.4677177432439734</v>
       </c>
       <c r="AS43" s="5">
-        <v>148.22351589214361</v>
+        <v>139.69294403876299</v>
       </c>
       <c r="AT43" s="5">
-        <v>110.3343213698477</v>
+        <v>109.86448370646082</v>
       </c>
       <c r="AU43" s="5">
-        <v>101.9253643087314</v>
+        <v>98.233597875201028</v>
       </c>
       <c r="AV43" s="5">
         <v>21.871102108874933</v>
@@ -10339,46 +10363,46 @@
         <v>17.750876956198308</v>
       </c>
       <c r="AZ43" s="5">
-        <v>308.3681456256337</v>
+        <v>297.04842216066794</v>
       </c>
       <c r="BA43" s="5">
-        <v>441.70597308603203</v>
+        <v>418.65297184001264</v>
       </c>
       <c r="BB43" s="5">
-        <v>47.506061693488562</v>
+        <v>44.614959267134942</v>
       </c>
       <c r="BC43" s="5">
-        <v>8.5955745935791938</v>
+        <v>8.2762353956812511</v>
       </c>
       <c r="BD43" s="5">
-        <v>1.4749140596102193</v>
+        <v>1.3519801488791818</v>
       </c>
       <c r="BE43" s="5">
-        <v>350.07038667312935</v>
+        <v>339.3851522594133</v>
       </c>
       <c r="BF43" s="5">
         <v>16.61667085865637</v>
       </c>
       <c r="BG43" s="5">
-        <v>1620.8921335195232</v>
+        <v>1692.5732734257492</v>
       </c>
       <c r="BH43" s="5">
-        <v>277.63099711304488</v>
+        <v>284.03763169928811</v>
       </c>
       <c r="BI43" s="5">
-        <v>1484.1794998693742</v>
+        <v>1504.391954316442</v>
       </c>
       <c r="BJ43" s="5">
-        <v>198.55665560409761</v>
+        <v>217.28141165404836</v>
       </c>
       <c r="BK43" s="5">
         <v>0</v>
       </c>
       <c r="BL43" s="6">
-        <v>8372.3285410952631</v>
+        <v>8372.3285410952831</v>
       </c>
       <c r="BM43" s="5">
-        <v>3831.7218213066012</v>
+        <v>3831.7218213066017</v>
       </c>
       <c r="BN43" s="5">
         <v>422.00327744489209</v>
@@ -10396,7 +10420,7 @@
         <v>4253.7250987514935</v>
       </c>
       <c r="BS43" s="5">
-        <v>12626.053639846756</v>
+        <v>12626.053639846778</v>
       </c>
       <c r="BT43" s="5">
         <v>0</v>
@@ -10419,34 +10443,34 @@
         <v>8</v>
       </c>
       <c r="C44" s="5">
-        <v>18.577890207226446</v>
+        <v>19.450819906346737</v>
       </c>
       <c r="D44" s="5">
-        <v>13.535552702508538</v>
+        <v>14.096538322174663</v>
       </c>
       <c r="E44" s="5">
-        <v>9.6966864778132127</v>
+        <v>9.9796013810265141</v>
       </c>
       <c r="F44" s="5">
-        <v>215.90326416098497</v>
+        <v>227.11910766561832</v>
       </c>
       <c r="G44" s="5">
-        <v>186.7905396894202</v>
+        <v>195.58365026579668</v>
       </c>
       <c r="H44" s="5">
-        <v>13218.593775504791</v>
+        <v>13158.088147001434</v>
       </c>
       <c r="I44" s="5">
-        <v>3379.6471419780009</v>
+        <v>3504.5111214024996</v>
       </c>
       <c r="J44" s="5">
-        <v>1018.1633485213384</v>
+        <v>1051.40900068325</v>
       </c>
       <c r="K44" s="5">
-        <v>122.54910503294305</v>
+        <v>126.75797240181555</v>
       </c>
       <c r="L44" s="5">
-        <v>1470.3891669456427</v>
+        <v>1475.7740874431829</v>
       </c>
       <c r="M44" s="5">
         <v>0</v>
@@ -10458,7 +10482,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="5">
-        <v>607.92527974094696</v>
+        <v>606.92983704606945</v>
       </c>
       <c r="Q44" s="5">
         <v>542.04413472706165</v>
@@ -10470,16 +10494,16 @@
         <v>0</v>
       </c>
       <c r="T44" s="5">
-        <v>12070.774516007792</v>
+        <v>11477.234904000459</v>
       </c>
       <c r="U44" s="5">
-        <v>6945.606940849586</v>
+        <v>6932.0223317526461</v>
       </c>
       <c r="V44" s="5">
-        <v>1417.109320945453</v>
+        <v>1385.8738650335113</v>
       </c>
       <c r="W44" s="5">
-        <v>734.52011847998824</v>
+        <v>687.83195595059249</v>
       </c>
       <c r="X44" s="5">
         <v>0</v>
@@ -10503,28 +10527,28 @@
         <v>0</v>
       </c>
       <c r="AE44" s="5">
-        <v>976.46521769465039</v>
+        <v>1023.879789621192</v>
       </c>
       <c r="AF44" s="5">
-        <v>1423.5755253604582</v>
+        <v>1487.2675357924484</v>
       </c>
       <c r="AG44" s="5">
-        <v>742.11343184821123</v>
+        <v>776.21584265381921</v>
       </c>
       <c r="AH44" s="5">
-        <v>686.13466776758492</v>
+        <v>719.46733147635655</v>
       </c>
       <c r="AI44" s="5">
-        <v>1433.3564238665081</v>
+        <v>1502.560553313783</v>
       </c>
       <c r="AJ44" s="5">
-        <v>6960.4231101582409</v>
+        <v>7260.1778792748191</v>
       </c>
       <c r="AK44" s="5">
-        <v>13520.103457522144</v>
+        <v>14133.537041865067</v>
       </c>
       <c r="AL44" s="5">
-        <v>2339.3870658205319</v>
+        <v>2406.0884797156564</v>
       </c>
       <c r="AM44" s="5">
         <v>0</v>
@@ -10536,34 +10560,34 @@
         <v>0</v>
       </c>
       <c r="AP44" s="5">
-        <v>3010.6901716090333</v>
+        <v>3118.9551474883597</v>
       </c>
       <c r="AQ44" s="5">
-        <v>6323.8027587425613</v>
+        <v>6633.9346366322616</v>
       </c>
       <c r="AR44" s="5">
-        <v>191.29078571827279</v>
+        <v>197.11096422802979</v>
       </c>
       <c r="AS44" s="5">
         <v>0</v>
       </c>
       <c r="AT44" s="5">
-        <v>12474.797696534768</v>
+        <v>12775.448519933943</v>
       </c>
       <c r="AU44" s="5">
-        <v>17701.389928290799</v>
+        <v>18189.307946447243</v>
       </c>
       <c r="AV44" s="5">
-        <v>7224.0867053423799</v>
+        <v>7563.5787995250084</v>
       </c>
       <c r="AW44" s="5">
-        <v>7752.1487836107035</v>
+        <v>8118.6700239773072</v>
       </c>
       <c r="AX44" s="5">
-        <v>14575.179190810331</v>
+        <v>15312.122008248991</v>
       </c>
       <c r="AY44" s="5">
-        <v>7236.7277159059895</v>
+        <v>7533.5232522562155</v>
       </c>
       <c r="AZ44" s="5">
         <v>0</v>
@@ -10572,58 +10596,58 @@
         <v>0</v>
       </c>
       <c r="BB44" s="5">
-        <v>8700.2211337246208</v>
+        <v>9110.3553744550009</v>
       </c>
       <c r="BC44" s="5">
-        <v>1579.6460148703609</v>
+        <v>1650.556517731193</v>
       </c>
       <c r="BD44" s="5">
-        <v>377.80446073918239</v>
+        <v>396.76425408605479</v>
       </c>
       <c r="BE44" s="5">
-        <v>51777.610560650544</v>
+        <v>52186.467261541846</v>
       </c>
       <c r="BF44" s="5">
-        <v>1229.916970420767</v>
+        <v>1270.7241079784246</v>
       </c>
       <c r="BG44" s="5">
         <v>35641.571428571428</v>
       </c>
       <c r="BH44" s="5">
-        <v>4066.261859221016</v>
+        <v>4054.8570691976797</v>
       </c>
       <c r="BI44" s="5">
-        <v>8126.481186525496</v>
+        <v>8479.289995142628</v>
       </c>
       <c r="BJ44" s="5">
-        <v>2965.6752784697583</v>
+        <v>3048.5761062446622</v>
       </c>
       <c r="BK44" s="5">
         <v>0</v>
       </c>
       <c r="BL44" s="6">
-        <v>261008.68831176776</v>
+        <v>266005.71494238294</v>
       </c>
       <c r="BM44" s="5">
-        <v>0</v>
+        <v>3203</v>
       </c>
       <c r="BN44" s="5">
         <v>0</v>
       </c>
       <c r="BO44" s="5">
-        <v>4715971.2527384581</v>
+        <v>6457491.2827384574</v>
       </c>
       <c r="BP44" s="5">
         <v>0</v>
       </c>
       <c r="BQ44" s="5">
-        <v>1749720.0589497739</v>
+        <v>0</v>
       </c>
       <c r="BR44" s="6">
-        <v>6465691.3116882322</v>
+        <v>6460694.2827384574</v>
       </c>
       <c r="BS44" s="5">
-        <v>6726700</v>
+        <v>6726699.9976808401</v>
       </c>
       <c r="BT44" s="5">
         <v>0</v>
@@ -10646,193 +10670,193 @@
         <v>45</v>
       </c>
       <c r="C45" s="5">
-        <v>159.4047704651947</v>
+        <v>157.80787481666533</v>
       </c>
       <c r="D45" s="5">
-        <v>51.331953569013159</v>
+        <v>51.230641878980812</v>
       </c>
       <c r="E45" s="5">
-        <v>33.498339864241416</v>
+        <v>33.677545010891528</v>
       </c>
       <c r="F45" s="5">
-        <v>779.93135594975422</v>
+        <v>773.03199055695131</v>
       </c>
       <c r="G45" s="5">
-        <v>740.62978626795541</v>
+        <v>733.35572675789115</v>
       </c>
       <c r="H45" s="5">
-        <v>51667.161043996908</v>
+        <v>53140.953527072161</v>
       </c>
       <c r="I45" s="5">
-        <v>12604.220465194099</v>
+        <v>13367.965564618782</v>
       </c>
       <c r="J45" s="5">
-        <v>3834.5347488409861</v>
+        <v>3980.5101309400948</v>
       </c>
       <c r="K45" s="5">
-        <v>394.64558555201393</v>
+        <v>400.39719698362364</v>
       </c>
       <c r="L45" s="5">
-        <v>5587.3081712847088</v>
+        <v>5460.3146990708838</v>
       </c>
       <c r="M45" s="5">
-        <v>778.95831896463039</v>
+        <v>778.95831896463051</v>
       </c>
       <c r="N45" s="5">
         <v>43.822864372063719</v>
       </c>
       <c r="O45" s="5">
-        <v>4273.1177808132707</v>
+        <v>4273.1177808132716</v>
       </c>
       <c r="P45" s="5">
-        <v>2087.7628514197645</v>
+        <v>2100.2699077419811</v>
       </c>
       <c r="Q45" s="5">
-        <v>1090.663604739651</v>
+        <v>1147.1729407197984</v>
       </c>
       <c r="R45" s="5">
-        <v>23937.637302218907</v>
+        <v>26375.652423199012</v>
       </c>
       <c r="S45" s="5">
-        <v>931.87765804179628</v>
+        <v>974.40774562754859</v>
       </c>
       <c r="T45" s="5">
-        <v>20226.26437241261</v>
+        <v>23947.61325804441</v>
       </c>
       <c r="U45" s="5">
-        <v>5332.2462204913936</v>
+        <v>5949.5510985229248</v>
       </c>
       <c r="V45" s="5">
-        <v>1692.9683163885759</v>
+        <v>1660.9359065525978</v>
       </c>
       <c r="W45" s="5">
-        <v>1920.9807998704473</v>
+        <v>1884.6572874655362</v>
       </c>
       <c r="X45" s="5">
-        <v>41369.824850972858</v>
+        <v>42106.876903102821</v>
       </c>
       <c r="Y45" s="5">
-        <v>110684.65967504741</v>
+        <v>113519.0284399121</v>
       </c>
       <c r="Z45" s="5">
-        <v>17428.18592046971</v>
+        <v>18250.560087512757</v>
       </c>
       <c r="AA45" s="5">
-        <v>27575.720541243467</v>
+        <v>27962.114337754414</v>
       </c>
       <c r="AB45" s="5">
-        <v>54242.03725249663</v>
+        <v>55553.894517459681</v>
       </c>
       <c r="AC45" s="5">
-        <v>14618.5153322761</v>
+        <v>14901.291633217585</v>
       </c>
       <c r="AD45" s="5">
-        <v>10269.271166393984</v>
+        <v>10525.151696433535</v>
       </c>
       <c r="AE45" s="5">
-        <v>9855.6578733736806</v>
+        <v>10150.928936488599</v>
       </c>
       <c r="AF45" s="5">
-        <v>7732.0371833055169</v>
+        <v>7696.076320991282</v>
       </c>
       <c r="AG45" s="5">
-        <v>5102.4896315702526</v>
+        <v>5269.8139974066471</v>
       </c>
       <c r="AH45" s="5">
-        <v>6851.1731747741651</v>
+        <v>7036.5576527824051</v>
       </c>
       <c r="AI45" s="5">
-        <v>9587.6263993375087</v>
+        <v>9983.6182840325055</v>
       </c>
       <c r="AJ45" s="5">
-        <v>27389.368676336424</v>
+        <v>30785.222963731398</v>
       </c>
       <c r="AK45" s="5">
-        <v>47382.330437561614</v>
+        <v>49371.331949696389</v>
       </c>
       <c r="AL45" s="5">
-        <v>28115.694100592271</v>
+        <v>28893.917612050529</v>
       </c>
       <c r="AM45" s="5">
-        <v>3154.6589208811429</v>
+        <v>3165.8511528914996</v>
       </c>
       <c r="AN45" s="5">
-        <v>3679.8992491944173</v>
+        <v>3669.0831578845391</v>
       </c>
       <c r="AO45" s="5">
-        <v>4701.9277303489407</v>
+        <v>4835.3372328781443</v>
       </c>
       <c r="AP45" s="5">
-        <v>42034.396632538519</v>
+        <v>43156.861185921705</v>
       </c>
       <c r="AQ45" s="5">
-        <v>522.75044530151138</v>
+        <v>502.83771519690578</v>
       </c>
       <c r="AR45" s="5">
         <v>117.93493852472469</v>
       </c>
       <c r="AS45" s="5">
-        <v>361109.53182283079</v>
+        <v>370267.06703124079</v>
       </c>
       <c r="AT45" s="5">
-        <v>14175.825079628146</v>
+        <v>13889.324395763468</v>
       </c>
       <c r="AU45" s="5">
-        <v>212427.06420164628</v>
+        <v>219657.96981963157</v>
       </c>
       <c r="AV45" s="5">
-        <v>15632.174222187277</v>
+        <v>15986.713529293054</v>
       </c>
       <c r="AW45" s="5">
-        <v>10892.889459717699</v>
+        <v>10909.178416320701</v>
       </c>
       <c r="AX45" s="5">
-        <v>0</v>
+        <v>2001.2</v>
       </c>
       <c r="AY45" s="5">
-        <v>2130.2791820190259</v>
+        <v>2112.1971433837966</v>
       </c>
       <c r="AZ45" s="5">
-        <v>5844.5789836057156</v>
+        <v>5503.7171747780649</v>
       </c>
       <c r="BA45" s="5">
-        <v>84552.953536561399</v>
+        <v>85711.271034523423</v>
       </c>
       <c r="BB45" s="5">
-        <v>16760.853087037663</v>
+        <v>17653.124287859835</v>
       </c>
       <c r="BC45" s="5">
-        <v>1093.4373516647406</v>
+        <v>1035.9368198151349</v>
       </c>
       <c r="BD45" s="5">
-        <v>178.9278302074095</v>
+        <v>167.93724496579171</v>
       </c>
       <c r="BE45" s="5">
-        <v>7925.047326070915</v>
+        <v>7843.0172205686295</v>
       </c>
       <c r="BF45" s="5">
-        <v>1994.1633358174699</v>
+        <v>1935.2966281253132</v>
       </c>
       <c r="BG45" s="5">
-        <v>44725.495319320034</v>
+        <v>46104.393322264819</v>
       </c>
       <c r="BH45" s="5">
         <v>7454.7564170427841</v>
       </c>
       <c r="BI45" s="5">
-        <v>35358.458460018686</v>
+        <v>36423.802237632663</v>
       </c>
       <c r="BJ45" s="5">
-        <v>6912.4819286599404</v>
+        <v>7058.1111634885474</v>
       </c>
       <c r="BK45" s="5">
         <v>0</v>
       </c>
       <c r="BL45" s="6">
-        <v>1439754.0439872949</v>
+        <v>1486404.7090322988</v>
       </c>
       <c r="BM45" s="5">
-        <v>143402.28468101437</v>
+        <v>123390.28468101437</v>
       </c>
       <c r="BN45" s="5">
         <v>0</v>
@@ -10844,13 +10868,13 @@
         <v>0</v>
       </c>
       <c r="BQ45" s="5">
-        <v>167548.06527108478</v>
+        <v>140909.40022608044</v>
       </c>
       <c r="BR45" s="6">
-        <v>310950.34995209915</v>
+        <v>264299.68490709481</v>
       </c>
       <c r="BS45" s="5">
-        <v>1750704.393939394</v>
+        <v>1750704.3939393936</v>
       </c>
       <c r="BT45" s="5">
         <v>0</v>
@@ -10885,19 +10909,19 @@
         <v>31.372166119203271</v>
       </c>
       <c r="G46" s="5">
-        <v>89.398588131453906</v>
+        <v>89.398588131453891</v>
       </c>
       <c r="H46" s="5">
-        <v>15345.312246613283</v>
+        <v>15345.312246613281</v>
       </c>
       <c r="I46" s="5">
-        <v>1735.0949420568199</v>
+        <v>1735.0949420568202</v>
       </c>
       <c r="J46" s="5">
         <v>834.77163335217347</v>
       </c>
       <c r="K46" s="5">
-        <v>39.172433859617229</v>
+        <v>39.172433859617236</v>
       </c>
       <c r="L46" s="5">
         <v>1192.3666661275031</v>
@@ -10915,16 +10939,16 @@
         <v>912.21719780179876</v>
       </c>
       <c r="Q46" s="5">
-        <v>493.37936805814707</v>
+        <v>493.37936805814701</v>
       </c>
       <c r="R46" s="5">
-        <v>5335.3380259951509</v>
+        <v>5335.33802599515</v>
       </c>
       <c r="S46" s="5">
-        <v>1878.0336501127279</v>
+        <v>1914.9630194300562</v>
       </c>
       <c r="T46" s="5">
-        <v>13033.575005023717</v>
+        <v>13033.575005023718</v>
       </c>
       <c r="U46" s="5">
         <v>1321.3064827518208</v>
@@ -10939,7 +10963,7 @@
         <v>2293.0942964930118</v>
       </c>
       <c r="Y46" s="5">
-        <v>19369.636299464801</v>
+        <v>19369.636299464797</v>
       </c>
       <c r="Z46" s="5">
         <v>1668.6246599202218</v>
@@ -10948,7 +10972,7 @@
         <v>2842.8951401930249</v>
       </c>
       <c r="AB46" s="5">
-        <v>5027.8763842022272</v>
+        <v>5027.8763842022281</v>
       </c>
       <c r="AC46" s="5">
         <v>1708.925122990024</v>
@@ -10960,16 +10984,16 @@
         <v>1088.5158481107715</v>
       </c>
       <c r="AF46" s="5">
-        <v>965.74607809138831</v>
+        <v>965.74607809138843</v>
       </c>
       <c r="AG46" s="5">
-        <v>509.50519416657556</v>
+        <v>509.50519416657562</v>
       </c>
       <c r="AH46" s="5">
-        <v>3659.1378710372328</v>
+        <v>3659.1378710372337</v>
       </c>
       <c r="AI46" s="5">
-        <v>664.99040229607328</v>
+        <v>664.9904022960734</v>
       </c>
       <c r="AJ46" s="5">
         <v>6946.5192725259585</v>
@@ -11020,13 +11044,13 @@
         <v>2130.2791820190259</v>
       </c>
       <c r="AZ46" s="5">
-        <v>10785.670204857761</v>
+        <v>10832.045958099787</v>
       </c>
       <c r="BA46" s="5">
-        <v>35049.134736231434</v>
+        <v>34367.749381915477</v>
       </c>
       <c r="BB46" s="5">
-        <v>6169.4409354271302</v>
+        <v>6200.2481581371803</v>
       </c>
       <c r="BC46" s="5">
         <v>1093.4373516647406</v>
@@ -11035,31 +11059,31 @@
         <v>178.9278302074095</v>
       </c>
       <c r="BE46" s="5">
-        <v>8249.4424599005615</v>
+        <v>8341.9207765575811</v>
       </c>
       <c r="BF46" s="5">
         <v>1994.1633358174699</v>
       </c>
       <c r="BG46" s="5">
-        <v>28654.620230805176</v>
+        <v>28715.161010379059</v>
       </c>
       <c r="BH46" s="5">
-        <v>11423.123421767707</v>
+        <v>11447.765440913648</v>
       </c>
       <c r="BI46" s="5">
         <v>8484.3973723213512</v>
       </c>
       <c r="BJ46" s="5">
-        <v>30983.817559579558</v>
+        <v>31510.586863881028</v>
       </c>
       <c r="BK46" s="5">
         <v>0</v>
       </c>
       <c r="BL46" s="6">
-        <v>308608.89815455722</v>
+        <v>308746.05556518893</v>
       </c>
       <c r="BM46" s="5">
-        <v>1252474.558664531</v>
+        <v>1242660.271822426</v>
       </c>
       <c r="BN46" s="5">
         <v>0</v>
@@ -11071,13 +11095,13 @@
         <v>0</v>
       </c>
       <c r="BQ46" s="5">
-        <v>1010210.0671038817</v>
+        <v>1019887.1965353553</v>
       </c>
       <c r="BR46" s="6">
-        <v>2262684.6257684128</v>
+        <v>2262547.4683577814</v>
       </c>
       <c r="BS46" s="5">
-        <v>2571293.5239229701</v>
+        <v>2571293.5239229705</v>
       </c>
       <c r="BT46" s="5">
         <v>0</v>
@@ -11100,193 +11124,193 @@
         <v>47</v>
       </c>
       <c r="C47" s="5">
-        <v>47.781634996150174</v>
+        <v>47.307106151738544</v>
       </c>
       <c r="D47" s="5">
-        <v>20.637112089824953</v>
+        <v>20.688493831343372</v>
       </c>
       <c r="E47" s="5">
-        <v>13.60847348694988</v>
+        <v>13.646674883557584</v>
       </c>
       <c r="F47" s="5">
-        <v>344.36003658276059</v>
+        <v>347.68493571072798</v>
       </c>
       <c r="G47" s="5">
-        <v>312.41177743145818</v>
+        <v>314.3876197917902</v>
       </c>
       <c r="H47" s="5">
-        <v>20004.664824736137</v>
+        <v>19991.821958010536</v>
       </c>
       <c r="I47" s="5">
-        <v>5316.9897764658281</v>
+        <v>5360.9864927258786</v>
       </c>
       <c r="J47" s="5">
-        <v>1644.1145324894574</v>
+        <v>1647.7382502716589</v>
       </c>
       <c r="K47" s="5">
-        <v>171.13681997063856</v>
+        <v>171.71731054149856</v>
       </c>
       <c r="L47" s="5">
-        <v>2190.2005433998975</v>
+        <v>2193.5475634986124</v>
       </c>
       <c r="M47" s="5">
-        <v>371.31939419443012</v>
+        <v>372.0278052771655</v>
       </c>
       <c r="N47" s="5">
-        <v>21.299895208725982</v>
+        <v>21.379599463209814</v>
       </c>
       <c r="O47" s="5">
-        <v>1902.3426024456503</v>
+        <v>1903.4793862365123</v>
       </c>
       <c r="P47" s="5">
-        <v>1913.5833933187323</v>
+        <v>1911.7188524722787</v>
       </c>
       <c r="Q47" s="5">
-        <v>1174.4423524762772</v>
+        <v>1173.3078027578995</v>
       </c>
       <c r="R47" s="5">
-        <v>8325.8730063387102</v>
+        <v>8297.8072355336517</v>
       </c>
       <c r="S47" s="5">
-        <v>503.01913425124343</v>
+        <v>501.83225099745823</v>
       </c>
       <c r="T47" s="5">
-        <v>31454.005837998455</v>
+        <v>30910.416810160728</v>
       </c>
       <c r="U47" s="5">
-        <v>8631.8228456279758</v>
+        <v>8658.6961105127557</v>
       </c>
       <c r="V47" s="5">
-        <v>2626.5746857771846</v>
+        <v>2604.571727366254</v>
       </c>
       <c r="W47" s="5">
-        <v>2342.0616374152946</v>
+        <v>2308.1048931856371</v>
       </c>
       <c r="X47" s="5">
-        <v>13636.834457479197</v>
+        <v>13657.658913656336</v>
       </c>
       <c r="Y47" s="5">
-        <v>26092.186758704047</v>
+        <v>26032.163953048253</v>
       </c>
       <c r="Z47" s="5">
-        <v>6029.5005009523447</v>
+        <v>6023.3685824305212</v>
       </c>
       <c r="AA47" s="5">
-        <v>6759.9004810005044</v>
+        <v>6751.0919910434823</v>
       </c>
       <c r="AB47" s="5">
-        <v>10819.126588336891</v>
+        <v>10811.764413602841</v>
       </c>
       <c r="AC47" s="5">
-        <v>3619.9446685488333</v>
+        <v>3618.2524999106022</v>
       </c>
       <c r="AD47" s="5">
-        <v>2263.383164470511</v>
+        <v>2271.7630480715252</v>
       </c>
       <c r="AE47" s="5">
-        <v>2032.5678787645875</v>
+        <v>2032.3133921730512</v>
       </c>
       <c r="AF47" s="5">
-        <v>4112.7971774578391</v>
+        <v>4114.114352469398</v>
       </c>
       <c r="AG47" s="5">
-        <v>1402.5130720969453</v>
+        <v>1375.4887028307803</v>
       </c>
       <c r="AH47" s="5">
-        <v>2021.7234650952225</v>
+        <v>2003.1864268532956</v>
       </c>
       <c r="AI47" s="5">
-        <v>2733.9505299274801</v>
+        <v>2735.5328874367901</v>
       </c>
       <c r="AJ47" s="5">
-        <v>28857.034920622784</v>
+        <v>28783.085686041464</v>
       </c>
       <c r="AK47" s="5">
-        <v>40811.447083918298</v>
+        <v>40758.047378778014</v>
       </c>
       <c r="AL47" s="5">
-        <v>4875.9852381173005</v>
+        <v>4856.1722513550285</v>
       </c>
       <c r="AM47" s="5">
-        <v>657.81801901792915</v>
+        <v>655.06459741474066</v>
       </c>
       <c r="AN47" s="5">
-        <v>699.37721189666388</v>
+        <v>655.06510360102925</v>
       </c>
       <c r="AO47" s="5">
-        <v>696.5167915541374</v>
+        <v>692.91433009697266</v>
       </c>
       <c r="AP47" s="5">
-        <v>8019.4556471034575</v>
+        <v>7992.7093708790308</v>
       </c>
       <c r="AQ47" s="5">
-        <v>1710.2893004526863</v>
+        <v>1711.2129872006308</v>
       </c>
       <c r="AR47" s="5">
-        <v>177.40269133720372</v>
+        <v>177.81091392583573</v>
       </c>
       <c r="AS47" s="5">
-        <v>155173.6602615497</v>
+        <v>156160.67936265489</v>
       </c>
       <c r="AT47" s="5">
-        <v>39373.427709335949</v>
+        <v>39362.245206510022</v>
       </c>
       <c r="AU47" s="5">
-        <v>37413.387124732275</v>
+        <v>37461.143356984809</v>
       </c>
       <c r="AV47" s="5">
-        <v>659.14378882881658</v>
+        <v>564.90840942056673</v>
       </c>
       <c r="AW47" s="5">
-        <v>574.67126727797415</v>
+        <v>488.76361694005016</v>
       </c>
       <c r="AX47" s="5">
         <v>0</v>
       </c>
       <c r="AY47" s="5">
-        <v>12758.659439168423</v>
+        <v>12899.279396998087</v>
       </c>
       <c r="AZ47" s="5">
-        <v>3628.5430814169563</v>
+        <v>3634.4991532216809</v>
       </c>
       <c r="BA47" s="5">
-        <v>13982.238002166248</v>
+        <v>13997.108446650942</v>
       </c>
       <c r="BB47" s="5">
-        <v>1431.7214258843921</v>
+        <v>1104.2470546332561</v>
       </c>
       <c r="BC47" s="5">
-        <v>274.5912483268126</v>
+        <v>209.14052668849433</v>
       </c>
       <c r="BD47" s="5">
-        <v>44.933544827472595</v>
+        <v>34.417108491998341</v>
       </c>
       <c r="BE47" s="5">
-        <v>3085.3285305964632</v>
+        <v>3087.0537900764093</v>
       </c>
       <c r="BF47" s="5">
-        <v>2719.4366071499035</v>
+        <v>2723.855061526152</v>
       </c>
       <c r="BG47" s="5">
-        <v>45577.330037212741</v>
+        <v>45787.021419839963</v>
       </c>
       <c r="BH47" s="5">
-        <v>8489.110758496432</v>
+        <v>8470.2016339024067</v>
       </c>
       <c r="BI47" s="5">
-        <v>13867.216931627554</v>
+        <v>13936.349354677501</v>
       </c>
       <c r="BJ47" s="5">
-        <v>6793.5073825078134</v>
+        <v>6806.349543236458</v>
       </c>
       <c r="BK47" s="5">
         <v>0</v>
       </c>
       <c r="BL47" s="6">
-        <v>603208.91310466256</v>
+        <v>603208.91310465429</v>
       </c>
       <c r="BM47" s="5">
-        <v>191535.66954673675</v>
+        <v>191535.66954673678</v>
       </c>
       <c r="BN47" s="5">
         <v>0</v>
@@ -11301,10 +11325,10 @@
         <v>-1.4210854715202004E-11</v>
       </c>
       <c r="BR47" s="6">
-        <v>191535.66954673675</v>
+        <v>191535.66954673678</v>
       </c>
       <c r="BS47" s="5">
-        <v>794744.58265139931</v>
+        <v>794744.58265139104</v>
       </c>
       <c r="BT47" s="5">
         <v>0</v>
@@ -11345,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="5">
-        <v>0</v>
+        <v>107.71255959590309</v>
       </c>
       <c r="J48" s="5">
         <v>0</v>
@@ -11372,115 +11396,115 @@
         <v>0</v>
       </c>
       <c r="R48" s="5">
-        <v>35950.021628977651</v>
+        <v>37997.006128058209</v>
       </c>
       <c r="S48" s="5">
         <v>0</v>
       </c>
       <c r="T48" s="5">
-        <v>63603.632864169187</v>
+        <v>63603.63286416918</v>
       </c>
       <c r="U48" s="5">
         <v>10689.87289223426</v>
       </c>
       <c r="V48" s="5">
-        <v>4582.0275177017347</v>
+        <v>4582.0275177017356</v>
       </c>
       <c r="W48" s="5">
         <v>3635.1064055969732</v>
       </c>
       <c r="X48" s="5">
-        <v>0</v>
+        <v>129.87337937139625</v>
       </c>
       <c r="Y48" s="5">
         <v>0</v>
       </c>
       <c r="Z48" s="5">
-        <v>0</v>
+        <v>80.172151203895893</v>
       </c>
       <c r="AA48" s="5">
-        <v>0</v>
+        <v>117.03601607782022</v>
       </c>
       <c r="AB48" s="5">
         <v>0</v>
       </c>
       <c r="AC48" s="5">
-        <v>0</v>
+        <v>86.61871672734226</v>
       </c>
       <c r="AD48" s="5">
-        <v>0</v>
+        <v>21.920099304314114</v>
       </c>
       <c r="AE48" s="5">
-        <v>0</v>
+        <v>47.165355347695858</v>
       </c>
       <c r="AF48" s="5">
-        <v>0</v>
+        <v>408.82849312632931</v>
       </c>
       <c r="AG48" s="5">
-        <v>0</v>
+        <v>26.754835116129676</v>
       </c>
       <c r="AH48" s="5">
-        <v>0</v>
+        <v>139.71430847234305</v>
       </c>
       <c r="AI48" s="5">
-        <v>0</v>
+        <v>23.572780878020101</v>
       </c>
       <c r="AJ48" s="5">
-        <v>0</v>
+        <v>948.93076579339788</v>
       </c>
       <c r="AK48" s="5">
-        <v>24442.356928585643</v>
+        <v>23071.050257889856</v>
       </c>
       <c r="AL48" s="5">
-        <v>0</v>
+        <v>180.70207646333191</v>
       </c>
       <c r="AM48" s="5">
-        <v>0</v>
+        <v>28.013344532821783</v>
       </c>
       <c r="AN48" s="5">
-        <v>0</v>
+        <v>31.581445042905948</v>
       </c>
       <c r="AO48" s="5">
-        <v>0</v>
+        <v>23.499796615190125</v>
       </c>
       <c r="AP48" s="5">
-        <v>0</v>
+        <v>220.76622831161245</v>
       </c>
       <c r="AQ48" s="5">
         <v>0</v>
       </c>
       <c r="AR48" s="5">
-        <v>0</v>
+        <v>3.7050758948930236</v>
       </c>
       <c r="AS48" s="5">
-        <v>0</v>
+        <v>1474.4890764519455</v>
       </c>
       <c r="AT48" s="5">
-        <v>60657.618153171359</v>
+        <v>63548.621129013234</v>
       </c>
       <c r="AU48" s="5">
-        <v>0</v>
+        <v>402.59445733615121</v>
       </c>
       <c r="AV48" s="5">
-        <v>0</v>
+        <v>68.9006640579654</v>
       </c>
       <c r="AW48" s="5">
-        <v>0</v>
+        <v>69.359978290626259</v>
       </c>
       <c r="AX48" s="5">
         <v>0</v>
       </c>
       <c r="AY48" s="5">
-        <v>15490.615293132376</v>
+        <v>15490.615293132374</v>
       </c>
       <c r="AZ48" s="5">
         <v>0</v>
       </c>
       <c r="BA48" s="5">
-        <v>0</v>
+        <v>247.13003792682392</v>
       </c>
       <c r="BB48" s="5">
-        <v>0</v>
+        <v>100.30424715495113</v>
       </c>
       <c r="BC48" s="5">
         <v>0</v>
@@ -11492,16 +11516,16 @@
         <v>0</v>
       </c>
       <c r="BF48" s="5">
-        <v>810.21599999999967</v>
+        <v>896.93922284018583</v>
       </c>
       <c r="BG48" s="5">
-        <v>0</v>
+        <v>644.43367122327038</v>
       </c>
       <c r="BH48" s="5">
         <v>0</v>
       </c>
       <c r="BI48" s="5">
-        <v>0</v>
+        <v>238.06075840504258</v>
       </c>
       <c r="BJ48" s="5">
         <v>0</v>
@@ -11510,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="BL48" s="6">
-        <v>219861.46768356915</v>
+        <v>229386.71202935811</v>
       </c>
       <c r="BM48" s="5">
         <v>113799.263289578</v>
@@ -11525,10 +11549,10 @@
         <v>0</v>
       </c>
       <c r="BQ48" s="5">
-        <v>345287.03992468579</v>
+        <v>335761.79557889682</v>
       </c>
       <c r="BR48" s="6">
-        <v>459086.30321426375</v>
+        <v>449561.05886847479</v>
       </c>
       <c r="BS48" s="5">
         <v>678947.77089783293</v>
@@ -11698,7 +11722,7 @@
         <v>0</v>
       </c>
       <c r="AY49" s="5">
-        <v>7196.9887478522023</v>
+        <v>6980.3441819222016</v>
       </c>
       <c r="AZ49" s="5">
         <v>0</v>
@@ -11719,7 +11743,7 @@
         <v>0</v>
       </c>
       <c r="BF49" s="5">
-        <v>1080.2879999999998</v>
+        <v>1134.1563252633468</v>
       </c>
       <c r="BG49" s="5">
         <v>0</v>
@@ -11737,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="BL49" s="6">
-        <v>8277.2767478522019</v>
+        <v>8114.5005071855485</v>
       </c>
       <c r="BM49" s="5">
         <v>132178.94736842107</v>
@@ -11752,13 +11776,13 @@
         <v>0</v>
       </c>
       <c r="BQ49" s="5">
-        <v>1222968.775883727</v>
+        <v>1223131.5521243934</v>
       </c>
       <c r="BR49" s="6">
-        <v>1355147.7232521481</v>
+        <v>1355310.4994928145</v>
       </c>
       <c r="BS49" s="5">
-        <v>1363425.0000000002</v>
+        <v>1363425</v>
       </c>
       <c r="BT49" s="5">
         <v>0</v>
@@ -11781,193 +11805,193 @@
         <v>50</v>
       </c>
       <c r="C50" s="5">
-        <v>10.216087301561627</v>
+        <v>9.4008524224056416</v>
       </c>
       <c r="D50" s="5">
-        <v>0.80643852525803483</v>
+        <v>0.68634337240443521</v>
       </c>
       <c r="E50" s="5">
-        <v>0.55661641719614119</v>
+        <v>0.47202913911245353</v>
       </c>
       <c r="F50" s="5">
-        <v>2.7117297664468967</v>
+        <v>2.4504574985382108</v>
       </c>
       <c r="G50" s="5">
         <v>9.8300367223275504</v>
       </c>
       <c r="H50" s="5">
-        <v>1763.7318046707173</v>
+        <v>1557.8062354683086</v>
       </c>
       <c r="I50" s="5">
-        <v>189.36909902780334</v>
+        <v>185.5406682291171</v>
       </c>
       <c r="J50" s="5">
-        <v>94.065696249104931</v>
+        <v>93.356649588389601</v>
       </c>
       <c r="K50" s="5">
-        <v>4.0675210223995251</v>
+        <v>4.067521022399526</v>
       </c>
       <c r="L50" s="5">
-        <v>135.11454430839501</v>
+        <v>123.6142572627211</v>
       </c>
       <c r="M50" s="5">
-        <v>6.6575616989638666</v>
+        <v>5.7178328342652431</v>
       </c>
       <c r="N50" s="5">
-        <v>0.15870192408293368</v>
+        <v>0.13452403454755307</v>
       </c>
       <c r="O50" s="5">
-        <v>82.640159556761418</v>
+        <v>71.73236137500821</v>
       </c>
       <c r="P50" s="5">
-        <v>93.28421851720887</v>
+        <v>86.930392583043485</v>
       </c>
       <c r="Q50" s="5">
-        <v>55.009555769819883</v>
+        <v>48.633521059961105</v>
       </c>
       <c r="R50" s="5">
-        <v>10060.524797552242</v>
+        <v>10566.450590033572</v>
       </c>
       <c r="S50" s="5">
-        <v>51.106047783228533</v>
+        <v>48.857133004575303</v>
       </c>
       <c r="T50" s="5">
-        <v>14534.455603461118</v>
+        <v>14878.715361829043</v>
       </c>
       <c r="U50" s="5">
-        <v>5184.9224746032769</v>
+        <v>5549.6546044391853</v>
       </c>
       <c r="V50" s="5">
-        <v>1468.8130224448389</v>
+        <v>1500.4962612448046</v>
       </c>
       <c r="W50" s="5">
-        <v>780.8231623265267</v>
+        <v>791.61881055966774</v>
       </c>
       <c r="X50" s="5">
-        <v>10636.441503142507</v>
+        <v>11374.443294406174</v>
       </c>
       <c r="Y50" s="5">
-        <v>6510.6054847461173</v>
+        <v>6839.5070845245709</v>
       </c>
       <c r="Z50" s="5">
-        <v>191.79342134322516</v>
+        <v>172.01417164155143</v>
       </c>
       <c r="AA50" s="5">
-        <v>325.13475069410083</v>
+        <v>286.35781524055193</v>
       </c>
       <c r="AB50" s="5">
-        <v>579.01687603537221</v>
+        <v>517.99115323152444</v>
       </c>
       <c r="AC50" s="5">
-        <v>195.54845236405461</v>
+        <v>175.51491823883111</v>
       </c>
       <c r="AD50" s="5">
-        <v>76.798694745478571</v>
+        <v>67.420407443895627</v>
       </c>
       <c r="AE50" s="5">
-        <v>1594.1746344978392</v>
+        <v>1702.6298167387001</v>
       </c>
       <c r="AF50" s="5">
-        <v>2291.4397955039258</v>
+        <v>2425.7935117398188</v>
       </c>
       <c r="AG50" s="5">
-        <v>1177.4146660936722</v>
+        <v>1257.6741100339259</v>
       </c>
       <c r="AH50" s="5">
-        <v>1429.3897891021761</v>
+        <v>1492.2451711780589</v>
       </c>
       <c r="AI50" s="5">
-        <v>2221.59749570336</v>
+        <v>2391.3006784472786</v>
       </c>
       <c r="AJ50" s="5">
         <v>9155.3060733332131</v>
       </c>
       <c r="AK50" s="5">
-        <v>14959.756837651054</v>
+        <v>15914.210248744796</v>
       </c>
       <c r="AL50" s="5">
-        <v>3945.0865369286075</v>
+        <v>4035.1560815295602</v>
       </c>
       <c r="AM50" s="5">
-        <v>414.98034605333413</v>
+        <v>435.36717370633244</v>
       </c>
       <c r="AN50" s="5">
-        <v>432.01392164515522</v>
+        <v>417.82983072447854</v>
       </c>
       <c r="AO50" s="5">
-        <v>627.96901026686646</v>
+        <v>639.38587314294659</v>
       </c>
       <c r="AP50" s="5">
-        <v>3578.7255515412485</v>
+        <v>3650.5158879651299</v>
       </c>
       <c r="AQ50" s="5">
-        <v>1848.9826570815917</v>
+        <v>1999.1920705362475</v>
       </c>
       <c r="AR50" s="5">
-        <v>65.359929789909501</v>
+        <v>68.32813109168589</v>
       </c>
       <c r="AS50" s="5">
-        <v>59124.556170012889</v>
+        <v>60919.955839352442</v>
       </c>
       <c r="AT50" s="5">
-        <v>55387.915121386832</v>
+        <v>57979.834001932206</v>
       </c>
       <c r="AU50" s="5">
-        <v>37725.079777553066</v>
+        <v>39321.44511951349</v>
       </c>
       <c r="AV50" s="5">
-        <v>13213.071984913791</v>
+        <v>13472.926459505454</v>
       </c>
       <c r="AW50" s="5">
-        <v>39440.479211900136</v>
+        <v>39533.209134548961</v>
       </c>
       <c r="AX50" s="5">
-        <v>120720.72703654025</v>
+        <v>125772.62105658467</v>
       </c>
       <c r="AY50" s="5">
-        <v>5796.1294955234353</v>
+        <v>5796.1294955234362</v>
       </c>
       <c r="AZ50" s="5">
-        <v>2994.3427581461706</v>
+        <v>3231.950471348403</v>
       </c>
       <c r="BA50" s="5">
-        <v>407.5786447831714</v>
+        <v>383.33359943932675</v>
       </c>
       <c r="BB50" s="5">
-        <v>10394.258188886282</v>
+        <v>11088.975578031248</v>
       </c>
       <c r="BC50" s="5">
-        <v>2441.5424524426198</v>
+        <v>2616.9129952902549</v>
       </c>
       <c r="BD50" s="5">
-        <v>604.90601631149218</v>
+        <v>651.54279285565281</v>
       </c>
       <c r="BE50" s="5">
-        <v>3188.8887893009141</v>
+        <v>3367.8161292169193</v>
       </c>
       <c r="BF50" s="5">
-        <v>1821.0957773076088</v>
+        <v>1922.8966555479874</v>
       </c>
       <c r="BG50" s="5">
-        <v>21734.438265452129</v>
+        <v>22310.51943948093</v>
       </c>
       <c r="BH50" s="5">
-        <v>4820.8462157486674</v>
+        <v>4990.4388314017469</v>
       </c>
       <c r="BI50" s="5">
-        <v>7068.3208983183704</v>
+        <v>7309.1564639966837</v>
       </c>
       <c r="BJ50" s="5">
-        <v>2319.3865601350949</v>
+        <v>2420.0190634171113</v>
       </c>
       <c r="BK50" s="5">
         <v>0</v>
       </c>
       <c r="BL50" s="6">
-        <v>485989.96467257512</v>
+        <v>503644.03307434957</v>
       </c>
       <c r="BM50" s="5">
-        <v>69594.659624308144</v>
+        <v>65623.769194558598</v>
       </c>
       <c r="BN50" s="5">
         <v>0</v>
@@ -11979,13 +12003,13 @@
         <v>0</v>
       </c>
       <c r="BQ50" s="5">
-        <v>35511.281929665252</v>
+        <v>21828.103957633692</v>
       </c>
       <c r="BR50" s="6">
-        <v>105105.94155397339</v>
+        <v>87451.873152192289</v>
       </c>
       <c r="BS50" s="5">
-        <v>591095.90622654848</v>
+        <v>591095.90622654185</v>
       </c>
       <c r="BT50" s="5">
         <v>0</v>
@@ -11994,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="BV50" s="6">
-        <v>591095.90622654185</v>
+        <v>591095.90622654196</v>
       </c>
       <c r="BW50" s="1">
-        <v>591095.90622654185</v>
+        <v>591095.90622654196</v>
       </c>
     </row>
     <row r="51" spans="1:75" x14ac:dyDescent="0.3">
@@ -12137,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="AT51" s="5">
-        <v>6399.7410878893388</v>
+        <v>6539.5592757816321</v>
       </c>
       <c r="AU51" s="5">
         <v>0</v>
@@ -12164,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="BC51" s="5">
-        <v>467.81671908910516</v>
+        <v>468.39187923397697</v>
       </c>
       <c r="BD51" s="5">
         <v>71.536901201038788</v>
@@ -12173,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="BF51" s="5">
-        <v>1694.9425172109468</v>
+        <v>1741.2601195344398</v>
       </c>
       <c r="BG51" s="5">
         <v>11172.77498004118</v>
@@ -12185,16 +12209,16 @@
         <v>0</v>
       </c>
       <c r="BJ51" s="5">
-        <v>1972.1412765957448</v>
+        <v>1814.0904819544551</v>
       </c>
       <c r="BK51" s="5">
         <v>0</v>
       </c>
       <c r="BL51" s="6">
-        <v>25476.845551992599</v>
+        <v>25505.505707711967</v>
       </c>
       <c r="BM51" s="5">
-        <v>157525.33350990739</v>
+        <v>155790.48482569685</v>
       </c>
       <c r="BN51" s="5">
         <v>0</v>
@@ -12206,13 +12230,13 @@
         <v>0</v>
       </c>
       <c r="BQ51" s="5">
-        <v>294573.18325694057</v>
+        <v>296279.37178543175</v>
       </c>
       <c r="BR51" s="6">
-        <v>452098.51676684793</v>
+        <v>452069.85661112861</v>
       </c>
       <c r="BS51" s="5">
-        <v>477575.36231884052</v>
+        <v>477575.36231884058</v>
       </c>
       <c r="BT51" s="5">
         <v>0</v>
@@ -12382,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="5">
-        <v>9713.0376007240611</v>
+        <v>10300.504010395134</v>
       </c>
       <c r="BA52" s="5">
         <v>0</v>
@@ -12412,16 +12436,16 @@
         <v>24857.517232376766</v>
       </c>
       <c r="BJ52" s="5">
-        <v>10608.648846050621</v>
+        <v>10119.490693437589</v>
       </c>
       <c r="BK52" s="5">
         <v>0</v>
       </c>
       <c r="BL52" s="6">
-        <v>60088.716513237014</v>
+        <v>60187.024770295058</v>
       </c>
       <c r="BM52" s="5">
-        <v>766389.07960022672</v>
+        <v>759697.52038970031</v>
       </c>
       <c r="BN52" s="5">
         <v>0</v>
@@ -12433,10 +12457,10 @@
         <v>0</v>
       </c>
       <c r="BQ52" s="5">
-        <v>921828.87055320281</v>
+        <v>928422.12150667119</v>
       </c>
       <c r="BR52" s="6">
-        <v>1688217.9501534295</v>
+        <v>1688119.6418963715</v>
       </c>
       <c r="BS52" s="5">
         <v>1748306.6666666665</v>
@@ -12462,208 +12486,208 @@
         <v>53</v>
       </c>
       <c r="C53" s="5">
-        <v>14.923195548893768</v>
+        <v>13.313928303533013</v>
       </c>
       <c r="D53" s="5">
-        <v>1.1041590007521844</v>
+        <v>0.98242805689051949</v>
       </c>
       <c r="E53" s="5">
-        <v>0.76363151516721695</v>
+        <v>0.67846195770871209</v>
       </c>
       <c r="F53" s="5">
-        <v>4.0577758236929951</v>
+        <v>3.3338321931409429</v>
       </c>
       <c r="G53" s="5">
-        <v>14.615666376372053</v>
+        <v>12.268532924986548</v>
       </c>
       <c r="H53" s="5">
-        <v>2416.6866716740465</v>
+        <v>2151.3116690340212</v>
       </c>
       <c r="I53" s="5">
-        <v>262.55564325326662</v>
+        <v>231.48383281386467</v>
       </c>
       <c r="J53" s="5">
-        <v>128.56172492602491</v>
+        <v>114.56006422848809</v>
       </c>
       <c r="K53" s="5">
-        <v>5.8554701611232698</v>
+        <v>5.0215019328392652</v>
       </c>
       <c r="L53" s="5">
-        <v>188.41257768011084</v>
+        <v>165.99634194933287</v>
       </c>
       <c r="M53" s="5">
-        <v>9.1971286571261128</v>
+        <v>8.1251726876139063</v>
       </c>
       <c r="N53" s="5">
-        <v>0.23850688723037936</v>
+        <v>0.19460980504042219</v>
       </c>
       <c r="O53" s="5">
-        <v>118.12198500616844</v>
+        <v>105.32216843954735</v>
       </c>
       <c r="P53" s="5">
-        <v>156.30547989281209</v>
+        <v>134.72384004534868</v>
       </c>
       <c r="Q53" s="5">
-        <v>112.99409107329369</v>
+        <v>87.639336815516174</v>
       </c>
       <c r="R53" s="5">
-        <v>890.72752477696508</v>
+        <v>778.62958109879878</v>
       </c>
       <c r="S53" s="5">
-        <v>80.641993862591761</v>
+        <v>71.874095409179915</v>
       </c>
       <c r="T53" s="5">
-        <v>2580.496007942254</v>
+        <v>2217.5431825456649</v>
       </c>
       <c r="U53" s="5">
-        <v>235.73689250805845</v>
+        <v>191.18012681512812</v>
       </c>
       <c r="V53" s="5">
-        <v>188.88208076950096</v>
+        <v>152.54474592064167</v>
       </c>
       <c r="W53" s="5">
-        <v>237.50115201319264</v>
+        <v>210.12006858574787</v>
       </c>
       <c r="X53" s="5">
-        <v>367.39367390478878</v>
+        <v>319.12858769365215</v>
       </c>
       <c r="Y53" s="5">
-        <v>3381.6943041304157</v>
+        <v>3004.3735288904768</v>
       </c>
       <c r="Z53" s="5">
-        <v>268.50382953772765</v>
+        <v>237.41858725454782</v>
       </c>
       <c r="AA53" s="5">
-        <v>554.13842581473307</v>
+        <v>451.14443208905698</v>
       </c>
       <c r="AB53" s="5">
-        <v>1133.216818712895</v>
+        <v>883.87593254485887</v>
       </c>
       <c r="AC53" s="5">
-        <v>293.40919368225991</v>
+        <v>250.61814622504519</v>
       </c>
       <c r="AD53" s="5">
-        <v>150.30576161558605</v>
+        <v>112.55422653046661</v>
       </c>
       <c r="AE53" s="5">
-        <v>1488.4926276139292</v>
+        <v>1674.8682344772719</v>
       </c>
       <c r="AF53" s="5">
-        <v>215.99879497038884</v>
+        <v>178.29262091582621</v>
       </c>
       <c r="AG53" s="5">
-        <v>2789.2844450324701</v>
+        <v>3165.5247754390252</v>
       </c>
       <c r="AH53" s="5">
-        <v>3756.542177650605</v>
+        <v>3679.4887304822032</v>
       </c>
       <c r="AI53" s="5">
-        <v>148.49135596841765</v>
+        <v>121.86403221635261</v>
       </c>
       <c r="AJ53" s="5">
-        <v>1568.6457466326333</v>
+        <v>1370.0034003947499</v>
       </c>
       <c r="AK53" s="5">
-        <v>2236.9456818525764</v>
+        <v>1900.754710038196</v>
       </c>
       <c r="AL53" s="5">
-        <v>3629.259034674692</v>
+        <v>4006.9331362033581</v>
       </c>
       <c r="AM53" s="5">
-        <v>402.63860583952584</v>
+        <v>440.97721781942425</v>
       </c>
       <c r="AN53" s="5">
-        <v>97.63678353766943</v>
+        <v>87.993853273784282</v>
       </c>
       <c r="AO53" s="5">
-        <v>147.902892812022</v>
+        <v>128.75053187395508</v>
       </c>
       <c r="AP53" s="5">
-        <v>5895.8217925571798</v>
+        <v>6182.6135319259893</v>
       </c>
       <c r="AQ53" s="5">
-        <v>103.15779624333288</v>
+        <v>80.346336974258023</v>
       </c>
       <c r="AR53" s="5">
-        <v>23.177850448311407</v>
+        <v>18.785065760908616</v>
       </c>
       <c r="AS53" s="5">
-        <v>4146.6926874798401</v>
+        <v>3781.8395836718751</v>
       </c>
       <c r="AT53" s="5">
-        <v>39247.023201897573</v>
+        <v>40398.116462304693</v>
       </c>
       <c r="AU53" s="5">
-        <v>46629.658498956866</v>
+        <v>49210.525948315204</v>
       </c>
       <c r="AV53" s="5">
-        <v>7246.3293787928587</v>
+        <v>7475.1489990302234</v>
       </c>
       <c r="AW53" s="5">
-        <v>7647.2758368184195</v>
+        <v>7813.3893737789731</v>
       </c>
       <c r="AX53" s="5">
-        <v>35081.600255800447</v>
+        <v>38944.455211959445</v>
       </c>
       <c r="AY53" s="5">
-        <v>21109.253132997881</v>
+        <v>23092.221947156679</v>
       </c>
       <c r="AZ53" s="5">
-        <v>5947.4868244738918</v>
+        <v>6692.6474526321063</v>
       </c>
       <c r="BA53" s="5">
-        <v>617.55830594454665</v>
+        <v>520.61549936641131</v>
       </c>
       <c r="BB53" s="5">
-        <v>44934.116373439385</v>
+        <v>46375.836727884831</v>
       </c>
       <c r="BC53" s="5">
-        <v>12342.393419903665</v>
+        <v>13372.557764806175</v>
       </c>
       <c r="BD53" s="5">
-        <v>2118.888043490263</v>
+        <v>2284.0884287154477</v>
       </c>
       <c r="BE53" s="5">
-        <v>7719.6106466447709</v>
+        <v>7384.0926067749915</v>
       </c>
       <c r="BF53" s="5">
-        <v>8147.4083153641886</v>
+        <v>8024.632619607909</v>
       </c>
       <c r="BG53" s="5">
-        <v>87458.883809846549</v>
+        <v>86953.961189594542</v>
       </c>
       <c r="BH53" s="5">
-        <v>22043.584887348592</v>
+        <v>21863.140670495981</v>
       </c>
       <c r="BI53" s="5">
-        <v>28252.094908189771</v>
+        <v>29782.536830712525</v>
       </c>
       <c r="BJ53" s="5">
-        <v>14305.616671726033</v>
+        <v>15019.554623837157</v>
       </c>
       <c r="BK53" s="5">
         <v>0</v>
       </c>
       <c r="BL53" s="6">
-        <v>431296.51215169637</v>
+        <v>443942.51908123161</v>
       </c>
       <c r="BM53" s="5">
-        <v>390040.76374610793</v>
+        <v>367158.67283940723</v>
       </c>
       <c r="BN53" s="5">
         <v>17156.280000000002</v>
       </c>
       <c r="BO53" s="5">
-        <v>106043.89027470363</v>
+        <v>100292.42189743495</v>
       </c>
       <c r="BP53" s="5">
         <v>0</v>
       </c>
       <c r="BQ53" s="5">
-        <v>235478.68285975046</v>
+        <v>251466.23521418445</v>
       </c>
       <c r="BR53" s="6">
-        <v>748719.61688056204</v>
+        <v>736073.60995102674</v>
       </c>
       <c r="BS53" s="5">
         <v>1180016.1290322584</v>
@@ -12689,190 +12713,190 @@
         <v>54</v>
       </c>
       <c r="C54" s="5">
-        <v>33.054730168737322</v>
+        <v>29.880472158282352</v>
       </c>
       <c r="D54" s="5">
-        <v>17.58852847135293</v>
+        <v>18.26094997370015</v>
       </c>
       <c r="E54" s="5">
-        <v>11.16981957727088</v>
+        <v>11.578159443857691</v>
       </c>
       <c r="F54" s="5">
-        <v>248.01473638158268</v>
+        <v>257.94074094507698</v>
       </c>
       <c r="G54" s="5">
-        <v>245.18250331662199</v>
+        <v>253.53406813560201</v>
       </c>
       <c r="H54" s="5">
-        <v>15303.003250481343</v>
+        <v>15175.16801140298</v>
       </c>
       <c r="I54" s="5">
-        <v>3768.2034273379813</v>
+        <v>3874.2608340027773</v>
       </c>
       <c r="J54" s="5">
-        <v>1279.6461229486883</v>
+        <v>1293.1999866668245</v>
       </c>
       <c r="K54" s="5">
-        <v>142.83339715718401</v>
+        <v>148.24621144901232</v>
       </c>
       <c r="L54" s="5">
-        <v>1724.0952169446261</v>
+        <v>1726.1781779442003</v>
       </c>
       <c r="M54" s="5">
-        <v>278.70299919849549</v>
+        <v>285.45024090831635</v>
       </c>
       <c r="N54" s="5">
-        <v>19.581773369151424</v>
+        <v>20.192268025497203</v>
       </c>
       <c r="O54" s="5">
-        <v>1818.004742863382</v>
+        <v>1844.9019203697617</v>
       </c>
       <c r="P54" s="5">
-        <v>712.84046635021446</v>
+        <v>686.46409216456402</v>
       </c>
       <c r="Q54" s="5">
-        <v>419.64172364829091</v>
+        <v>397.21136304308163</v>
       </c>
       <c r="R54" s="5">
-        <v>7053.1022319756285</v>
+        <v>6473.5187703726688</v>
       </c>
       <c r="S54" s="5">
-        <v>187.25459605715537</v>
+        <v>170.02675052548551</v>
       </c>
       <c r="T54" s="5">
-        <v>8633.0985801739971</v>
+        <v>8088.7806281775283</v>
       </c>
       <c r="U54" s="5">
-        <v>3137.3830043181392</v>
+        <v>3156.2985166479402</v>
       </c>
       <c r="V54" s="5">
-        <v>847.62924672938743</v>
+        <v>811.6352428673755</v>
       </c>
       <c r="W54" s="5">
-        <v>759.88023097184157</v>
+        <v>730.8917883892741</v>
       </c>
       <c r="X54" s="5">
-        <v>4788.6625919852031</v>
+        <v>4822.9977012023983</v>
       </c>
       <c r="Y54" s="5">
-        <v>7623.4559886637999</v>
+        <v>7343.2878866118444</v>
       </c>
       <c r="Z54" s="5">
-        <v>1914.6070681321207</v>
+        <v>1910.0452122178438</v>
       </c>
       <c r="AA54" s="5">
-        <v>2581.8656000895526</v>
+        <v>2563.1982538620264</v>
       </c>
       <c r="AB54" s="5">
-        <v>5121.2666917526658</v>
+        <v>5095.3798384672009</v>
       </c>
       <c r="AC54" s="5">
-        <v>1702.5921356759191</v>
+        <v>1697.4172747397829</v>
       </c>
       <c r="AD54" s="5">
-        <v>1310.5854287801321</v>
+        <v>1326.5653173111853</v>
       </c>
       <c r="AE54" s="5">
-        <v>1485.9801960589552</v>
+        <v>1484.3028255914853</v>
       </c>
       <c r="AF54" s="5">
-        <v>1641.5799440481694</v>
+        <v>1638.3505911746936</v>
       </c>
       <c r="AG54" s="5">
-        <v>853.16964365404681</v>
+        <v>856.39746731573462</v>
       </c>
       <c r="AH54" s="5">
-        <v>1275.8662176314253</v>
+        <v>1237.0138399298098</v>
       </c>
       <c r="AI54" s="5">
-        <v>1624.1242441426348</v>
+        <v>1630.2788204680078</v>
       </c>
       <c r="AJ54" s="5">
-        <v>6004.5696258806702</v>
+        <v>5895.4323608965069</v>
       </c>
       <c r="AK54" s="5">
-        <v>10935.849608695369</v>
+        <v>10839.144794149941</v>
       </c>
       <c r="AL54" s="5">
-        <v>2728.9987728180595</v>
+        <v>2710.6414745864513</v>
       </c>
       <c r="AM54" s="5">
-        <v>444.49405589614378</v>
+        <v>446.44598372933865</v>
       </c>
       <c r="AN54" s="5">
-        <v>412.58433590233744</v>
+        <v>403.27502848238356</v>
       </c>
       <c r="AO54" s="5">
-        <v>465.01627853723755</v>
+        <v>452.37240131030723</v>
       </c>
       <c r="AP54" s="5">
-        <v>2486.3949012544895</v>
+        <v>2432.2081728657081</v>
       </c>
       <c r="AQ54" s="5">
-        <v>2780.036544271547</v>
+        <v>2809.5998826144705</v>
       </c>
       <c r="AR54" s="5">
-        <v>74.684855066488339</v>
+        <v>74.77480930983667</v>
       </c>
       <c r="AS54" s="5">
-        <v>54056.901169407749</v>
+        <v>54389.010867747325</v>
       </c>
       <c r="AT54" s="5">
-        <v>25815.000680975198</v>
+        <v>25675.789247879184</v>
       </c>
       <c r="AU54" s="5">
-        <v>26882.885276167544</v>
+        <v>26853.033962310194</v>
       </c>
       <c r="AV54" s="5">
-        <v>7847.2866868834553</v>
+        <v>7918.1405623805076</v>
       </c>
       <c r="AW54" s="5">
-        <v>8207.7147432786933</v>
+        <v>8278.6817085835555</v>
       </c>
       <c r="AX54" s="5">
-        <v>21479.143653513991</v>
+        <v>22266.82885285615</v>
       </c>
       <c r="AY54" s="5">
-        <v>7916.3087899104876</v>
+        <v>8041.9338846193305</v>
       </c>
       <c r="AZ54" s="5">
-        <v>3271.9582317121954</v>
+        <v>3330.3868726432611</v>
       </c>
       <c r="BA54" s="5">
-        <v>8290.9750294680744</v>
+        <v>8323.4561360477637</v>
       </c>
       <c r="BB54" s="5">
-        <v>12117.539500009842</v>
+        <v>12238.098443547371</v>
       </c>
       <c r="BC54" s="5">
-        <v>5321.5718033711573</v>
+        <v>5458.6305046026546</v>
       </c>
       <c r="BD54" s="5">
-        <v>1493.3947776031159</v>
+        <v>1541.3285426215853</v>
       </c>
       <c r="BE54" s="5">
-        <v>8916.5572705094073</v>
+        <v>8929.145934314578</v>
       </c>
       <c r="BF54" s="5">
-        <v>2209.2289040243227</v>
+        <v>2222.4190845632088</v>
       </c>
       <c r="BG54" s="5">
-        <v>10636.110565668108</v>
+        <v>10665.612805290821</v>
       </c>
       <c r="BH54" s="5">
-        <v>2344.199820100639</v>
+        <v>2326.2881378439138</v>
       </c>
       <c r="BI54" s="5">
-        <v>6562.8823279109774</v>
+        <v>6612.9423096214832</v>
       </c>
       <c r="BJ54" s="5">
-        <v>4025.8480404439565</v>
+        <v>4097.3263404131922</v>
       </c>
       <c r="BK54" s="5">
         <v>0</v>
       </c>
       <c r="BL54" s="6">
-        <v>322291.80332833692</v>
+        <v>322291.80332833686</v>
       </c>
       <c r="BM54" s="5">
         <v>113827.50835997488</v>
@@ -12893,7 +12917,7 @@
         <v>113827.50835997488</v>
       </c>
       <c r="BS54" s="5">
-        <v>436119.31168831181</v>
+        <v>436119.31168831175</v>
       </c>
       <c r="BT54" s="5">
         <v>0</v>
@@ -12916,190 +12940,190 @@
         <v>55</v>
       </c>
       <c r="C55" s="5">
-        <v>4.0500143488594649</v>
+        <v>3.9884822142039349</v>
       </c>
       <c r="D55" s="5">
-        <v>2.3438133418492928</v>
+        <v>2.3569497858492339</v>
       </c>
       <c r="E55" s="5">
-        <v>1.5542920742101107</v>
+        <v>1.5684252896568716</v>
       </c>
       <c r="F55" s="5">
-        <v>37.309752168131411</v>
+        <v>37.146912771422805</v>
       </c>
       <c r="G55" s="5">
-        <v>32.422846780656933</v>
+        <v>32.292493701235429</v>
       </c>
       <c r="H55" s="5">
-        <v>2113.9281128319103</v>
+        <v>2102.8883850653297</v>
       </c>
       <c r="I55" s="5">
-        <v>548.74677744022915</v>
+        <v>547.54503639206882</v>
       </c>
       <c r="J55" s="5">
-        <v>172.60274826503814</v>
+        <v>171.88431290198719</v>
       </c>
       <c r="K55" s="5">
-        <v>19.044817675396132</v>
+        <v>18.987099045796352</v>
       </c>
       <c r="L55" s="5">
-        <v>229.46139910846463</v>
+        <v>228.64897739907258</v>
       </c>
       <c r="M55" s="5">
-        <v>83.817913461419437</v>
+        <v>83.356119855845265</v>
       </c>
       <c r="N55" s="5">
-        <v>6.0705552366919289</v>
+        <v>6.0368447924016762</v>
       </c>
       <c r="O55" s="5">
-        <v>518.29943118495271</v>
+        <v>515.43386338161724</v>
       </c>
       <c r="P55" s="5">
-        <v>137.93789095902065</v>
+        <v>136.72994984058175</v>
       </c>
       <c r="Q55" s="5">
-        <v>73.344715085039667</v>
+        <v>72.768889688328898</v>
       </c>
       <c r="R55" s="5">
-        <v>2030.0627886093562</v>
+        <v>2008.5139379010095</v>
       </c>
       <c r="S55" s="5">
-        <v>44.104476133810216</v>
+        <v>43.142945478394068</v>
       </c>
       <c r="T55" s="5">
-        <v>2125.9932368920508</v>
+        <v>2033.129077586872</v>
       </c>
       <c r="U55" s="5">
-        <v>855.7133288906856</v>
+        <v>851.8388325448434</v>
       </c>
       <c r="V55" s="5">
-        <v>271.87773898026774</v>
+        <v>256.2582804773624</v>
       </c>
       <c r="W55" s="5">
-        <v>133.81870463942943</v>
+        <v>127.19012242747868</v>
       </c>
       <c r="X55" s="5">
-        <v>24.262271700105959</v>
+        <v>18.133005553241002</v>
       </c>
       <c r="Y55" s="5">
-        <v>169.21417155932667</v>
+        <v>156.22930500611184</v>
       </c>
       <c r="Z55" s="5">
-        <v>13.226666340242248</v>
+        <v>12.828176582388</v>
       </c>
       <c r="AA55" s="5">
-        <v>24.850501659037189</v>
+        <v>22.037048240227971</v>
       </c>
       <c r="AB55" s="5">
-        <v>54.669663153436851</v>
+        <v>40.535328802027998</v>
       </c>
       <c r="AC55" s="5">
-        <v>13.05268299773947</v>
+        <v>13.026848287173147</v>
       </c>
       <c r="AD55" s="5">
-        <v>7.2511854941209757</v>
+        <v>5.3170307910324484</v>
       </c>
       <c r="AE55" s="5">
-        <v>11.729362921689201</v>
+        <v>9.8410624434931737</v>
       </c>
       <c r="AF55" s="5">
-        <v>10.420407787444937</v>
+        <v>8.4306478608378796</v>
       </c>
       <c r="AG55" s="5">
-        <v>5.5033634511822003</v>
+        <v>4.2779775306631898</v>
       </c>
       <c r="AH55" s="5">
-        <v>275.18557262981676</v>
+        <v>270.85362539728982</v>
       </c>
       <c r="AI55" s="5">
-        <v>7.1636533079440605</v>
+        <v>6.1446908605760928</v>
       </c>
       <c r="AJ55" s="5">
-        <v>75.676016415711587</v>
+        <v>59.817482140409851</v>
       </c>
       <c r="AK55" s="5">
-        <v>136.96005502655669</v>
+        <v>105.34774574928689</v>
       </c>
       <c r="AL55" s="5">
-        <v>27.882847461341044</v>
+        <v>24.372222638594465</v>
       </c>
       <c r="AM55" s="5">
-        <v>2.9351408203016929</v>
+        <v>2.8959871115430933</v>
       </c>
       <c r="AN55" s="5">
         <v>4.71028136826635</v>
       </c>
       <c r="AO55" s="5">
-        <v>7.1352641400398165</v>
+        <v>6.0658949823280048</v>
       </c>
       <c r="AP55" s="5">
-        <v>36.333582053513773</v>
+        <v>27.947374722647382</v>
       </c>
       <c r="AQ55" s="5">
-        <v>657.3396394154372</v>
+        <v>654.50936368865598</v>
       </c>
       <c r="AR55" s="5">
-        <v>1.0483418940300953</v>
+        <v>0.9469804415481955</v>
       </c>
       <c r="AS55" s="5">
         <v>200.0479686853615</v>
       </c>
       <c r="AT55" s="5">
-        <v>5320.8606474642484</v>
+        <v>5301.3141616042558</v>
       </c>
       <c r="AU55" s="5">
-        <v>5556.2879256915612</v>
+        <v>5570.5227430622308</v>
       </c>
       <c r="AV55" s="5">
-        <v>6051.3783309913615</v>
+        <v>6026.3539197982236</v>
       </c>
       <c r="AW55" s="5">
-        <v>7605.7313373746001</v>
+        <v>7643.4497253124919</v>
       </c>
       <c r="AX55" s="5">
-        <v>20383.552660409059</v>
+        <v>20505.968761556534</v>
       </c>
       <c r="AY55" s="5">
-        <v>1985.8068729207314</v>
+        <v>2054.9171191919822</v>
       </c>
       <c r="AZ55" s="5">
-        <v>6.5197291931795869</v>
+        <v>5.5306997753130158</v>
       </c>
       <c r="BA55" s="5">
-        <v>38.499181795546605</v>
+        <v>31.9431625779604</v>
       </c>
       <c r="BB55" s="5">
-        <v>2410.7046216439931</v>
+        <v>2528.5805327988051</v>
       </c>
       <c r="BC55" s="5">
-        <v>1906.7190046725393</v>
+        <v>1906.7190046725391</v>
       </c>
       <c r="BD55" s="5">
-        <v>1178.7692179209173</v>
+        <v>1183.9748875637579</v>
       </c>
       <c r="BE55" s="5">
-        <v>2049.3991849079675</v>
+        <v>2061.2941248826683</v>
       </c>
       <c r="BF55" s="5">
-        <v>389.64400648972185</v>
+        <v>395.62671322903515</v>
       </c>
       <c r="BG55" s="5">
-        <v>251.096548438144</v>
+        <v>224.51907513686254</v>
       </c>
       <c r="BH55" s="5">
-        <v>81.974434852613115</v>
+        <v>61.857418356842167</v>
       </c>
       <c r="BI55" s="5">
-        <v>90.976233804145863</v>
+        <v>76.456418917497331</v>
       </c>
       <c r="BJ55" s="5">
-        <v>818.14216938171785</v>
+        <v>820.11564647736827</v>
       </c>
       <c r="BK55" s="5">
         <v>0</v>
       </c>
       <c r="BL55" s="6">
-        <v>67335.166102342162</v>
+        <v>67335.166102339441</v>
       </c>
       <c r="BM55" s="5">
         <v>35012.709141325293</v>
@@ -13120,7 +13144,7 @@
         <v>35012.709141325293</v>
       </c>
       <c r="BS55" s="5">
-        <v>102347.87524366745</v>
+        <v>102347.87524366473</v>
       </c>
       <c r="BT55" s="5">
         <v>0</v>
@@ -13143,55 +13167,55 @@
         <v>56</v>
       </c>
       <c r="C56" s="5">
-        <v>7.2283012935025592</v>
+        <v>7.8503013837183246</v>
       </c>
       <c r="D56" s="5">
-        <v>0.53785470416961467</v>
+        <v>0.57867582627739278</v>
       </c>
       <c r="E56" s="5">
-        <v>0.37044283958053242</v>
+        <v>0.39941105868854293</v>
       </c>
       <c r="F56" s="5">
-        <v>1.7867154647700052</v>
+        <v>1.9458550330759075</v>
       </c>
       <c r="G56" s="5">
-        <v>6.4767962451888712</v>
+        <v>7.0537362048891437</v>
       </c>
       <c r="H56" s="5">
-        <v>1165.4399049255676</v>
+        <v>1265.6004486801712</v>
       </c>
       <c r="I56" s="5">
-        <v>125.495035010838</v>
+        <v>135.88552185829209</v>
       </c>
       <c r="J56" s="5">
-        <v>62.150164051242157</v>
+        <v>67.498690596275807</v>
       </c>
       <c r="K56" s="5">
-        <v>2.6885510359341915</v>
+        <v>2.9187297169174506</v>
       </c>
       <c r="L56" s="5">
-        <v>89.978395460768766</v>
+        <v>96.954098943544821</v>
       </c>
       <c r="M56" s="5">
-        <v>4.4921567040156392</v>
+        <v>4.777264349948978</v>
       </c>
       <c r="N56" s="5">
-        <v>0.11373283716879116</v>
+        <v>0.11387968725963182</v>
       </c>
       <c r="O56" s="5">
-        <v>57.625006191704401</v>
+        <v>62.084580318756224</v>
       </c>
       <c r="P56" s="5">
-        <v>69.205677051948811</v>
+        <v>75.254177232187999</v>
       </c>
       <c r="Q56" s="5">
-        <v>37.821382463878365</v>
+        <v>41.02392939258705</v>
       </c>
       <c r="R56" s="5">
-        <v>408.97008595414633</v>
+        <v>444.06259731979907</v>
       </c>
       <c r="S56" s="5">
-        <v>38.733590532612176</v>
+        <v>42.155888409734622</v>
       </c>
       <c r="T56" s="5">
         <v>1097.8223102185968</v>
@@ -13209,10 +13233,10 @@
         <v>184.3912716365956</v>
       </c>
       <c r="Y56" s="5">
-        <v>1560.0943166346863</v>
+        <v>1647.6241570941461</v>
       </c>
       <c r="Z56" s="5">
-        <v>129.97010994450611</v>
+        <v>137.62514202163996</v>
       </c>
       <c r="AA56" s="5">
         <v>233.30683569364638</v>
@@ -13221,13 +13245,13 @@
         <v>415.48494854101125</v>
       </c>
       <c r="AC56" s="5">
-        <v>138.05285319781203</v>
+        <v>140.31963839131734</v>
       </c>
       <c r="AD56" s="5">
         <v>55.108414029011293</v>
       </c>
       <c r="AE56" s="5">
-        <v>1185.6763500091631</v>
+        <v>1139.6716571337647</v>
       </c>
       <c r="AF56" s="5">
         <v>79.194243088558949</v>
@@ -13263,7 +13287,7 @@
         <v>276.13223859539647</v>
       </c>
       <c r="AQ56" s="5">
-        <v>41.572558208069992</v>
+        <v>44.701801414290706</v>
       </c>
       <c r="AR56" s="5">
         <v>10.084934884556823</v>
@@ -13272,10 +13296,10 @@
         <v>1521.1233524766626</v>
       </c>
       <c r="AT56" s="5">
-        <v>26915.708370955599</v>
+        <v>26835.478544962258</v>
       </c>
       <c r="AU56" s="5">
-        <v>44590.944714955702</v>
+        <v>44052.293039847063</v>
       </c>
       <c r="AV56" s="5">
         <v>224.44916356200534</v>
@@ -13287,46 +13311,46 @@
         <v>0</v>
       </c>
       <c r="AY56" s="5">
-        <v>11644.261864983095</v>
+        <v>11443.306636616682</v>
       </c>
       <c r="AZ56" s="5">
-        <v>7176.6972956085428</v>
+        <v>6931.2785506738865</v>
       </c>
       <c r="BA56" s="5">
-        <v>15451.422795452798</v>
+        <v>15155.5498917398</v>
       </c>
       <c r="BB56" s="5">
-        <v>18055.332288647893</v>
+        <v>18012.893086797703</v>
       </c>
       <c r="BC56" s="5">
-        <v>6092.8434813505501</v>
+        <v>6057.3681667336659</v>
       </c>
       <c r="BD56" s="5">
-        <v>1043.4172501240882</v>
+        <v>1045.6203897261407</v>
       </c>
       <c r="BE56" s="5">
-        <v>4199.0991351110742</v>
+        <v>4085.9574492480101</v>
       </c>
       <c r="BF56" s="5">
-        <v>3616.0342941351892</v>
+        <v>3655.2901479887678</v>
       </c>
       <c r="BG56" s="5">
-        <v>37489.817064371702</v>
+        <v>38369.343478846407</v>
       </c>
       <c r="BH56" s="5">
-        <v>10332.773291721389</v>
+        <v>10539.354834402297</v>
       </c>
       <c r="BI56" s="5">
-        <v>14137.422939481865</v>
+        <v>14151.284048466718</v>
       </c>
       <c r="BJ56" s="5">
-        <v>10294.290087844736</v>
+        <v>10473.426407388803</v>
       </c>
       <c r="BK56" s="5">
         <v>0</v>
       </c>
       <c r="BL56" s="6">
-        <v>223073.30874578131</v>
+        <v>223073.30874578125</v>
       </c>
       <c r="BM56" s="5">
         <v>785507.03875837079</v>
@@ -13347,19 +13371,19 @@
         <v>811183.10151062906</v>
       </c>
       <c r="BS56" s="5">
+        <v>1034256.4102564103</v>
+      </c>
+      <c r="BT56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV56" s="6">
         <v>1034256.4102564104</v>
       </c>
-      <c r="BT56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV56" s="6">
-        <v>1034256.4102564103</v>
-      </c>
       <c r="BW56" s="1">
-        <v>1034256.4102564103</v>
+        <v>1034256.4102564104</v>
       </c>
     </row>
     <row r="57" spans="1:75" x14ac:dyDescent="0.3">
@@ -13370,193 +13394,193 @@
         <v>57</v>
       </c>
       <c r="C57" s="5">
-        <v>7.0418779661477293</v>
+        <v>7.0369591045073676</v>
       </c>
       <c r="D57" s="5">
-        <v>3.2361122241495686</v>
+        <v>3.2380084960864348</v>
       </c>
       <c r="E57" s="5">
-        <v>2.123024158907401</v>
+        <v>2.1241892138216225</v>
       </c>
       <c r="F57" s="5">
-        <v>51.203258872495148</v>
+        <v>51.244986995946704</v>
       </c>
       <c r="G57" s="5">
-        <v>48.681953347107381</v>
+        <v>48.785999496918627</v>
       </c>
       <c r="H57" s="5">
-        <v>3107.1616507419653</v>
+        <v>3106.9773487029597</v>
       </c>
       <c r="I57" s="5">
-        <v>764.33078182763848</v>
+        <v>764.43148504615101</v>
       </c>
       <c r="J57" s="5">
-        <v>250.08889269009254</v>
+        <v>250.10866860425313</v>
       </c>
       <c r="K57" s="5">
-        <v>26.221636465065973</v>
+        <v>26.225637570189143</v>
       </c>
       <c r="L57" s="5">
-        <v>332.11824347684245</v>
+        <v>332.09522493535877</v>
       </c>
       <c r="M57" s="5">
-        <v>58.445682653858917</v>
+        <v>58.472415860970699</v>
       </c>
       <c r="N57" s="5">
-        <v>4.2359110102046245</v>
+        <v>4.2444525082681004</v>
       </c>
       <c r="O57" s="5">
-        <v>240.36630736208909</v>
+        <v>240.54358450958432</v>
       </c>
       <c r="P57" s="5">
-        <v>374.46372650550023</v>
+        <v>372.98052555748461</v>
       </c>
       <c r="Q57" s="5">
-        <v>186.19708261783418</v>
+        <v>185.22861127969566</v>
       </c>
       <c r="R57" s="5">
-        <v>1021.4769718596594</v>
+        <v>1018.9993508746072</v>
       </c>
       <c r="S57" s="5">
-        <v>42.42912304552376</v>
+        <v>42.35861506827154</v>
       </c>
       <c r="T57" s="5">
-        <v>4707.5986852521228</v>
+        <v>4629.6198801827031</v>
       </c>
       <c r="U57" s="5">
-        <v>971.05854440906433</v>
+        <v>970.78356031139924</v>
       </c>
       <c r="V57" s="5">
-        <v>391.01079521319161</v>
+        <v>385.88422616335941</v>
       </c>
       <c r="W57" s="5">
-        <v>450.11900586396058</v>
+        <v>444.17101199029787</v>
       </c>
       <c r="X57" s="5">
-        <v>970.44081062087082</v>
+        <v>970.63872172268805</v>
       </c>
       <c r="Y57" s="5">
-        <v>1904.2323625638896</v>
+        <v>1902.4705379088871</v>
       </c>
       <c r="Z57" s="5">
-        <v>526.00646846853704</v>
+        <v>525.98452883552068</v>
       </c>
       <c r="AA57" s="5">
-        <v>538.04987886729714</v>
+        <v>537.75501323139326</v>
       </c>
       <c r="AB57" s="5">
-        <v>1366.4338356739624</v>
+        <v>1365.3055267695945</v>
       </c>
       <c r="AC57" s="5">
-        <v>618.83100857456282</v>
+        <v>618.75147649362225</v>
       </c>
       <c r="AD57" s="5">
-        <v>407.19740657367481</v>
+        <v>407.40542740112511</v>
       </c>
       <c r="AE57" s="5">
-        <v>309.35740764152541</v>
+        <v>309.21138090598168</v>
       </c>
       <c r="AF57" s="5">
-        <v>348.85473927474453</v>
+        <v>346.49474758603657</v>
       </c>
       <c r="AG57" s="5">
-        <v>212.90967584780037</v>
+        <v>212.89283048021034</v>
       </c>
       <c r="AH57" s="5">
-        <v>809.48672861957868</v>
+        <v>806.04809133273147</v>
       </c>
       <c r="AI57" s="5">
-        <v>486.5384553253254</v>
+        <v>486.54043433167783</v>
       </c>
       <c r="AJ57" s="5">
-        <v>2113.438764372459</v>
+        <v>2110.4959038200468</v>
       </c>
       <c r="AK57" s="5">
-        <v>3819.6586635970643</v>
+        <v>3815.3257813640398</v>
       </c>
       <c r="AL57" s="5">
-        <v>1370.9641534135483</v>
+        <v>1368.6378534965027</v>
       </c>
       <c r="AM57" s="5">
-        <v>144.45461178205122</v>
+        <v>144.41727601117191</v>
       </c>
       <c r="AN57" s="5">
-        <v>87.541775564005192</v>
+        <v>87.394688993892004</v>
       </c>
       <c r="AO57" s="5">
-        <v>153.3085310996934</v>
+        <v>152.54393469556899</v>
       </c>
       <c r="AP57" s="5">
-        <v>1551.6837509730894</v>
+        <v>1546.0534557025121</v>
       </c>
       <c r="AQ57" s="5">
-        <v>945.98560942540666</v>
+        <v>946.97933146743389</v>
       </c>
       <c r="AR57" s="5">
-        <v>56.585984852348766</v>
+        <v>56.556685125538031</v>
       </c>
       <c r="AS57" s="5">
-        <v>20519.053109952438</v>
+        <v>20554.57579904548</v>
       </c>
       <c r="AT57" s="5">
-        <v>5564.7535280441571</v>
+        <v>5554.5994293559597</v>
       </c>
       <c r="AU57" s="5">
-        <v>5357.3642329376171</v>
+        <v>5348.1091860162232</v>
       </c>
       <c r="AV57" s="5">
-        <v>1839.3302360835921</v>
+        <v>1843.3594499114643</v>
       </c>
       <c r="AW57" s="5">
-        <v>2014.8977508958717</v>
+        <v>2021.7793086129905</v>
       </c>
       <c r="AX57" s="5">
-        <v>5612.5702285975458</v>
+        <v>5668.9546080199752</v>
       </c>
       <c r="AY57" s="5">
-        <v>2452.7470207188076</v>
+        <v>2465.2482716245336</v>
       </c>
       <c r="AZ57" s="5">
-        <v>956.98554813556837</v>
+        <v>957.80149752877014</v>
       </c>
       <c r="BA57" s="5">
-        <v>1120.7559656238736</v>
+        <v>1120.7405058257841</v>
       </c>
       <c r="BB57" s="5">
-        <v>6779.8844608403233</v>
+        <v>6812.465781034507</v>
       </c>
       <c r="BC57" s="5">
-        <v>1756.0242612756203</v>
+        <v>1769.0476810634273</v>
       </c>
       <c r="BD57" s="5">
-        <v>407.20144126909878</v>
+        <v>408.7118478328436</v>
       </c>
       <c r="BE57" s="5">
-        <v>4902.1546594028587</v>
+        <v>4896.6625787001722</v>
       </c>
       <c r="BF57" s="5">
-        <v>1068.78944805231</v>
+        <v>1068.3788916691733</v>
       </c>
       <c r="BG57" s="5">
-        <v>17078.974298434303</v>
+        <v>17066.158081801717</v>
       </c>
       <c r="BH57" s="5">
-        <v>3116.4727550788821</v>
+        <v>3103.2249839144679</v>
       </c>
       <c r="BI57" s="5">
-        <v>6486.3352659472466</v>
+        <v>6491.036195427092</v>
       </c>
       <c r="BJ57" s="5">
-        <v>2469.0190014093087</v>
+        <v>2470.5706358607049</v>
       </c>
       <c r="BK57" s="5">
         <v>0</v>
       </c>
       <c r="BL57" s="6">
-        <v>121284.88310339427</v>
+        <v>121284.8831033943</v>
       </c>
       <c r="BM57" s="5">
-        <v>20260.432751226668</v>
+        <v>20260.432751226665</v>
       </c>
       <c r="BN57" s="5">
         <v>2685.253483967841</v>
@@ -13571,10 +13595,10 @@
         <v>0</v>
       </c>
       <c r="BR57" s="6">
-        <v>46538.836061691203</v>
+        <v>46538.836061691196</v>
       </c>
       <c r="BS57" s="5">
-        <v>167823.71916508547</v>
+        <v>167823.71916508549</v>
       </c>
       <c r="BT57" s="5">
         <v>0</v>
@@ -13875,40 +13899,40 @@
         <v>0</v>
       </c>
       <c r="T59" s="5">
-        <v>3976.7402964271901</v>
+        <v>3996.3524082892695</v>
       </c>
       <c r="U59" s="5">
-        <v>371.10338441996868</v>
+        <v>367.67634254102433</v>
       </c>
       <c r="V59" s="5">
-        <v>269.05138998184282</v>
+        <v>269.83214184153508</v>
       </c>
       <c r="W59" s="5">
         <v>290.80851244775783</v>
       </c>
       <c r="X59" s="5">
-        <v>791.82904404536202</v>
+        <v>784.13854062969506</v>
       </c>
       <c r="Y59" s="5">
-        <v>7848.3351162083745</v>
+        <v>7780.7372675139131</v>
       </c>
       <c r="Z59" s="5">
-        <v>655.27222574286293</v>
+        <v>649.1479931074216</v>
       </c>
       <c r="AA59" s="5">
-        <v>909.38502563688098</v>
+        <v>901.07542032665026</v>
       </c>
       <c r="AB59" s="5">
-        <v>1624.1297598961892</v>
+        <v>1610.5120482975212</v>
       </c>
       <c r="AC59" s="5">
-        <v>547.00639334979246</v>
+        <v>541.97810504574443</v>
       </c>
       <c r="AD59" s="5">
-        <v>214.68543414308053</v>
+        <v>212.65535299149721</v>
       </c>
       <c r="AE59" s="5">
-        <v>295.4934796089496</v>
+        <v>293.09835974353751</v>
       </c>
       <c r="AF59" s="5">
         <v>0</v>
@@ -13917,34 +13941,34 @@
         <v>0</v>
       </c>
       <c r="AH59" s="5">
-        <v>1034.5457604860972</v>
+        <v>1040.052168058683</v>
       </c>
       <c r="AI59" s="5">
-        <v>212.77499751609525</v>
+        <v>210.78594858989965</v>
       </c>
       <c r="AJ59" s="5">
-        <v>2326.0613067576483</v>
+        <v>2343.8264513838094</v>
       </c>
       <c r="AK59" s="5">
-        <v>4150.7121584465804</v>
+        <v>4151.5987529222266</v>
       </c>
       <c r="AL59" s="5">
         <v>762.48630191300788</v>
       </c>
       <c r="AM59" s="5">
-        <v>75.335893470923097</v>
+        <v>74.752461280691008</v>
       </c>
       <c r="AN59" s="5">
-        <v>119.14319424520502</v>
+        <v>118.66323459464026</v>
       </c>
       <c r="AO59" s="5">
-        <v>147.08689441523552</v>
+        <v>146.70354227393122</v>
       </c>
       <c r="AP59" s="5">
-        <v>922.55304405659786</v>
+        <v>922.08818093038985</v>
       </c>
       <c r="AQ59" s="5">
-        <v>175.6934926775335</v>
+        <v>173.46388511859658</v>
       </c>
       <c r="AR59" s="5">
         <v>0</v>
@@ -13953,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="AT59" s="5">
-        <v>4159.9120118996407</v>
+        <v>4166.7322360125363</v>
       </c>
       <c r="AU59" s="5">
-        <v>3671.8639861125052</v>
+        <v>3678.4559244631637</v>
       </c>
       <c r="AV59" s="5">
         <v>874.91552530647812</v>
@@ -13971,13 +13995,13 @@
         <v>608.65119486257879</v>
       </c>
       <c r="AZ59" s="5">
-        <v>201.50542791282845</v>
+        <v>194.85420071494727</v>
       </c>
       <c r="BA59" s="5">
-        <v>1397.8003080008687</v>
+        <v>1384.8712053076595</v>
       </c>
       <c r="BB59" s="5">
-        <v>1458.67007518988</v>
+        <v>1420.427462238983</v>
       </c>
       <c r="BC59" s="5">
         <v>312.4106719042116</v>
@@ -14007,13 +14031,13 @@
         <v>0</v>
       </c>
       <c r="BL59" s="6">
-        <v>51722.185181389395</v>
+        <v>51599.974714959222</v>
       </c>
       <c r="BM59" s="5">
-        <v>456139.90214292542</v>
+        <v>454971.6714980657</v>
       </c>
       <c r="BN59" s="5">
-        <v>418512.90869192546</v>
+        <v>419803.3482431157</v>
       </c>
       <c r="BO59" s="5">
         <v>0</v>
@@ -14022,13 +14046,13 @@
         <v>0</v>
       </c>
       <c r="BQ59" s="5">
-        <v>0</v>
+        <v>7.1054273576010019E-12</v>
       </c>
       <c r="BR59" s="6">
-        <v>874652.81083485088</v>
+        <v>874775.0197411814</v>
       </c>
       <c r="BS59" s="5">
-        <v>926374.99601624033</v>
+        <v>926374.99445614067</v>
       </c>
       <c r="BT59" s="5">
         <v>0</v>
@@ -14237,10 +14261,10 @@
         <v>51201.951219512186</v>
       </c>
       <c r="BM60" s="5">
-        <v>547256.95930413087</v>
+        <v>846664.12496104499</v>
       </c>
       <c r="BN60" s="5">
-        <v>146818.0511481775</v>
+        <v>146593.62110686285</v>
       </c>
       <c r="BO60" s="5">
         <v>0</v>
@@ -14249,7 +14273,7 @@
         <v>0</v>
       </c>
       <c r="BQ60" s="5">
-        <v>473655.96515744773</v>
+        <v>174473.22954184824</v>
       </c>
       <c r="BR60" s="6">
         <v>1167730.9756097561</v>
@@ -14264,10 +14288,10 @@
         <v>0</v>
       </c>
       <c r="BV60" s="6">
-        <v>1218932.9268292685</v>
+        <v>1218932.9268292682</v>
       </c>
       <c r="BW60" s="1">
-        <v>1218932.9268292685</v>
+        <v>1218932.9268292682</v>
       </c>
     </row>
     <row r="61" spans="1:75" x14ac:dyDescent="0.3">
@@ -14320,7 +14344,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="5">
-        <v>57.05842648434016</v>
+        <v>50.70774873256628</v>
       </c>
       <c r="R61" s="5">
         <v>0</v>
@@ -14329,145 +14353,145 @@
         <v>0</v>
       </c>
       <c r="T61" s="5">
-        <v>2265.8973896700618</v>
+        <v>2117.8468488404087</v>
       </c>
       <c r="U61" s="5">
-        <v>204.53989730636755</v>
+        <v>187.63916781266897</v>
       </c>
       <c r="V61" s="5">
-        <v>128.54479407812457</v>
+        <v>124.29230627876075</v>
       </c>
       <c r="W61" s="5">
-        <v>130.87052700244541</v>
+        <v>130.13951379813003</v>
       </c>
       <c r="X61" s="5">
-        <v>414.09689165078981</v>
+        <v>391.62238116662127</v>
       </c>
       <c r="Y61" s="5">
-        <v>3826.9567572609044</v>
+        <v>3818.7489854651158</v>
       </c>
       <c r="Z61" s="5">
-        <v>319.37308207842995</v>
+        <v>318.68305747410341</v>
       </c>
       <c r="AA61" s="5">
-        <v>445.91951069901211</v>
+        <v>443.2163856741534</v>
       </c>
       <c r="AB61" s="5">
-        <v>793.61747203368304</v>
+        <v>788.95556509307823</v>
       </c>
       <c r="AC61" s="5">
-        <v>266.14968411982312</v>
+        <v>265.73368246667133</v>
       </c>
       <c r="AD61" s="5">
-        <v>116.17157969690852</v>
+        <v>106.631935409482</v>
       </c>
       <c r="AE61" s="5">
-        <v>175.42315354885221</v>
+        <v>154.63210576557734</v>
       </c>
       <c r="AF61" s="5">
-        <v>151.35136293937649</v>
+        <v>150.38990854865264</v>
       </c>
       <c r="AG61" s="5">
-        <v>68.751044133588948</v>
+        <v>67.521384890320803</v>
       </c>
       <c r="AH61" s="5">
-        <v>530.65603149665083</v>
+        <v>516.79565771048374</v>
       </c>
       <c r="AI61" s="5">
-        <v>134.97880710161908</v>
+        <v>112.66299700698906</v>
       </c>
       <c r="AJ61" s="5">
-        <v>1207.8784411628519</v>
+        <v>1140.0737471454574</v>
       </c>
       <c r="AK61" s="5">
-        <v>2021.4859905549486</v>
+        <v>1991.0641424307298</v>
       </c>
       <c r="AL61" s="5">
-        <v>344.43141731258748</v>
+        <v>341.26696422390529</v>
       </c>
       <c r="AM61" s="5">
-        <v>36.312571776798279</v>
+        <v>35.907389449216225</v>
       </c>
       <c r="AN61" s="5">
-        <v>157.39658272463942</v>
+        <v>154.80693201391512</v>
       </c>
       <c r="AO61" s="5">
-        <v>73.910764130456386</v>
+        <v>72.062520095310504</v>
       </c>
       <c r="AP61" s="5">
-        <v>507.03602175942189</v>
+        <v>474.02740154973003</v>
       </c>
       <c r="AQ61" s="5">
-        <v>1596.8206317462536</v>
+        <v>1564.9745344839591</v>
       </c>
       <c r="AR61" s="5">
-        <v>83.236667548600366</v>
+        <v>82.682039192948338</v>
       </c>
       <c r="AS61" s="5">
-        <v>3952.636978066766</v>
+        <v>3929.6106860662808</v>
       </c>
       <c r="AT61" s="5">
-        <v>7347.0062046389721</v>
+        <v>7338.3394358371352</v>
       </c>
       <c r="AU61" s="5">
-        <v>9092.2992325929954</v>
+        <v>9069.4050238039363</v>
       </c>
       <c r="AV61" s="5">
-        <v>2870.3988912589962</v>
+        <v>2970.6319868682735</v>
       </c>
       <c r="AW61" s="5">
-        <v>2949.1695389307765</v>
+        <v>3037.49256241893</v>
       </c>
       <c r="AX61" s="5">
-        <v>8199.5004740980385</v>
+        <v>8403.5208224902362</v>
       </c>
       <c r="AY61" s="5">
-        <v>5394.8838903925898</v>
+        <v>5583.0737253899215</v>
       </c>
       <c r="AZ61" s="5">
-        <v>2022.5679259411042</v>
+        <v>1979.3848670969771</v>
       </c>
       <c r="BA61" s="5">
-        <v>1445.2665853189553</v>
+        <v>1410.5006125666018</v>
       </c>
       <c r="BB61" s="5">
-        <v>9373.3408713537301</v>
+        <v>9961.3308248943376</v>
       </c>
       <c r="BC61" s="5">
-        <v>2168.6043431197927</v>
+        <v>2121.9711136036126</v>
       </c>
       <c r="BD61" s="5">
-        <v>661.64732884348223</v>
+        <v>660.25622485667225</v>
       </c>
       <c r="BE61" s="5">
-        <v>5443.1047658985126</v>
+        <v>5405.073320004105</v>
       </c>
       <c r="BF61" s="5">
-        <v>1536.7604657901559</v>
+        <v>1528.4377111996721</v>
       </c>
       <c r="BG61" s="5">
-        <v>44845.973995568595</v>
+        <v>44301.999221562168</v>
       </c>
       <c r="BH61" s="5">
-        <v>11409.529012471519</v>
+        <v>11264.09172936844</v>
       </c>
       <c r="BI61" s="5">
-        <v>16961.87668006105</v>
+        <v>16869.431869545428</v>
       </c>
       <c r="BJ61" s="5">
-        <v>7861.0698428899395</v>
+        <v>7946.0267589462483</v>
       </c>
       <c r="BK61" s="5">
         <v>0</v>
       </c>
       <c r="BL61" s="6">
-        <v>159594.5025272535</v>
+        <v>159383.6637992379</v>
       </c>
       <c r="BM61" s="5">
-        <v>216350.34843653152</v>
+        <v>216317.09986711125</v>
       </c>
       <c r="BN61" s="5">
-        <v>23691.016302523993</v>
+        <v>23681.330239153569</v>
       </c>
       <c r="BO61" s="5">
         <v>0</v>
@@ -14476,13 +14500,13 @@
         <v>0</v>
       </c>
       <c r="BQ61" s="5">
-        <v>3325.9426153392301</v>
+        <v>3579.7159761455041</v>
       </c>
       <c r="BR61" s="6">
-        <v>243367.30735439475</v>
+        <v>243578.14608241033</v>
       </c>
       <c r="BS61" s="5">
-        <v>402961.80988164828</v>
+        <v>402961.80988164822</v>
       </c>
       <c r="BT61" s="5">
         <v>0</v>
@@ -14491,10 +14515,10 @@
         <v>0</v>
       </c>
       <c r="BV61" s="6">
-        <v>402961.80988164811</v>
+        <v>402961.80988164805</v>
       </c>
       <c r="BW61" s="1">
-        <v>402961.80988164811</v>
+        <v>402961.80988164805</v>
       </c>
     </row>
     <row r="62" spans="1:75" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14690,253 +14714,230 @@
       <c r="BL62" s="6">
         <v>0</v>
       </c>
-      <c r="BM62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BN62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BO62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BP62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BQ62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BR62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BS62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BT62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BU62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BV62" s="6">
-        <v>0</v>
-      </c>
-      <c r="BW62" s="1">
-        <v>0</v>
-      </c>
+      <c r="BM62" s="6"/>
+      <c r="BN62" s="6"/>
+      <c r="BO62" s="6"/>
+      <c r="BP62" s="6"/>
+      <c r="BQ62" s="6"/>
+      <c r="BR62" s="6"/>
+      <c r="BS62" s="6"/>
+      <c r="BT62" s="6"/>
+      <c r="BU62" s="6"/>
+      <c r="BV62" s="6"/>
     </row>
     <row r="63" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
-        <v>190</v>
+      <c r="A63" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="5">
-        <v>1661.1769823919446</v>
+        <v>1728.6741918102614</v>
       </c>
       <c r="D63" s="5">
-        <v>293.08805242682519</v>
+        <v>294.60656419466727</v>
       </c>
       <c r="E63" s="5">
-        <v>202.18217280609511</v>
+        <v>200.31362898717182</v>
       </c>
       <c r="F63" s="5">
-        <v>4228.0470389815218</v>
+        <v>4203.2927061877872</v>
       </c>
       <c r="G63" s="5">
-        <v>4861.559841410749</v>
+        <v>4834.3393069399253</v>
       </c>
       <c r="H63" s="5">
-        <v>488082.5371917311</v>
+        <v>492362.23062133678</v>
       </c>
       <c r="I63" s="5">
-        <v>88647.19818279687</v>
+        <v>90759.246233512386</v>
       </c>
       <c r="J63" s="5">
-        <v>32841.943941915502</v>
+        <v>33126.300994995807</v>
       </c>
       <c r="K63" s="5">
-        <v>2742.5765496477625</v>
+        <v>2772.8590995375102</v>
       </c>
       <c r="L63" s="5">
-        <v>44912.867320849546</v>
+        <v>45680.373367968932</v>
       </c>
       <c r="M63" s="5">
-        <v>9223.5896121817786</v>
+        <v>10084.840379785379</v>
       </c>
       <c r="N63" s="5">
-        <v>610.25007896369823</v>
+        <v>674.53051310304545</v>
       </c>
       <c r="O63" s="5">
-        <v>77299.813236268412</v>
+        <v>81798.035967798205</v>
       </c>
       <c r="P63" s="5">
-        <v>12457.238182533305</v>
+        <v>12335.740874195659</v>
       </c>
       <c r="Q63" s="5">
-        <v>9000.365031382913</v>
+        <v>9000.6648801527335</v>
       </c>
       <c r="R63" s="5">
-        <v>163457.03874030727</v>
+        <v>168365.73968443985</v>
       </c>
       <c r="S63" s="5">
-        <v>17165.628846095729</v>
+        <v>20575.097505669808</v>
       </c>
       <c r="T63" s="5">
-        <v>410914.35751404066</v>
+        <v>416821.92030113685</v>
       </c>
       <c r="U63" s="5">
-        <v>91139.272650182786</v>
+        <v>91885.479420291857</v>
       </c>
       <c r="V63" s="5">
-        <v>32537.787737583352</v>
+        <v>32562.548346499854</v>
       </c>
       <c r="W63" s="5">
-        <v>21669.100123379016</v>
+        <v>21691.078378252838</v>
       </c>
       <c r="X63" s="5">
-        <v>351388.74713085266</v>
+        <v>371765.37180820596</v>
       </c>
       <c r="Y63" s="5">
-        <v>1735558.1851303293</v>
+        <v>1765901.7639694361</v>
       </c>
       <c r="Z63" s="5">
-        <v>74438.690494479524</v>
+        <v>75599.645902358316</v>
       </c>
       <c r="AA63" s="5">
-        <v>141605.81628126712</v>
+        <v>147011.06555663998</v>
       </c>
       <c r="AB63" s="5">
-        <v>412398.78425863571</v>
+        <v>447919.49002964469</v>
       </c>
       <c r="AC63" s="5">
-        <v>86150.647356867892</v>
+        <v>86713.077544935048</v>
       </c>
       <c r="AD63" s="5">
-        <v>48974.537366336561</v>
+        <v>51456.68485938356</v>
       </c>
       <c r="AE63" s="5">
-        <v>42519.059958561003</v>
+        <v>47005.362876645777</v>
       </c>
       <c r="AF63" s="5">
-        <v>108237.63491441526</v>
+        <v>110369.74304379364</v>
       </c>
       <c r="AG63" s="5">
-        <v>34142.929532879687</v>
+        <v>34533.770810614806</v>
       </c>
       <c r="AH63" s="5">
-        <v>55263.493420748579</v>
+        <v>61828.113699025489</v>
       </c>
       <c r="AI63" s="5">
-        <v>60222.559701041522</v>
+        <v>67422.808805630732</v>
       </c>
       <c r="AJ63" s="5">
-        <v>638682.01124281308</v>
+        <v>653991.87882619654</v>
       </c>
       <c r="AK63" s="5">
-        <v>1071813.6358769843</v>
+        <v>1140357.7590270424</v>
       </c>
       <c r="AL63" s="5">
-        <v>158330.17645141578</v>
+        <v>165118.11725202147</v>
       </c>
       <c r="AM63" s="5">
-        <v>16300.531328315263</v>
+        <v>17111.643842924208</v>
       </c>
       <c r="AN63" s="5">
-        <v>24187.623912985655</v>
+        <v>25382.439572438812</v>
       </c>
       <c r="AO63" s="5">
-        <v>20024.73586145461</v>
+        <v>21392.904899924048</v>
       </c>
       <c r="AP63" s="5">
-        <v>125721.35069620852</v>
+        <v>126475.78136496831</v>
       </c>
       <c r="AQ63" s="5">
-        <v>27540.603873256285</v>
+        <v>27900.168607635536</v>
       </c>
       <c r="AR63" s="5">
-        <v>1971.7724635417485</v>
+        <v>2018.9087737517814</v>
       </c>
       <c r="AS63" s="5">
-        <v>2627888.4152140175</v>
+        <v>2722035.9630550509</v>
       </c>
       <c r="AT63" s="5">
-        <v>344744.30824373063</v>
+        <v>352008.29146638373</v>
       </c>
       <c r="AU63" s="5">
-        <v>492782.62033011147</v>
+        <v>505142.32171693211</v>
       </c>
       <c r="AV63" s="5">
-        <v>106592.11785465313</v>
+        <v>109002.01528836841</v>
       </c>
       <c r="AW63" s="5">
-        <v>136135.01462333152</v>
+        <v>135553.68665771457</v>
       </c>
       <c r="AX63" s="5">
-        <v>275802.1823334691</v>
+        <v>289497.10149758012</v>
       </c>
       <c r="AY63" s="5">
-        <v>119208.89453563202</v>
+        <v>121976.4369296761</v>
       </c>
       <c r="AZ63" s="5">
-        <v>102731.32132998997</v>
+        <v>109474.57498173765</v>
       </c>
       <c r="BA63" s="5">
-        <v>668683.4334255727</v>
+        <v>715045.79223926482</v>
       </c>
       <c r="BB63" s="5">
-        <v>180240.09738141546</v>
+        <v>185167.97746684842</v>
       </c>
       <c r="BC63" s="5">
-        <v>40022.448034500616</v>
+        <v>41253.56087058581</v>
       </c>
       <c r="BD63" s="5">
-        <v>8929.901909412567</v>
+        <v>9197.8307097518264</v>
       </c>
       <c r="BE63" s="5">
-        <v>133439.34706886238</v>
+        <v>135389.95529485543</v>
       </c>
       <c r="BF63" s="5">
-        <v>36600.93324836289</v>
+        <v>36910.108277828767</v>
       </c>
       <c r="BG63" s="5">
-        <v>496651.69327050215</v>
+        <v>506293.87262965075</v>
       </c>
       <c r="BH63" s="5">
-        <v>125208.7244419519</v>
+        <v>126833.94608785733</v>
       </c>
       <c r="BI63" s="5">
-        <v>278068.62368679111</v>
+        <v>282986.3759202669</v>
       </c>
       <c r="BJ63" s="5">
-        <v>110712.01765489842</v>
+        <v>112071.54322867026</v>
       </c>
       <c r="BK63" s="5">
         <v>0</v>
       </c>
       <c r="BL63" s="6">
-        <v>13033863.24086847</v>
+        <v>13484875.768359033</v>
       </c>
       <c r="BM63" s="5">
-        <v>10510515.993121587</v>
+        <v>10652547.40649596</v>
       </c>
       <c r="BN63" s="5">
-        <v>3230041.7789858202</v>
+        <v>3231098.1024323255</v>
       </c>
       <c r="BO63" s="5">
-        <v>5391991.0726912729</v>
+        <v>7154611.9231360005</v>
       </c>
       <c r="BP63" s="5">
-        <v>106277.90119054123</v>
+        <v>305874.95578579517</v>
       </c>
       <c r="BQ63" s="5">
-        <v>19134131.06359376</v>
+        <v>16577812.890363032</v>
       </c>
       <c r="BR63" s="6">
-        <v>38372957.809582986</v>
+        <v>37921945.278213121</v>
       </c>
       <c r="BS63" s="5">
-        <v>51406821.050451465</v>
+        <v>51406821.046572179</v>
       </c>
       <c r="BT63" s="5">
         <v>0</v>
@@ -14945,15 +14946,15 @@
         <v>0</v>
       </c>
       <c r="BV63" s="6">
-        <v>51406821.053006634</v>
+        <v>51406821.053006649</v>
       </c>
       <c r="BW63" s="9">
-        <v>51406821.053006634</v>
+        <v>51406821.053006649</v>
       </c>
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
-        <v>195</v>
+      <c r="A64" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
@@ -15179,221 +15180,221 @@
       </c>
     </row>
     <row r="65" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
-        <v>200</v>
+      <c r="A65" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C65" s="5">
-        <v>3734.1526268437119</v>
+        <v>3666.6554174253943</v>
       </c>
       <c r="D65" s="5">
-        <v>803.79773306648883</v>
+        <v>802.27922129864692</v>
       </c>
       <c r="E65" s="5">
-        <v>527.40298374737642</v>
+        <v>529.27152756629903</v>
       </c>
       <c r="F65" s="5">
-        <v>10099.913554154831</v>
+        <v>10124.66788694857</v>
       </c>
       <c r="G65" s="5">
-        <v>10576.161146619608</v>
+        <v>10603.381681090439</v>
       </c>
       <c r="H65" s="5">
-        <v>905698.24360867916</v>
+        <v>901418.55017907405</v>
       </c>
       <c r="I65" s="5">
-        <v>174280.26933514513</v>
+        <v>172168.22128442966</v>
       </c>
       <c r="J65" s="5">
-        <v>62668.24344458626</v>
+        <v>62383.886391505919</v>
       </c>
       <c r="K65" s="5">
-        <v>5482.8629349409721</v>
+        <v>5452.5803850512311</v>
       </c>
       <c r="L65" s="5">
-        <v>85141.333823514215</v>
+        <v>84373.827776394843</v>
       </c>
       <c r="M65" s="5">
-        <v>8980.982222685423</v>
+        <v>8119.7314550818264</v>
       </c>
       <c r="N65" s="5">
-        <v>545.46071786421896</v>
+        <v>481.18028372487197</v>
       </c>
       <c r="O65" s="5">
-        <v>58940.90579311995</v>
+        <v>54442.68306159004</v>
       </c>
       <c r="P65" s="5">
-        <v>32873.926081613856</v>
+        <v>32995.423389951524</v>
       </c>
       <c r="Q65" s="5">
-        <v>16816.370248528721</v>
+        <v>16816.070399758915</v>
       </c>
       <c r="R65" s="5">
-        <v>284982.82896749221</v>
+        <v>280074.12802336016</v>
       </c>
       <c r="S65" s="5">
-        <v>13937.736167692112</v>
+        <v>10528.267508118035</v>
       </c>
       <c r="T65" s="5">
-        <v>600517.85513262858</v>
+        <v>594610.29234553152</v>
       </c>
       <c r="U65" s="5">
-        <v>126903.48084937893</v>
+        <v>126157.2740792699</v>
       </c>
       <c r="V65" s="5">
-        <v>46189.818830448035</v>
+        <v>46165.058221531508</v>
       </c>
       <c r="W65" s="5">
-        <v>39218.02862949649</v>
+        <v>39196.050374622719</v>
       </c>
       <c r="X65" s="5">
-        <v>181443.17042464387</v>
+        <v>161066.5457472906</v>
       </c>
       <c r="Y65" s="5">
-        <v>165530.25564841245</v>
+        <v>135186.67680930626</v>
       </c>
       <c r="Z65" s="5">
-        <v>236376.46396368984</v>
+        <v>235215.50855581116</v>
       </c>
       <c r="AA65" s="5">
-        <v>198202.02375719641</v>
+        <v>192796.77448182349</v>
       </c>
       <c r="AB65" s="5">
-        <v>243124.74161585819</v>
+        <v>207604.03584484942</v>
       </c>
       <c r="AC65" s="5">
-        <v>156352.12870654391</v>
+        <v>155789.6985184768</v>
       </c>
       <c r="AD65" s="5">
-        <v>73038.226849673927</v>
+        <v>70556.079356626899</v>
       </c>
       <c r="AE65" s="5">
-        <v>58339.7711169432</v>
+        <v>53853.46819885842</v>
       </c>
       <c r="AF65" s="5">
-        <v>38738.464921606879</v>
+        <v>36606.356792228515</v>
       </c>
       <c r="AG65" s="5">
-        <v>29562.781147533609</v>
+        <v>29171.939869798491</v>
       </c>
       <c r="AH65" s="5">
-        <v>113172.89693207011</v>
+        <v>106608.27665379328</v>
       </c>
       <c r="AI65" s="5">
-        <v>73311.910102414302</v>
+        <v>66111.660997825034</v>
       </c>
       <c r="AJ65" s="5">
-        <v>296707.35371097096</v>
+        <v>281397.4861275875</v>
       </c>
       <c r="AK65" s="5">
-        <v>634713.72235618869</v>
+        <v>566169.59920613072</v>
       </c>
       <c r="AL65" s="5">
-        <v>92668.675557571041</v>
+        <v>85880.734756965307</v>
       </c>
       <c r="AM65" s="5">
-        <v>18972.922968001509</v>
+        <v>18161.810453392565</v>
       </c>
       <c r="AN65" s="5">
-        <v>17125.427122939811</v>
+        <v>15930.611463486646</v>
       </c>
       <c r="AO65" s="5">
-        <v>23804.0598390458</v>
+        <v>22435.890800576359</v>
       </c>
       <c r="AP65" s="5">
-        <v>157927.81833319829</v>
+        <v>157173.38766443852</v>
       </c>
       <c r="AQ65" s="5">
-        <v>113116.98170896943</v>
+        <v>112757.41697459016</v>
       </c>
       <c r="AR65" s="5">
-        <v>3986.2079557368111</v>
+        <v>3939.0716455267784</v>
       </c>
       <c r="AS65" s="5">
-        <v>1554532.6630152641</v>
+        <v>1460385.1151742316</v>
       </c>
       <c r="AT65" s="5">
-        <v>199170.0077355619</v>
+        <v>191906.02451290889</v>
       </c>
       <c r="AU65" s="5">
-        <v>256283.92507595441</v>
+        <v>243924.223689134</v>
       </c>
       <c r="AV65" s="5">
-        <v>300828.39272548986</v>
+        <v>298418.49529177445</v>
       </c>
       <c r="AW65" s="5">
-        <v>302374.9904476105</v>
+        <v>302956.31841322745</v>
       </c>
       <c r="AX65" s="5">
-        <v>593184.88773577311</v>
+        <v>579489.96857166197</v>
       </c>
       <c r="AY65" s="5">
-        <v>148825.55496350178</v>
+        <v>146058.01256945776</v>
       </c>
       <c r="AZ65" s="5">
-        <v>92631.530060327161</v>
+        <v>85888.276408579492</v>
       </c>
       <c r="BA65" s="5">
-        <v>352477.35316510801</v>
+        <v>306114.99435141601</v>
       </c>
       <c r="BB65" s="5">
-        <v>272821.54891882633</v>
+        <v>267893.66883339349</v>
       </c>
       <c r="BC65" s="5">
-        <v>58101.297009355316</v>
+        <v>56870.18417327007</v>
       </c>
       <c r="BD65" s="5">
-        <v>15144.800863205081</v>
+        <v>14876.872062865819</v>
       </c>
       <c r="BE65" s="5">
-        <v>105506.88027499946</v>
+        <v>103556.27204900654</v>
       </c>
       <c r="BF65" s="5">
-        <v>37751.190299766888</v>
+        <v>37442.015270300995</v>
       </c>
       <c r="BG65" s="5">
-        <v>662057.80740942748</v>
+        <v>652415.62805027911</v>
       </c>
       <c r="BH65" s="5">
-        <v>147591.59542689633</v>
+        <v>145966.37378099095</v>
       </c>
       <c r="BI65" s="5">
-        <v>479011.02125705697</v>
+        <v>474093.26902358106</v>
       </c>
       <c r="BJ65" s="5">
-        <v>76792.239861914393</v>
+        <v>75432.714288142539</v>
       </c>
       <c r="BK65" s="5">
         <v>0</v>
       </c>
       <c r="BL65" s="1">
-        <v>11070223.465817494</v>
+        <v>10619210.938326932</v>
       </c>
       <c r="BM65" s="1">
-        <v>3434211.4606957822</v>
+        <v>3296192.5536170024</v>
       </c>
       <c r="BN65" s="1">
-        <v>55635.114379380364</v>
+        <v>54578.790932875592</v>
       </c>
       <c r="BO65" s="1">
-        <v>3512082.7860294692</v>
+        <v>1749843.124948622</v>
       </c>
       <c r="BP65" s="1">
-        <v>762152.38830751809</v>
+        <v>562566.177973588</v>
       </c>
       <c r="BQ65" s="1">
         <v>0</v>
       </c>
       <c r="BR65" s="1">
-        <v>7764081.7494121501</v>
+        <v>5663180.6474720882</v>
       </c>
       <c r="BS65" s="1">
-        <v>18834305.215229645</v>
+        <v>16282391.58579902</v>
       </c>
       <c r="BT65" s="1">
-        <v>18834305.215229645</v>
+        <v>16282391.58579902</v>
       </c>
       <c r="BU65" s="1">
         <v>0</v>
@@ -15402,206 +15403,206 @@
         <v>0</v>
       </c>
       <c r="BW65" s="1">
-        <v>18834305.215229645</v>
+        <v>16282391.58579902</v>
       </c>
     </row>
     <row r="66" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
-        <v>201</v>
+      <c r="A66" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C66" s="5">
-        <v>6249.6386088944082</v>
+        <v>6249.6386088944073</v>
       </c>
       <c r="D66" s="5">
         <v>1482.8798725996855</v>
       </c>
       <c r="E66" s="5">
-        <v>1157.91184205834</v>
+        <v>1157.9118420583397</v>
       </c>
       <c r="F66" s="5">
-        <v>16202.223316452162</v>
+        <v>16202.22331645216</v>
       </c>
       <c r="G66" s="5">
-        <v>17098.619200377187</v>
+        <v>17098.61920037719</v>
       </c>
       <c r="H66" s="5">
-        <v>869655.6368963127</v>
+        <v>869655.31575369346</v>
       </c>
       <c r="I66" s="5">
-        <v>270447.11025969859</v>
+        <v>270447.10774411727</v>
       </c>
       <c r="J66" s="5">
-        <v>63943.745391364449</v>
+        <v>63943.699770198335</v>
       </c>
       <c r="K66" s="5">
-        <v>10700.402015514861</v>
+        <v>10700.953234188526</v>
       </c>
       <c r="L66" s="5">
-        <v>119410.66622758996</v>
+        <v>119416.10078270111</v>
       </c>
       <c r="M66" s="5">
-        <v>12128.834648333659</v>
+        <v>12128.834648333657</v>
       </c>
       <c r="N66" s="5">
-        <v>690.76171316438172</v>
+        <v>690.76171316438194</v>
       </c>
       <c r="O66" s="5">
-        <v>54924.874944379248</v>
+        <v>54932.657421875389</v>
       </c>
       <c r="P66" s="5">
-        <v>57512.592924224773</v>
+        <v>57512.59292422478</v>
       </c>
       <c r="Q66" s="5">
-        <v>36882.225663341327</v>
+        <v>36882.606411210363</v>
       </c>
       <c r="R66" s="5">
-        <v>569444.17915234971</v>
+        <v>569458.20534826803</v>
       </c>
       <c r="S66" s="5">
-        <v>17880.195791988492</v>
+        <v>17883.087366634871</v>
       </c>
       <c r="T66" s="5">
-        <v>347655.37693919154</v>
+        <v>347656.14121315995</v>
       </c>
       <c r="U66" s="5">
-        <v>112181.84745964689</v>
+        <v>112182.52910383308</v>
       </c>
       <c r="V66" s="5">
-        <v>28929.921395267844</v>
+        <v>28930.113487532617</v>
       </c>
       <c r="W66" s="5">
         <v>27849.172036932061</v>
       </c>
       <c r="X66" s="5">
-        <v>93264.496680093842</v>
+        <v>93269.823993178376</v>
       </c>
       <c r="Y66" s="5">
-        <v>251892.84885276254</v>
+        <v>251892.96314204432</v>
       </c>
       <c r="Z66" s="5">
-        <v>47241.577661435011</v>
+        <v>47241.577661435003</v>
       </c>
       <c r="AA66" s="5">
-        <v>63983.598353854584</v>
+        <v>63983.59835385457</v>
       </c>
       <c r="AB66" s="5">
-        <v>136073.17549044496</v>
+        <v>136080.66566802238</v>
       </c>
       <c r="AC66" s="5">
-        <v>33346.417239272268</v>
+        <v>33343.142934977244</v>
       </c>
       <c r="AD66" s="5">
-        <v>32807.490474533355</v>
+        <v>32807.490474533348</v>
       </c>
       <c r="AE66" s="5">
-        <v>18914.275877842287</v>
+        <v>18926.091137132942</v>
       </c>
       <c r="AF66" s="5">
-        <v>36578.684369276751</v>
+        <v>36578.684369276736</v>
       </c>
       <c r="AG66" s="5">
-        <v>11082.747355313955</v>
+        <v>11082.747355313953</v>
       </c>
       <c r="AH66" s="5">
-        <v>33592.192610298742</v>
+        <v>33592.192610298727</v>
       </c>
       <c r="AI66" s="5">
-        <v>21317.185225625082</v>
+        <v>21315.572567134066</v>
       </c>
       <c r="AJ66" s="5">
-        <v>218149.75938962362</v>
+        <v>218164.38521690806</v>
       </c>
       <c r="AK66" s="5">
-        <v>282345.2889178709</v>
+        <v>282348.80719832698</v>
       </c>
       <c r="AL66" s="5">
-        <v>52704.830026496733</v>
+        <v>52704.830026496726</v>
       </c>
       <c r="AM66" s="5">
-        <v>11341.684306744728</v>
+        <v>11341.684306744726</v>
       </c>
       <c r="AN66" s="5">
-        <v>15016.120665246061</v>
+        <v>15016.120665246057</v>
       </c>
       <c r="AO66" s="5">
-        <v>14755.7348240875</v>
+        <v>14755.734824087496</v>
       </c>
       <c r="AP66" s="5">
-        <v>79679.971369932318</v>
+        <v>79679.971369932304</v>
       </c>
       <c r="AQ66" s="5">
-        <v>8772.0845023950551</v>
+        <v>8772.0845023950533</v>
       </c>
       <c r="AR66" s="5">
-        <v>2562.6303823487933</v>
+        <v>2562.6303823487938</v>
       </c>
       <c r="AS66" s="5">
         <v>1086367.0623405238</v>
       </c>
       <c r="AT66" s="5">
-        <v>493865.61461126123</v>
+        <v>493866.21698297356</v>
       </c>
       <c r="AU66" s="5">
-        <v>744027.46449237189</v>
+        <v>744034.96030844189</v>
       </c>
       <c r="AV66" s="5">
-        <v>145589.28536336674</v>
+        <v>145589.28536336671</v>
       </c>
       <c r="AW66" s="5">
-        <v>90612.048434602868</v>
+        <v>90611.973182539601</v>
       </c>
       <c r="AX66" s="5">
-        <v>186418.69268882208</v>
+        <v>186419.07600174448</v>
       </c>
       <c r="AY66" s="5">
-        <v>121988.35147734157</v>
+        <v>121996.18169594355</v>
       </c>
       <c r="AZ66" s="5">
-        <v>122983.34898151446</v>
+        <v>122986.80372692291</v>
       </c>
       <c r="BA66" s="5">
-        <v>328532.75756862998</v>
+        <v>328550.884054681</v>
       </c>
       <c r="BB66" s="5">
-        <v>308098.26369879983</v>
+        <v>308143.10503531934</v>
       </c>
       <c r="BC66" s="5">
-        <v>147233.3132582847</v>
+        <v>147233.31325828476</v>
       </c>
       <c r="BD66" s="5">
-        <v>33635.850916356074</v>
+        <v>33635.850916356081</v>
       </c>
       <c r="BE66" s="5">
         <v>78183.833720522263</v>
       </c>
       <c r="BF66" s="5">
-        <v>49092.474811932429</v>
+        <v>49092.474811932436</v>
       </c>
       <c r="BG66" s="5">
-        <v>1167160.1657290987</v>
+        <v>1167160.1657290992</v>
       </c>
       <c r="BH66" s="5">
-        <v>486198.32203476876</v>
+        <v>486203.02253340487</v>
       </c>
       <c r="BI66" s="5">
-        <v>296734.0414195648</v>
+        <v>296735.80764923897</v>
       </c>
       <c r="BJ66" s="5">
-        <v>116770.03875853059</v>
+        <v>116770.27774414347</v>
       </c>
       <c r="BK66" s="5">
         <v>0</v>
       </c>
       <c r="BL66" s="1">
-        <v>10111342.541181475</v>
+        <v>10111502.245615579</v>
       </c>
     </row>
     <row r="67" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
-        <v>202</v>
+      <c r="A67" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>66</v>
@@ -15610,192 +15611,192 @@
         <v>16491.692146105594</v>
       </c>
       <c r="D67" s="5">
-        <v>3793.3912474003132</v>
+        <v>3793.3912474003141</v>
       </c>
       <c r="E67" s="5">
-        <v>2848.4208779416599</v>
+        <v>2848.4208779416595</v>
       </c>
       <c r="F67" s="5">
-        <v>40178.770579547832</v>
+        <v>40178.770579547825</v>
       </c>
       <c r="G67" s="5">
         <v>44477.40687522282</v>
       </c>
       <c r="H67" s="5">
-        <v>2292246.1284711077</v>
+        <v>2292246.4496137267</v>
       </c>
       <c r="I67" s="5">
-        <v>684642.53102293832</v>
+        <v>684642.53353851975</v>
       </c>
       <c r="J67" s="5">
-        <v>157193.20022582417</v>
+        <v>157193.24584699029</v>
       </c>
       <c r="K67" s="5">
-        <v>27879.671352798887</v>
+        <v>27879.120134125227</v>
       </c>
       <c r="L67" s="5">
-        <v>307669.57748888677</v>
+        <v>307664.14293377561</v>
       </c>
       <c r="M67" s="5">
-        <v>30146.001782666335</v>
+        <v>30146.001782666342</v>
       </c>
       <c r="N67" s="5">
-        <v>1688.1092388356185</v>
+        <v>1688.1092388356183</v>
       </c>
       <c r="O67" s="5">
-        <v>135121.47916712076</v>
+        <v>135113.69668962463</v>
       </c>
       <c r="P67" s="5">
         <v>94812.40707577522</v>
       </c>
       <c r="Q67" s="5">
-        <v>84957.77433665868</v>
+        <v>84957.393588789622</v>
       </c>
       <c r="R67" s="5">
-        <v>1346391.0727547938</v>
+        <v>1346377.0465588754</v>
       </c>
       <c r="S67" s="5">
-        <v>39805.816887731518</v>
+        <v>39802.92531308515</v>
       </c>
       <c r="T67" s="5">
-        <v>1221228.7030608081</v>
+        <v>1221227.9387868396</v>
       </c>
       <c r="U67" s="5">
-        <v>345660.76254035305</v>
+        <v>345660.08089616691</v>
       </c>
       <c r="V67" s="5">
-        <v>100362.33060473218</v>
+        <v>100362.13851246741</v>
       </c>
       <c r="W67" s="5">
         <v>93352.885963067965</v>
       </c>
       <c r="X67" s="5">
-        <v>193102.57931990613</v>
+        <v>193097.25200682163</v>
       </c>
       <c r="Y67" s="5">
-        <v>571842.04214723757</v>
+        <v>571841.92785795568</v>
       </c>
       <c r="Z67" s="5">
-        <v>101931.80483856499</v>
+        <v>101931.80483856495</v>
       </c>
       <c r="AA67" s="5">
         <v>128666.44264614541</v>
       </c>
       <c r="AB67" s="5">
-        <v>267970.31350955501</v>
+        <v>267962.82333197759</v>
       </c>
       <c r="AC67" s="5">
-        <v>72350.306760727733</v>
+        <v>72353.58106502275</v>
       </c>
       <c r="AD67" s="5">
-        <v>66899.389025466633</v>
+        <v>66899.389025466618</v>
       </c>
       <c r="AE67" s="5">
-        <v>33934.086122157707</v>
+        <v>33922.270862867059</v>
       </c>
       <c r="AF67" s="5">
-        <v>69118.039630723244</v>
+        <v>69118.039630723259</v>
       </c>
       <c r="AG67" s="5">
         <v>20027.285394686038</v>
       </c>
       <c r="AH67" s="5">
-        <v>68722.672389701242</v>
+        <v>68722.672389701256</v>
       </c>
       <c r="AI67" s="5">
-        <v>40902.880274374911</v>
+        <v>40904.49293286592</v>
       </c>
       <c r="AJ67" s="5">
-        <v>409266.86661037634</v>
+        <v>409252.24078309204</v>
       </c>
       <c r="AK67" s="5">
-        <v>556464.78508212895</v>
+        <v>556461.26680167287</v>
       </c>
       <c r="AL67" s="5">
-        <v>96468.552473503267</v>
+        <v>96468.552473503238</v>
       </c>
       <c r="AM67" s="5">
-        <v>19768.348443255265</v>
+        <v>19768.348443255261</v>
       </c>
       <c r="AN67" s="5">
-        <v>28460.537834753934</v>
+        <v>28460.53783475393</v>
       </c>
       <c r="AO67" s="5">
-        <v>28720.923675912494</v>
+        <v>28720.923675912491</v>
       </c>
       <c r="AP67" s="5">
-        <v>118959.91413006766</v>
+        <v>118959.91413006767</v>
       </c>
       <c r="AQ67" s="5">
         <v>19702.365497604944</v>
       </c>
       <c r="AR67" s="5">
-        <v>3922.819617651207</v>
+        <v>3922.8196176512065</v>
       </c>
       <c r="AS67" s="5">
         <v>1358365.537659476</v>
       </c>
       <c r="AT67" s="5">
-        <v>682845.00338873861</v>
+        <v>682844.40101702628</v>
       </c>
       <c r="AU67" s="5">
-        <v>1031845.2175076281</v>
+        <v>1031837.7216915581</v>
       </c>
       <c r="AV67" s="5">
-        <v>230681.23263663324</v>
+        <v>230681.23263663327</v>
       </c>
       <c r="AW67" s="5">
-        <v>142104.30956539715</v>
+        <v>142104.38481746044</v>
       </c>
       <c r="AX67" s="5">
-        <v>289689.31731117796</v>
+        <v>289688.93399825552</v>
       </c>
       <c r="AY67" s="5">
-        <v>190841.86252265854</v>
+        <v>190834.03230405654</v>
       </c>
       <c r="AZ67" s="5">
-        <v>150657.80851848552</v>
+        <v>150654.35377307708</v>
       </c>
       <c r="BA67" s="5">
-        <v>375549.13493136998</v>
+        <v>375531.00844531896</v>
       </c>
       <c r="BB67" s="5">
-        <v>398776.23630120017</v>
+        <v>398731.39496468054</v>
       </c>
       <c r="BC67" s="5">
-        <v>181316.71474171529</v>
+        <v>181316.71474171526</v>
       </c>
       <c r="BD67" s="5">
-        <v>42373.971083643926</v>
+        <v>42373.971083643919</v>
       </c>
       <c r="BE67" s="5">
         <v>702441.11627947772</v>
       </c>
       <c r="BF67" s="5">
-        <v>41976.425188067573</v>
+        <v>41976.425188067558</v>
       </c>
       <c r="BG67" s="5">
-        <v>338775.33427090157</v>
+        <v>338775.33427090105</v>
       </c>
       <c r="BH67" s="5">
-        <v>158629.72796523129</v>
+        <v>158625.02746659523</v>
       </c>
       <c r="BI67" s="5">
-        <v>156837.05858043517</v>
+        <v>156835.29235076101</v>
       </c>
       <c r="BJ67" s="5">
-        <v>92381.211241469209</v>
+        <v>92380.972255856323</v>
       </c>
       <c r="BK67" s="5">
         <v>0</v>
       </c>
       <c r="BL67" s="1">
-        <v>16554238.30881853</v>
+        <v>16554078.604384422</v>
       </c>
     </row>
     <row r="68" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
-        <v>203</v>
+      <c r="A68" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>67</v>
@@ -15804,10 +15805,10 @@
         <v>378.723995</v>
       </c>
       <c r="D68" s="5">
-        <v>100.97087999999999</v>
+        <v>100.97087999999998</v>
       </c>
       <c r="E68" s="5">
-        <v>76.814279999999997</v>
+        <v>76.814279999999982</v>
       </c>
       <c r="F68" s="5">
         <v>1122.319704</v>
@@ -15816,28 +15817,28 @@
         <v>1177.5728844</v>
       </c>
       <c r="H68" s="5">
-        <v>57215.705049034696</v>
+        <v>57215.705049034717</v>
       </c>
       <c r="I68" s="5">
         <v>18321.560947107799</v>
       </c>
       <c r="J68" s="5">
-        <v>4122.9774284163996</v>
+        <v>4122.9774284164005</v>
       </c>
       <c r="K68" s="5">
-        <v>738.59575337174704</v>
+        <v>738.59575337174749</v>
       </c>
       <c r="L68" s="5">
-        <v>7875.9848778328296</v>
+        <v>7875.9848778328287</v>
       </c>
       <c r="M68" s="5">
-        <v>816.87066899999991</v>
+        <v>816.87066899999979</v>
       </c>
       <c r="N68" s="5">
         <v>47.685048000000002</v>
       </c>
       <c r="O68" s="5">
-        <v>3578.2287884999996</v>
+        <v>3578.2287885000001</v>
       </c>
       <c r="P68" s="5">
         <v>2675</v>
@@ -15849,10 +15850,10 @@
         <v>33548.802923056501</v>
       </c>
       <c r="S68" s="5">
-        <v>956.23677228000008</v>
+        <v>956.23677227999997</v>
       </c>
       <c r="T68" s="5">
-        <v>26238.320000000003</v>
+        <v>26238.32</v>
       </c>
       <c r="U68" s="5">
         <v>8355.09</v>
@@ -15861,13 +15862,13 @@
         <v>2220.348</v>
       </c>
       <c r="W68" s="5">
-        <v>2055.2419999999997</v>
+        <v>2055.2420000000002</v>
       </c>
       <c r="X68" s="5">
         <v>7303.5239999999994</v>
       </c>
       <c r="Y68" s="5">
-        <v>14604.009000000002</v>
+        <v>14604.008999999998</v>
       </c>
       <c r="Z68" s="5">
         <v>3448.7174999999997</v>
@@ -15879,22 +15880,22 @@
         <v>9389.8109999999997</v>
       </c>
       <c r="AC68" s="5">
-        <v>2492.3760000000002</v>
+        <v>2492.3759999999997</v>
       </c>
       <c r="AD68" s="5">
-        <v>2695.4205000000002</v>
+        <v>2695.4204999999997</v>
       </c>
       <c r="AE68" s="5">
-        <v>1246.1880000000001</v>
+        <v>1246.1879999999999</v>
       </c>
       <c r="AF68" s="5">
-        <v>2492.3760000000002</v>
+        <v>2492.3759999999997</v>
       </c>
       <c r="AG68" s="5">
         <v>768.01724999999999</v>
       </c>
       <c r="AH68" s="5">
-        <v>1999.4849999999999</v>
+        <v>1999.4849999999997</v>
       </c>
       <c r="AI68" s="5">
         <v>1536.0345</v>
@@ -15903,7 +15904,7 @@
         <v>13968.474</v>
       </c>
       <c r="AK68" s="5">
-        <v>18953.226000000002</v>
+        <v>18953.225999999999</v>
       </c>
       <c r="AL68" s="5">
         <v>3448.7174999999997</v>
@@ -15921,22 +15922,22 @@
         <v>4202.0144999999993</v>
       </c>
       <c r="AQ68" s="5">
-        <v>1175.5500000000002</v>
+        <v>1175.55</v>
       </c>
       <c r="AR68" s="5">
         <v>164.55</v>
       </c>
       <c r="AS68" s="5">
-        <v>62387.4</v>
+        <v>62387.399999999994</v>
       </c>
       <c r="AT68" s="5">
-        <v>27371.382000000001</v>
+        <v>27371.381999999994</v>
       </c>
       <c r="AU68" s="5">
-        <v>42465.318000000007</v>
+        <v>42465.317999999992</v>
       </c>
       <c r="AV68" s="5">
-        <v>9645.2819999999992</v>
+        <v>9645.2820000000011</v>
       </c>
       <c r="AW68" s="5">
         <v>6035.442</v>
@@ -15945,10 +15946,10 @@
         <v>14724.99</v>
       </c>
       <c r="AY68" s="5">
-        <v>8679.1859999999997</v>
+        <v>8679.1860000000015</v>
       </c>
       <c r="AZ68" s="5">
-        <v>7655.8425000000007</v>
+        <v>7655.8424999999988</v>
       </c>
       <c r="BA68" s="5">
         <v>17201.107499999998</v>
@@ -15963,7 +15964,7 @@
         <v>2235.3780000000002</v>
       </c>
       <c r="BE68" s="5">
-        <v>14185.050000000001</v>
+        <v>14185.05</v>
       </c>
       <c r="BF68" s="5">
         <v>2231.1</v>
@@ -15975,21 +15976,21 @@
         <v>8111.95</v>
       </c>
       <c r="BI68" s="5">
-        <v>6578.9</v>
+        <v>6578.8999999999987</v>
       </c>
       <c r="BJ68" s="5">
-        <v>5298.75</v>
+        <v>5298.7499999999964</v>
       </c>
       <c r="BK68" s="5">
         <v>0</v>
       </c>
       <c r="BL68" s="1">
-        <v>555499.14999999979</v>
+        <v>555499.14999999967</v>
       </c>
     </row>
     <row r="69" spans="1:75" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="7">
-        <v>209</v>
+      <c r="A69" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>68</v>
@@ -15998,13 +15999,13 @@
         <v>23120.054750000003</v>
       </c>
       <c r="D69" s="6">
-        <v>5377.2419999999984</v>
+        <v>5377.2419999999993</v>
       </c>
       <c r="E69" s="6">
-        <v>4083.1469999999999</v>
+        <v>4083.1469999999995</v>
       </c>
       <c r="F69" s="6">
-        <v>57503.313599999994</v>
+        <v>57503.313599999987</v>
       </c>
       <c r="G69" s="6">
         <v>62753.598960000003</v>
@@ -16013,10 +16014,10 @@
         <v>3219117.4704164551</v>
       </c>
       <c r="I69" s="6">
-        <v>973411.20222974475</v>
+        <v>973411.20222974487</v>
       </c>
       <c r="J69" s="6">
-        <v>225259.92304560501</v>
+        <v>225259.92304560504</v>
       </c>
       <c r="K69" s="6">
         <v>39318.669121685496</v>
@@ -16037,19 +16038,19 @@
         <v>155000</v>
       </c>
       <c r="Q69" s="6">
-        <v>124000</v>
+        <v>123999.99999999999</v>
       </c>
       <c r="R69" s="6">
-        <v>1949384.0548302</v>
+        <v>1949384.0548301998</v>
       </c>
       <c r="S69" s="6">
-        <v>58642.249452000004</v>
+        <v>58642.249452000018</v>
       </c>
       <c r="T69" s="6">
         <v>1595122.3999999997</v>
       </c>
       <c r="U69" s="6">
-        <v>466197.69999999995</v>
+        <v>466197.7</v>
       </c>
       <c r="V69" s="6">
         <v>131512.60000000003</v>
@@ -16064,22 +16065,22 @@
         <v>838338.9</v>
       </c>
       <c r="Z69" s="6">
-        <v>152622.1</v>
+        <v>152622.09999999995</v>
       </c>
       <c r="AA69" s="6">
-        <v>197055.1</v>
+        <v>197055.09999999998</v>
       </c>
       <c r="AB69" s="6">
         <v>413433.29999999993</v>
       </c>
       <c r="AC69" s="6">
-        <v>108189.1</v>
+        <v>108189.09999999999</v>
       </c>
       <c r="AD69" s="6">
-        <v>102402.29999999999</v>
+        <v>102402.29999999996</v>
       </c>
       <c r="AE69" s="6">
-        <v>54094.549999999996</v>
+        <v>54094.55</v>
       </c>
       <c r="AF69" s="6">
         <v>108189.09999999999</v>
@@ -16091,19 +16092,19 @@
         <v>104314.34999999999</v>
       </c>
       <c r="AI69" s="6">
-        <v>63756.1</v>
+        <v>63756.099999999984</v>
       </c>
       <c r="AJ69" s="6">
-        <v>641385.1</v>
+        <v>641385.10000000021</v>
       </c>
       <c r="AK69" s="6">
         <v>857763.29999999981</v>
       </c>
       <c r="AL69" s="6">
-        <v>152622.1</v>
+        <v>152622.09999999995</v>
       </c>
       <c r="AM69" s="6">
-        <v>31878.049999999992</v>
+        <v>31878.049999999988</v>
       </c>
       <c r="AN69" s="6">
         <v>44432.999999999993</v>
@@ -16133,7 +16134,7 @@
         <v>385915.8</v>
       </c>
       <c r="AW69" s="6">
-        <v>238751.80000000002</v>
+        <v>238751.80000000005</v>
       </c>
       <c r="AX69" s="6">
         <v>490833</v>
@@ -16148,10 +16149,10 @@
         <v>721283</v>
       </c>
       <c r="BB69" s="6">
-        <v>726250</v>
+        <v>726249.99999999988</v>
       </c>
       <c r="BC69" s="6">
-        <v>337864.8</v>
+        <v>337864.80000000005</v>
       </c>
       <c r="BD69" s="6">
         <v>78245.2</v>
@@ -16178,12 +16179,12 @@
         <v>0</v>
       </c>
       <c r="BL69" s="1">
-        <v>27221080.000000004</v>
+        <v>27221080</v>
       </c>
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <v>210</v>
+      <c r="A70" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
@@ -16192,10 +16193,10 @@
         <v>28430.61</v>
       </c>
       <c r="D70" s="1">
-        <v>6459.449999999998</v>
+        <v>6459.4499999999989</v>
       </c>
       <c r="E70" s="1">
-        <v>4802.8500000000004</v>
+        <v>4802.8499999999995</v>
       </c>
       <c r="F70" s="1">
         <v>71628.419999999984</v>
@@ -16204,7 +16205,7 @@
         <v>77958.024000000005</v>
       </c>
       <c r="H70" s="1">
-        <v>4588098.518704134</v>
+        <v>4588098.518704135</v>
       </c>
       <c r="I70" s="1">
         <v>1231851.6751225377</v>
@@ -16213,19 +16214,19 @@
         <v>319106.44593745301</v>
       </c>
       <c r="K70" s="1">
-        <v>47407.592756882907</v>
+        <v>47407.592756882914</v>
       </c>
       <c r="L70" s="1">
         <v>562760.25827916444</v>
       </c>
       <c r="M70" s="1">
-        <v>60865.165000000001</v>
+        <v>60865.165000000008</v>
       </c>
       <c r="N70" s="1">
         <v>3554.64</v>
       </c>
       <c r="O70" s="1">
-        <v>326089.97000000009</v>
+        <v>326089.96999999997</v>
       </c>
       <c r="P70" s="1">
         <v>199700.19986675552</v>
@@ -16234,67 +16235,67 @@
         <v>149361.20789779327</v>
       </c>
       <c r="R70" s="1">
-        <v>2389374.66</v>
+        <v>2389374.6600000006</v>
       </c>
       <c r="S70" s="1">
-        <v>88697.947079999998</v>
+        <v>88697.947080000013</v>
       </c>
       <c r="T70" s="1">
-        <v>2610024.4080117047</v>
+        <v>2610024.4080117038</v>
       </c>
       <c r="U70" s="1">
-        <v>684983.70259708969</v>
+        <v>684983.70259708981</v>
       </c>
       <c r="V70" s="1">
-        <v>210509.70637491212</v>
+        <v>210509.70637491206</v>
       </c>
       <c r="W70" s="1">
-        <v>184326.07852531195</v>
+        <v>184326.07852531201</v>
       </c>
       <c r="X70" s="1">
         <v>830454.92408838845</v>
       </c>
       <c r="Y70" s="1">
-        <v>2759109.7937030387</v>
+        <v>2759109.7937030392</v>
       </c>
       <c r="Z70" s="1">
-        <v>464308.74238864298</v>
+        <v>464308.74238864309</v>
       </c>
       <c r="AA70" s="1">
-        <v>538444.31536309922</v>
+        <v>538444.3153630991</v>
       </c>
       <c r="AB70" s="1">
-        <v>1073720.7919098942</v>
+        <v>1073720.7919098944</v>
       </c>
       <c r="AC70" s="1">
         <v>351691.79825948051</v>
       </c>
       <c r="AD70" s="1">
-        <v>224953.52406354848</v>
+        <v>224953.52406354842</v>
       </c>
       <c r="AE70" s="1">
-        <v>155420.83059307383</v>
+        <v>155420.83059307386</v>
       </c>
       <c r="AF70" s="1">
-        <v>256375.05885365274</v>
+        <v>256375.05885365279</v>
       </c>
       <c r="AG70" s="1">
         <v>95965.715503048181</v>
       </c>
       <c r="AH70" s="1">
-        <v>273398.59238890064</v>
+        <v>273398.5923889007</v>
       </c>
       <c r="AI70" s="1">
-        <v>197962.48672300734</v>
+        <v>197962.48672300729</v>
       </c>
       <c r="AJ70" s="1">
-        <v>1583910.0135168072</v>
+        <v>1583910.0135168075</v>
       </c>
       <c r="AK70" s="1">
         <v>2576442.2980268253</v>
       </c>
       <c r="AL70" s="1">
-        <v>405405.13914149825</v>
+        <v>405405.13914149819</v>
       </c>
       <c r="AM70" s="1">
         <v>67331.381074136298</v>
@@ -16333,7 +16334,7 @@
         <v>1363425</v>
       </c>
       <c r="AY70" s="1">
-        <v>591095.90622654185</v>
+        <v>591095.90622654196</v>
       </c>
       <c r="AZ70" s="1">
         <v>477575.36231884058</v>
@@ -16351,7 +16352,7 @@
         <v>102347.87524366472</v>
       </c>
       <c r="BE70" s="1">
-        <v>1034256.4102564103</v>
+        <v>1034256.4102564104</v>
       </c>
       <c r="BF70" s="1">
         <v>167823.71916508535</v>
@@ -16363,16 +16364,16 @@
         <v>926375</v>
       </c>
       <c r="BI70" s="1">
-        <v>1218932.9268292685</v>
+        <v>1218932.9268292682</v>
       </c>
       <c r="BJ70" s="1">
-        <v>402961.80988164811</v>
+        <v>402961.80988164805</v>
       </c>
       <c r="BK70" s="1">
         <v>0</v>
       </c>
       <c r="BL70" s="1">
-        <v>51406821.053006634</v>
+        <v>51406821.053006627</v>
       </c>
     </row>
   </sheetData>

--- a/io betibel.xlsx
+++ b/io betibel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{5ECE58BD-8314-4A0D-8E60-0098AB06E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9A8476-4106-462A-98EE-BBAA3F5E1452}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{5ECE58BD-8314-4A0D-8E60-0098AB06E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017FCD96-55FE-4B0F-B108-181F7EDFE50E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3A7F3E9-C459-4210-B485-72C402A5A280}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B3A7F3E9-C459-4210-B485-72C402A5A280}"/>
   </bookViews>
   <sheets>
     <sheet name="io" sheetId="1" r:id="rId1"/>
@@ -14714,16 +14714,39 @@
       <c r="BL62" s="6">
         <v>0</v>
       </c>
-      <c r="BM62" s="6"/>
-      <c r="BN62" s="6"/>
-      <c r="BO62" s="6"/>
-      <c r="BP62" s="6"/>
-      <c r="BQ62" s="6"/>
-      <c r="BR62" s="6"/>
-      <c r="BS62" s="6"/>
-      <c r="BT62" s="6"/>
-      <c r="BU62" s="6"/>
-      <c r="BV62" s="6"/>
+      <c r="BM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BO62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BP62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BQ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BR62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW62" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
